--- a/utilities/Punto_de_equilibrio.xlsx
+++ b/utilities/Punto_de_equilibrio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MaBel\utilities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE6C900C-9515-406B-A208-B6786B8521BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B51FFB-BE8E-4ED2-9E37-FAB97703844D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E75E3C13-AC3D-4914-9135-F849659ACBFB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{E75E3C13-AC3D-4914-9135-F849659ACBFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Ejercicio Clase" sheetId="3" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -42,12 +45,21 @@
     <author>tc={4B60C5BC-3C9F-47DB-9187-2A1DFB66CF7B}</author>
   </authors>
   <commentList>
-    <comment ref="B21" authorId="0" shapeId="0" xr:uid="{4B60C5BC-3C9F-47DB-9187-2A1DFB66CF7B}">
+    <comment ref="B25" authorId="0" shapeId="0" xr:uid="{4B60C5BC-3C9F-47DB-9187-2A1DFB66CF7B}">
       <text>
-        <t>[Comentario encadenado]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Este valor lo ubica Ud.</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -55,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t xml:space="preserve">Descripción </t>
   </si>
@@ -113,13 +125,40 @@
   <si>
     <t>Total Costo Variable</t>
   </si>
+  <si>
+    <t>Predio</t>
+  </si>
+  <si>
+    <t>Mano de obra</t>
+  </si>
+  <si>
+    <t>Servicios básicos</t>
+  </si>
+  <si>
+    <t>Publicidad y marketing digital</t>
+  </si>
+  <si>
+    <t>Dominio y mantenimiento de plataforma web de pedidos</t>
+  </si>
+  <si>
+    <t>Utensilios y mantenimiento de cocina</t>
+  </si>
+  <si>
+    <t>Equipos de Seguridad y EPP's</t>
+  </si>
+  <si>
+    <t>Merma</t>
+  </si>
+  <si>
+    <t>Insumos</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_ &quot;$&quot;* #,##0.00_ ;_ &quot;$&quot;* \-#,##0.00_ ;_ &quot;$&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;* #,##0.00_ ;_ &quot;$&quot;* \-#,##0.00_ ;_ &quot;$&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -191,41 +230,41 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -312,7 +351,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-EC"/>
+          <a:endParaRPr lang="es-PE"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -970,7 +1009,7 @@
             <c:numRef>
               <c:f>'Ejercicio Clase'!$B$26:$B$226</c:f>
               <c:numCache>
-                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>_ "$"* #,##0.00_ ;_ "$"* \-#,##0.00_ ;_ "$"* "-"??_ ;_ @_ </c:formatCode>
                 <c:ptCount val="201"/>
                 <c:pt idx="0">
                   <c:v>20000</c:v>
@@ -1658,7 +1697,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-EC"/>
+                <a:endParaRPr lang="es-PE"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2302,7 +2341,7 @@
             <c:numRef>
               <c:f>'Ejercicio Clase'!$C$26:$C$226</c:f>
               <c:numCache>
-                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>_ "$"* #,##0.00_ ;_ "$"* \-#,##0.00_ ;_ "$"* "-"??_ ;_ @_ </c:formatCode>
                 <c:ptCount val="201"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -2978,7 +3017,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-EC"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1710371328"/>
@@ -3007,7 +3046,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="_ &quot;$&quot;* #,##0.00_ ;_ &quot;$&quot;* \-#,##0.00_ ;_ &quot;$&quot;* &quot;-&quot;??_ ;_ @_ " sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3039,7 +3078,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-EC"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1710370848"/>
@@ -3080,13 +3119,12 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-EC"/>
+          <a:endParaRPr lang="es-PE"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3094,6 +3132,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3120,7 +3159,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="es-EC"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3199,7 +3238,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-EC"/>
+          <a:endParaRPr lang="es-PE"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3224,7 +3263,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Ejercicio 2'!$B$25</c:f>
+              <c:f>'Ejercicio 2'!$B$29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3253,7 +3292,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Ejercicio 2'!$A$26:$A$226</c:f>
+              <c:f>'Ejercicio 2'!$A$30:$A$230</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="201"/>
@@ -3865,612 +3904,612 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Ejercicio 2'!$B$26:$B$226</c:f>
+              <c:f>'Ejercicio 2'!$B$30:$B$230</c:f>
               <c:numCache>
-                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>_ "$"* #,##0.00_ ;_ "$"* \-#,##0.00_ ;_ "$"* "-"??_ ;_ @_ </c:formatCode>
                 <c:ptCount val="201"/>
                 <c:pt idx="0">
-                  <c:v>20000</c:v>
+                  <c:v>590.55999999999995</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20100</c:v>
+                  <c:v>593.16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20200</c:v>
+                  <c:v>595.76</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20300</c:v>
+                  <c:v>598.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20400</c:v>
+                  <c:v>600.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20500</c:v>
+                  <c:v>603.55999999999995</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20600</c:v>
+                  <c:v>606.16</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>20700</c:v>
+                  <c:v>608.76</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>20800</c:v>
+                  <c:v>611.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>20900</c:v>
+                  <c:v>613.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>21000</c:v>
+                  <c:v>616.55999999999995</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>21100</c:v>
+                  <c:v>619.16</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>21200</c:v>
+                  <c:v>621.76</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>21300</c:v>
+                  <c:v>624.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>21400</c:v>
+                  <c:v>626.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>21500</c:v>
+                  <c:v>629.55999999999995</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>21600</c:v>
+                  <c:v>632.16</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>21700</c:v>
+                  <c:v>634.76</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>21800</c:v>
+                  <c:v>637.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>21900</c:v>
+                  <c:v>639.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>22000</c:v>
+                  <c:v>642.55999999999995</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>22100</c:v>
+                  <c:v>645.16</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>22200</c:v>
+                  <c:v>647.76</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>22300</c:v>
+                  <c:v>650.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>22400</c:v>
+                  <c:v>652.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>22500</c:v>
+                  <c:v>655.56</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>22600</c:v>
+                  <c:v>658.16</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>22700</c:v>
+                  <c:v>660.76</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>22800</c:v>
+                  <c:v>663.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>22900</c:v>
+                  <c:v>665.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>23000</c:v>
+                  <c:v>668.56</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>23100</c:v>
+                  <c:v>671.16</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>23200</c:v>
+                  <c:v>673.76</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>23300</c:v>
+                  <c:v>676.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>23400</c:v>
+                  <c:v>678.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>23500</c:v>
+                  <c:v>681.56</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>23600</c:v>
+                  <c:v>684.16</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>23700</c:v>
+                  <c:v>686.76</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>23800</c:v>
+                  <c:v>689.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>23900</c:v>
+                  <c:v>691.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>24000</c:v>
+                  <c:v>694.56</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>24100</c:v>
+                  <c:v>697.16</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>24200</c:v>
+                  <c:v>699.76</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>24300</c:v>
+                  <c:v>702.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>24400</c:v>
+                  <c:v>704.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>24500</c:v>
+                  <c:v>707.56</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>24600</c:v>
+                  <c:v>710.16</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>24700</c:v>
+                  <c:v>712.76</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>24800</c:v>
+                  <c:v>715.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>24900</c:v>
+                  <c:v>717.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>25000</c:v>
+                  <c:v>720.56</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>25100</c:v>
+                  <c:v>723.16</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>25200</c:v>
+                  <c:v>725.76</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>25300</c:v>
+                  <c:v>728.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>25400</c:v>
+                  <c:v>730.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>25500</c:v>
+                  <c:v>733.56</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>25600</c:v>
+                  <c:v>736.16</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>25700</c:v>
+                  <c:v>738.76</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>25800</c:v>
+                  <c:v>741.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>25900</c:v>
+                  <c:v>743.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>26000</c:v>
+                  <c:v>746.56</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>26100</c:v>
+                  <c:v>749.16</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>26200</c:v>
+                  <c:v>751.76</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>26300</c:v>
+                  <c:v>754.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>26400</c:v>
+                  <c:v>756.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>26500</c:v>
+                  <c:v>759.56</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>26600</c:v>
+                  <c:v>762.16</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>26700</c:v>
+                  <c:v>764.76</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>26800</c:v>
+                  <c:v>767.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>26900</c:v>
+                  <c:v>769.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>27000</c:v>
+                  <c:v>772.56</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>27100</c:v>
+                  <c:v>775.16</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>27200</c:v>
+                  <c:v>777.76</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>27300</c:v>
+                  <c:v>780.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>27400</c:v>
+                  <c:v>782.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>27500</c:v>
+                  <c:v>785.56</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>27600</c:v>
+                  <c:v>788.16</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>27700</c:v>
+                  <c:v>790.76</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>27800</c:v>
+                  <c:v>793.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>27900</c:v>
+                  <c:v>795.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>28000</c:v>
+                  <c:v>798.56</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>28100</c:v>
+                  <c:v>801.16</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>28200</c:v>
+                  <c:v>803.76</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>28300</c:v>
+                  <c:v>806.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>28400</c:v>
+                  <c:v>808.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>28500</c:v>
+                  <c:v>811.56</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>28600</c:v>
+                  <c:v>814.16</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>28700</c:v>
+                  <c:v>816.76</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>28800</c:v>
+                  <c:v>819.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>28900</c:v>
+                  <c:v>821.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>29000</c:v>
+                  <c:v>824.56</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>29100</c:v>
+                  <c:v>827.16</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>29200</c:v>
+                  <c:v>829.76</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>29300</c:v>
+                  <c:v>832.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>29400</c:v>
+                  <c:v>834.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>29500</c:v>
+                  <c:v>837.56</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>29600</c:v>
+                  <c:v>840.16</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>29700</c:v>
+                  <c:v>842.76</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>29800</c:v>
+                  <c:v>845.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>29900</c:v>
+                  <c:v>847.96</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>30000</c:v>
+                  <c:v>850.56</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>30100</c:v>
+                  <c:v>853.16</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>30200</c:v>
+                  <c:v>855.76</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>30300</c:v>
+                  <c:v>858.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>30400</c:v>
+                  <c:v>860.96</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>30500</c:v>
+                  <c:v>863.56</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>30600</c:v>
+                  <c:v>866.16</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>30700</c:v>
+                  <c:v>868.76</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>30800</c:v>
+                  <c:v>871.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>30900</c:v>
+                  <c:v>873.96</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>31000</c:v>
+                  <c:v>876.56</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>31100</c:v>
+                  <c:v>879.16</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>31200</c:v>
+                  <c:v>881.76</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>31300</c:v>
+                  <c:v>884.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>31400</c:v>
+                  <c:v>886.96</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>31500</c:v>
+                  <c:v>889.56</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>31600</c:v>
+                  <c:v>892.16</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>31700</c:v>
+                  <c:v>894.76</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>31800</c:v>
+                  <c:v>897.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>31900</c:v>
+                  <c:v>899.96</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>32000</c:v>
+                  <c:v>902.56</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>32100</c:v>
+                  <c:v>905.16</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>32200</c:v>
+                  <c:v>907.76</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>32300</c:v>
+                  <c:v>910.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>32400</c:v>
+                  <c:v>912.96</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>32500</c:v>
+                  <c:v>915.56</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>32600</c:v>
+                  <c:v>918.16</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>32700</c:v>
+                  <c:v>920.76</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>32800</c:v>
+                  <c:v>923.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>32900</c:v>
+                  <c:v>925.96</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>33000</c:v>
+                  <c:v>928.56</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>33100</c:v>
+                  <c:v>931.16</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>33200</c:v>
+                  <c:v>933.76</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>33300</c:v>
+                  <c:v>936.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>33400</c:v>
+                  <c:v>938.96</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>33500</c:v>
+                  <c:v>941.56</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>33600</c:v>
+                  <c:v>944.16</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>33700</c:v>
+                  <c:v>946.76</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>33800</c:v>
+                  <c:v>949.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>33900</c:v>
+                  <c:v>951.96</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>34000</c:v>
+                  <c:v>954.56</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>34100</c:v>
+                  <c:v>957.16</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>34200</c:v>
+                  <c:v>959.76</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>34300</c:v>
+                  <c:v>962.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>34400</c:v>
+                  <c:v>964.96</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>34500</c:v>
+                  <c:v>967.56</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>34600</c:v>
+                  <c:v>970.16</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>34700</c:v>
+                  <c:v>972.76</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>34800</c:v>
+                  <c:v>975.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>34900</c:v>
+                  <c:v>977.96</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>35000</c:v>
+                  <c:v>980.56</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>35100</c:v>
+                  <c:v>983.16</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>35200</c:v>
+                  <c:v>985.76</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>35300</c:v>
+                  <c:v>988.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>35400</c:v>
+                  <c:v>990.96</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>35500</c:v>
+                  <c:v>993.56</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>35600</c:v>
+                  <c:v>996.16</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>35700</c:v>
+                  <c:v>998.76</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>35800</c:v>
+                  <c:v>1001.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>35900</c:v>
+                  <c:v>1003.96</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>36000</c:v>
+                  <c:v>1006.56</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>36100</c:v>
+                  <c:v>1009.16</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>36200</c:v>
+                  <c:v>1011.76</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>36300</c:v>
+                  <c:v>1014.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>36400</c:v>
+                  <c:v>1016.96</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>36500</c:v>
+                  <c:v>1019.56</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>36600</c:v>
+                  <c:v>1022.16</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>36700</c:v>
+                  <c:v>1024.76</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>36800</c:v>
+                  <c:v>1027.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>36900</c:v>
+                  <c:v>1029.96</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>37000</c:v>
+                  <c:v>1032.56</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>37100</c:v>
+                  <c:v>1035.1599999999999</c:v>
                 </c:pt>
                 <c:pt idx="172">
-                  <c:v>37200</c:v>
+                  <c:v>1037.76</c:v>
                 </c:pt>
                 <c:pt idx="173">
-                  <c:v>37300</c:v>
+                  <c:v>1040.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="174">
-                  <c:v>37400</c:v>
+                  <c:v>1042.96</c:v>
                 </c:pt>
                 <c:pt idx="175">
-                  <c:v>37500</c:v>
+                  <c:v>1045.56</c:v>
                 </c:pt>
                 <c:pt idx="176">
-                  <c:v>37600</c:v>
+                  <c:v>1048.1599999999999</c:v>
                 </c:pt>
                 <c:pt idx="177">
-                  <c:v>37700</c:v>
+                  <c:v>1050.76</c:v>
                 </c:pt>
                 <c:pt idx="178">
-                  <c:v>37800</c:v>
+                  <c:v>1053.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="179">
-                  <c:v>37900</c:v>
+                  <c:v>1055.96</c:v>
                 </c:pt>
                 <c:pt idx="180">
-                  <c:v>38000</c:v>
+                  <c:v>1058.56</c:v>
                 </c:pt>
                 <c:pt idx="181">
-                  <c:v>38100</c:v>
+                  <c:v>1061.1599999999999</c:v>
                 </c:pt>
                 <c:pt idx="182">
-                  <c:v>38200</c:v>
+                  <c:v>1063.76</c:v>
                 </c:pt>
                 <c:pt idx="183">
-                  <c:v>38300</c:v>
+                  <c:v>1066.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="184">
-                  <c:v>38400</c:v>
+                  <c:v>1068.96</c:v>
                 </c:pt>
                 <c:pt idx="185">
-                  <c:v>38500</c:v>
+                  <c:v>1071.56</c:v>
                 </c:pt>
                 <c:pt idx="186">
-                  <c:v>38600</c:v>
+                  <c:v>1074.1599999999999</c:v>
                 </c:pt>
                 <c:pt idx="187">
-                  <c:v>38700</c:v>
+                  <c:v>1076.76</c:v>
                 </c:pt>
                 <c:pt idx="188">
-                  <c:v>38800</c:v>
+                  <c:v>1079.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="189">
-                  <c:v>38900</c:v>
+                  <c:v>1081.96</c:v>
                 </c:pt>
                 <c:pt idx="190">
-                  <c:v>39000</c:v>
+                  <c:v>1084.56</c:v>
                 </c:pt>
                 <c:pt idx="191">
-                  <c:v>39100</c:v>
+                  <c:v>1087.1599999999999</c:v>
                 </c:pt>
                 <c:pt idx="192">
-                  <c:v>39200</c:v>
+                  <c:v>1089.76</c:v>
                 </c:pt>
                 <c:pt idx="193">
-                  <c:v>39300</c:v>
+                  <c:v>1092.3599999999999</c:v>
                 </c:pt>
                 <c:pt idx="194">
-                  <c:v>39400</c:v>
+                  <c:v>1094.96</c:v>
                 </c:pt>
                 <c:pt idx="195">
-                  <c:v>39500</c:v>
+                  <c:v>1097.56</c:v>
                 </c:pt>
                 <c:pt idx="196">
-                  <c:v>39600</c:v>
+                  <c:v>1100.1599999999999</c:v>
                 </c:pt>
                 <c:pt idx="197">
-                  <c:v>39700</c:v>
+                  <c:v>1102.76</c:v>
                 </c:pt>
                 <c:pt idx="198">
-                  <c:v>39800</c:v>
+                  <c:v>1105.3600000000001</c:v>
                 </c:pt>
                 <c:pt idx="199">
-                  <c:v>39900</c:v>
+                  <c:v>1107.96</c:v>
                 </c:pt>
                 <c:pt idx="200">
-                  <c:v>40000</c:v>
+                  <c:v>1110.56</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4487,7 +4526,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Ejercicio 2'!$C$25</c:f>
+              <c:f>'Ejercicio 2'!$C$29</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4555,7 +4594,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-EC"/>
+                <a:endParaRPr lang="es-PE"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -4585,7 +4624,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'Ejercicio 2'!$A$26:$A$226</c:f>
+              <c:f>'Ejercicio 2'!$A$30:$A$230</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="201"/>
@@ -5197,612 +5236,612 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Ejercicio 2'!$C$26:$C$226</c:f>
+              <c:f>'Ejercicio 2'!$C$30:$C$230</c:f>
               <c:numCache>
-                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:formatCode>_ "$"* #,##0.00_ ;_ "$"* \-#,##0.00_ ;_ "$"* "-"??_ ;_ @_ </c:formatCode>
                 <c:ptCount val="201"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>400</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>800</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>198</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>228</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>246</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>258</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>264</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>276</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>282</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>288</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>294</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>312</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>318</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>324</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>330</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>336</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>342</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>348</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>354</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>366</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>372</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>378</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>384</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>396</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>402</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>408</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>414</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>426</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>432</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>438</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>444</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>456</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>462</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>468</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>474</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>486</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>492</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>498</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>504</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>516</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>522</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>528</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>534</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>540</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>546</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>552</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>558</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>564</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>570</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>576</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>582</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>588</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>594</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>606</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>612</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>618</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>624</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>630</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>636</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>642</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>648</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>654</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>666</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>672</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>678</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>684</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>696</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>702</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>708</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>714</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>720</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>726</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>732</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>738</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>756</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>762</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>768</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>774</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>780</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>786</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>792</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>798</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>804</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>816</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>822</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>828</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>834</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>852</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>858</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>864</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>876</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>882</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>888</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>894</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>906</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>912</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>918</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>924</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>930</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>936</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>942</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>948</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>954</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>966</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>972</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>978</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>984</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>990</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>996</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>1002</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>1008</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1014</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>1020</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>1026</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>1032</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>1038</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>1044</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>1056</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>1062</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>1068</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1074</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>1080</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>1086</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>1092</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>1098</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>1104</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>1110</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>1116</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>1122</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>1128</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>1134</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>1140</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>1146</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>1152</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>1158</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>1164</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>1170</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>1176</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>1182</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>1188</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1194</c:v>
+                </c:pt>
+                <c:pt idx="200">
                   <c:v>1200</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1600</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2400</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2800</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3200</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3600</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>4000</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>4400</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4800</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>5200</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5600</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6400</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6800</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7200</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>7600</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>8000</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>8400</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>8800</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>9200</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>9600</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>10400</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>10800</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>11200</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>11600</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>12000</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>12400</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>12800</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>13200</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>13600</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>14000</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>14400</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>14800</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>15200</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>15600</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>16400</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>16800</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>17200</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>17600</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>18000</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>18400</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>18800</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>19200</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>19600</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>20000</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>20400</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>20800</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>21200</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>21600</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>22000</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>22400</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>22800</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>23200</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>23600</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>24000</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>24400</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>24800</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>25200</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>25600</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>26000</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>26400</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>26800</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>27200</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>27600</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>28000</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>28400</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>28800</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>29200</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>29600</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>30000</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>30400</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>30800</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>31200</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>31600</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>32000</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>32400</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>32800</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>33200</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>33600</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>34000</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>34400</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>34800</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>35200</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>35600</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>36000</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>36400</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>36800</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>37200</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>37600</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>38000</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>38400</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>38800</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>39200</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>39600</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>40000</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>40400</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>40800</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>41200</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>41600</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>42000</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>42400</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>42800</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>43200</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>43600</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>44000</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>44400</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>44800</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>45200</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>45600</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>46000</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>46400</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>46800</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>47200</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>47600</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>48000</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>48400</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>48800</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>49200</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>49600</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>50400</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>50800</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>51200</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>51600</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>52000</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>52400</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>52800</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>53200</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>53600</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>54000</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>54400</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>54800</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>55200</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>55600</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>56000</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>56400</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>56800</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>57200</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>57600</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>58000</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>58400</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>58800</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>59200</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>59600</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>60000</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>60400</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>60800</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>61200</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>61600</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>62000</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>62400</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>62800</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>63200</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>63600</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>64000</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>64400</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>64800</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>65200</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>65600</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>66000</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>66400</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>66800</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>67200</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>67600</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>68000</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>68400</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>68800</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>69200</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>69600</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>70000</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>70400</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>70800</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>71200</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>71600</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>72000</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>72400</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>72800</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>73200</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>73600</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>74000</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>74400</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>74800</c:v>
-                </c:pt>
-                <c:pt idx="188">
-                  <c:v>75200</c:v>
-                </c:pt>
-                <c:pt idx="189">
-                  <c:v>75600</c:v>
-                </c:pt>
-                <c:pt idx="190">
-                  <c:v>76000</c:v>
-                </c:pt>
-                <c:pt idx="191">
-                  <c:v>76400</c:v>
-                </c:pt>
-                <c:pt idx="192">
-                  <c:v>76800</c:v>
-                </c:pt>
-                <c:pt idx="193">
-                  <c:v>77200</c:v>
-                </c:pt>
-                <c:pt idx="194">
-                  <c:v>77600</c:v>
-                </c:pt>
-                <c:pt idx="195">
-                  <c:v>78000</c:v>
-                </c:pt>
-                <c:pt idx="196">
-                  <c:v>78400</c:v>
-                </c:pt>
-                <c:pt idx="197">
-                  <c:v>78800</c:v>
-                </c:pt>
-                <c:pt idx="198">
-                  <c:v>79200</c:v>
-                </c:pt>
-                <c:pt idx="199">
-                  <c:v>79600</c:v>
-                </c:pt>
-                <c:pt idx="200">
-                  <c:v>80000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5829,6 +5868,8 @@
         <c:axId val="583106400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="500"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -5875,7 +5916,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-EC"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="583114560"/>
@@ -5886,6 +5927,8 @@
         <c:axId val="583114560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="2500"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -5904,7 +5947,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="_ &quot;$&quot;* #,##0.00_ ;_ &quot;$&quot;* \-#,##0.00_ ;_ &quot;$&quot;* &quot;-&quot;??_ ;_ @_ " sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -5936,11 +5979,11 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-EC"/>
+            <a:endParaRPr lang="es-PE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="583106400"/>
-        <c:crosses val="autoZero"/>
+        <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
@@ -5977,13 +6020,12 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-EC"/>
+          <a:endParaRPr lang="es-PE"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5991,6 +6033,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6017,7 +6060,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="es-EC"/>
+      <a:endParaRPr lang="es-PE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -7464,7 +7507,7 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>114299</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7537,13 +7580,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>4761</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>47624</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -7572,15 +7615,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:colOff>99332</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>167367</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>230606</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7594,9 +7637,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="4857750" y="5781675"/>
-          <a:ext cx="1171575" cy="19050"/>
+        <a:xfrm>
+          <a:off x="6696648" y="6263367"/>
+          <a:ext cx="1514905" cy="23133"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -7626,6 +7669,125 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>210553</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>10026</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>220579</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>30079</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="Conector recto 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1201A87A-B5BD-4DA7-8F38-188CE1EFC670}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="8191500" y="6296526"/>
+          <a:ext cx="10026" cy="972553"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1022684</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>20053</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>330869</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>100263</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Flecha: hacia abajo 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B69654D-3AEC-DF77-D0E4-8FE04FD71D61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="19760771">
+          <a:off x="7620000" y="5544553"/>
+          <a:ext cx="691816" cy="651710"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-PE" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -10732,23 +10894,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8A95A93-FC5C-4DD4-A0AD-5BD9DCA4E701}">
-  <dimension ref="A3:F226"/>
+  <dimension ref="A3:K255"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" style="11" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="18"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -10756,2744 +10918,3116 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B7" s="3">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="5">
-        <f>SUM(B5:B7)</f>
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="B12" s="5">
+        <f>SUM(B5:B11)</f>
+        <v>590.55999999999995</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J15">
+        <v>10</v>
+      </c>
+      <c r="K15">
+        <v>8.4499999999999993</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="E12" s="6" t="s">
+      <c r="B16" s="18"/>
+      <c r="E16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="7">
-        <f>B8/(B21-B18)</f>
-        <v>66.666666666666671</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="F16" s="7">
+        <f>B12/(B25-B22)</f>
+        <v>173.69411764705882</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <f>J16*K15/J15</f>
+        <v>0.84499999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B17" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="3">
-        <v>45</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="B18" s="3">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="7">
-        <f>F12*B21</f>
-        <v>26666.666666666668</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="F19" s="7">
+        <f>F16*B25</f>
+        <v>1042.1647058823528</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="B20" s="3">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="5">
-        <f>SUM(B14:B17)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="B22" s="5">
+        <f>SUM(B18:B21)</f>
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="5">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="B25" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B29" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C29" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="8">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
         <v>0</v>
       </c>
-      <c r="B26" s="13">
-        <f>$B$8+$B$18*A26</f>
-        <v>20000</v>
-      </c>
-      <c r="C26" s="9">
-        <f>$B$21*A26</f>
+      <c r="B30" s="13">
+        <f>$B$12+$B$22*A30</f>
+        <v>590.55999999999995</v>
+      </c>
+      <c r="C30" s="9">
+        <f>$B$25*A30</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="8">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
         <v>1</v>
       </c>
-      <c r="B27" s="13">
-        <f>$B$8+$B$18*A27</f>
-        <v>20100</v>
-      </c>
-      <c r="C27" s="9">
-        <f>$B$21*A27</f>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="8">
+      <c r="B31" s="13">
+        <f>$B$12+$B$22*A31</f>
+        <v>593.16</v>
+      </c>
+      <c r="C31" s="9">
+        <f>$B$25*A31</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="13">
-        <f t="shared" ref="B27:B90" si="0">$B$8+$B$18*A28</f>
-        <v>20200</v>
-      </c>
-      <c r="C28" s="9">
-        <f t="shared" ref="C27:C90" si="1">$B$21*A28</f>
-        <v>800</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="8">
-        <v>3</v>
-      </c>
-      <c r="B29" s="13">
-        <f t="shared" si="0"/>
-        <v>20300</v>
-      </c>
-      <c r="C29" s="9">
-        <f t="shared" si="1"/>
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="8">
-        <v>4</v>
-      </c>
-      <c r="B30" s="13">
-        <f t="shared" si="0"/>
-        <v>20400</v>
-      </c>
-      <c r="C30" s="9">
-        <f t="shared" si="1"/>
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="8">
-        <v>5</v>
-      </c>
-      <c r="B31" s="13">
-        <f t="shared" si="0"/>
-        <v>20500</v>
-      </c>
-      <c r="C31" s="9">
-        <f t="shared" si="1"/>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="8">
-        <v>6</v>
-      </c>
       <c r="B32" s="13">
-        <f t="shared" si="0"/>
-        <v>20600</v>
+        <f>$B$12+$B$22*A32</f>
+        <v>595.76</v>
       </c>
       <c r="C32" s="9">
-        <f t="shared" si="1"/>
-        <v>2400</v>
+        <f t="shared" ref="C32:C94" si="0">$B$25*A32</f>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B33" s="13">
+        <f>$B$12+$B$22*A33</f>
+        <v>598.3599999999999</v>
+      </c>
+      <c r="C33" s="9">
         <f t="shared" si="0"/>
-        <v>20700</v>
-      </c>
-      <c r="C33" s="9">
-        <f t="shared" si="1"/>
-        <v>2800</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B34" s="13">
+        <f>$B$12+$B$22*A34</f>
+        <v>600.95999999999992</v>
+      </c>
+      <c r="C34" s="9">
         <f t="shared" si="0"/>
-        <v>20800</v>
-      </c>
-      <c r="C34" s="9">
-        <f t="shared" si="1"/>
-        <v>3200</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B35" s="13">
+        <f>$B$12+$B$22*A35</f>
+        <v>603.55999999999995</v>
+      </c>
+      <c r="C35" s="9">
         <f t="shared" si="0"/>
-        <v>20900</v>
-      </c>
-      <c r="C35" s="9">
-        <f t="shared" si="1"/>
-        <v>3600</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B36" s="13">
+        <f>$B$12+$B$22*A36</f>
+        <v>606.16</v>
+      </c>
+      <c r="C36" s="9">
         <f t="shared" si="0"/>
-        <v>21000</v>
-      </c>
-      <c r="C36" s="9">
-        <f t="shared" si="1"/>
-        <v>4000</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B37" s="13">
+        <f>$B$12+$B$22*A37</f>
+        <v>608.76</v>
+      </c>
+      <c r="C37" s="9">
         <f t="shared" si="0"/>
-        <v>21100</v>
-      </c>
-      <c r="C37" s="9">
-        <f t="shared" si="1"/>
-        <v>4400</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B38" s="13">
+        <f>$B$12+$B$22*A38</f>
+        <v>611.3599999999999</v>
+      </c>
+      <c r="C38" s="9">
         <f t="shared" si="0"/>
-        <v>21200</v>
-      </c>
-      <c r="C38" s="9">
-        <f t="shared" si="1"/>
-        <v>4800</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B39" s="13">
+        <f>$B$12+$B$22*A39</f>
+        <v>613.95999999999992</v>
+      </c>
+      <c r="C39" s="9">
         <f t="shared" si="0"/>
-        <v>21300</v>
-      </c>
-      <c r="C39" s="9">
-        <f t="shared" si="1"/>
-        <v>5200</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B40" s="13">
+        <f>$B$12+$B$22*A40</f>
+        <v>616.55999999999995</v>
+      </c>
+      <c r="C40" s="9">
         <f t="shared" si="0"/>
-        <v>21400</v>
-      </c>
-      <c r="C40" s="9">
-        <f t="shared" si="1"/>
-        <v>5600</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B41" s="13">
+        <f>$B$12+$B$22*A41</f>
+        <v>619.16</v>
+      </c>
+      <c r="C41" s="9">
         <f t="shared" si="0"/>
-        <v>21500</v>
-      </c>
-      <c r="C41" s="9">
-        <f t="shared" si="1"/>
-        <v>6000</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B42" s="13">
+        <f>$B$12+$B$22*A42</f>
+        <v>621.76</v>
+      </c>
+      <c r="C42" s="9">
         <f t="shared" si="0"/>
-        <v>21600</v>
-      </c>
-      <c r="C42" s="9">
-        <f t="shared" si="1"/>
-        <v>6400</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B43" s="13">
+        <f>$B$12+$B$22*A43</f>
+        <v>624.3599999999999</v>
+      </c>
+      <c r="C43" s="9">
         <f t="shared" si="0"/>
-        <v>21700</v>
-      </c>
-      <c r="C43" s="9">
-        <f t="shared" si="1"/>
-        <v>6800</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B44" s="13">
+        <f>$B$12+$B$22*A44</f>
+        <v>626.95999999999992</v>
+      </c>
+      <c r="C44" s="9">
         <f t="shared" si="0"/>
-        <v>21800</v>
-      </c>
-      <c r="C44" s="9">
-        <f t="shared" si="1"/>
-        <v>7200</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B45" s="13">
+        <f>$B$12+$B$22*A45</f>
+        <v>629.55999999999995</v>
+      </c>
+      <c r="C45" s="9">
         <f t="shared" si="0"/>
-        <v>21900</v>
-      </c>
-      <c r="C45" s="9">
-        <f t="shared" si="1"/>
-        <v>7600</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B46" s="13">
+        <f>$B$12+$B$22*A46</f>
+        <v>632.16</v>
+      </c>
+      <c r="C46" s="9">
         <f t="shared" si="0"/>
-        <v>22000</v>
-      </c>
-      <c r="C46" s="9">
-        <f t="shared" si="1"/>
-        <v>8000</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B47" s="13">
+        <f>$B$12+$B$22*A47</f>
+        <v>634.76</v>
+      </c>
+      <c r="C47" s="9">
         <f t="shared" si="0"/>
-        <v>22100</v>
-      </c>
-      <c r="C47" s="9">
-        <f t="shared" si="1"/>
-        <v>8400</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B48" s="13">
+        <f>$B$12+$B$22*A48</f>
+        <v>637.3599999999999</v>
+      </c>
+      <c r="C48" s="9">
         <f t="shared" si="0"/>
-        <v>22200</v>
-      </c>
-      <c r="C48" s="9">
-        <f t="shared" si="1"/>
-        <v>8800</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B49" s="13">
+        <f>$B$12+$B$22*A49</f>
+        <v>639.95999999999992</v>
+      </c>
+      <c r="C49" s="9">
         <f t="shared" si="0"/>
-        <v>22300</v>
-      </c>
-      <c r="C49" s="9">
-        <f t="shared" si="1"/>
-        <v>9200</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B50" s="13">
+        <f>$B$12+$B$22*A50</f>
+        <v>642.55999999999995</v>
+      </c>
+      <c r="C50" s="9">
         <f t="shared" si="0"/>
-        <v>22400</v>
-      </c>
-      <c r="C50" s="9">
-        <f t="shared" si="1"/>
-        <v>9600</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B51" s="13">
+        <f>$B$12+$B$22*A51</f>
+        <v>645.16</v>
+      </c>
+      <c r="C51" s="9">
         <f t="shared" si="0"/>
-        <v>22500</v>
-      </c>
-      <c r="C51" s="9">
-        <f t="shared" si="1"/>
-        <v>10000</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B52" s="13">
+        <f>$B$12+$B$22*A52</f>
+        <v>647.76</v>
+      </c>
+      <c r="C52" s="9">
         <f t="shared" si="0"/>
-        <v>22600</v>
-      </c>
-      <c r="C52" s="9">
-        <f t="shared" si="1"/>
-        <v>10400</v>
+        <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B53" s="13">
+        <f>$B$12+$B$22*A53</f>
+        <v>650.3599999999999</v>
+      </c>
+      <c r="C53" s="9">
         <f t="shared" si="0"/>
-        <v>22700</v>
-      </c>
-      <c r="C53" s="9">
-        <f t="shared" si="1"/>
-        <v>10800</v>
+        <v>138</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B54" s="13">
+        <f>$B$12+$B$22*A54</f>
+        <v>652.95999999999992</v>
+      </c>
+      <c r="C54" s="9">
         <f t="shared" si="0"/>
-        <v>22800</v>
-      </c>
-      <c r="C54" s="9">
-        <f t="shared" si="1"/>
-        <v>11200</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B55" s="13">
+        <f>$B$12+$B$22*A55</f>
+        <v>655.56</v>
+      </c>
+      <c r="C55" s="9">
         <f t="shared" si="0"/>
-        <v>22900</v>
-      </c>
-      <c r="C55" s="9">
-        <f t="shared" si="1"/>
-        <v>11600</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B56" s="13">
+        <f>$B$12+$B$22*A56</f>
+        <v>658.16</v>
+      </c>
+      <c r="C56" s="9">
         <f t="shared" si="0"/>
-        <v>23000</v>
-      </c>
-      <c r="C56" s="9">
-        <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B57" s="13">
+        <f>$B$12+$B$22*A57</f>
+        <v>660.76</v>
+      </c>
+      <c r="C57" s="9">
         <f t="shared" si="0"/>
-        <v>23100</v>
-      </c>
-      <c r="C57" s="9">
-        <f t="shared" si="1"/>
-        <v>12400</v>
+        <v>162</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B58" s="13">
+        <f>$B$12+$B$22*A58</f>
+        <v>663.3599999999999</v>
+      </c>
+      <c r="C58" s="9">
         <f t="shared" si="0"/>
-        <v>23200</v>
-      </c>
-      <c r="C58" s="9">
-        <f t="shared" si="1"/>
-        <v>12800</v>
+        <v>168</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B59" s="13">
+        <f>$B$12+$B$22*A59</f>
+        <v>665.95999999999992</v>
+      </c>
+      <c r="C59" s="9">
         <f t="shared" si="0"/>
-        <v>23300</v>
-      </c>
-      <c r="C59" s="9">
-        <f t="shared" si="1"/>
-        <v>13200</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B60" s="13">
+        <f>$B$12+$B$22*A60</f>
+        <v>668.56</v>
+      </c>
+      <c r="C60" s="9">
         <f t="shared" si="0"/>
-        <v>23400</v>
-      </c>
-      <c r="C60" s="9">
-        <f t="shared" si="1"/>
-        <v>13600</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B61" s="13">
+        <f>$B$12+$B$22*A61</f>
+        <v>671.16</v>
+      </c>
+      <c r="C61" s="9">
         <f t="shared" si="0"/>
-        <v>23500</v>
-      </c>
-      <c r="C61" s="9">
-        <f t="shared" si="1"/>
-        <v>14000</v>
+        <v>186</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B62" s="13">
+        <f>$B$12+$B$22*A62</f>
+        <v>673.76</v>
+      </c>
+      <c r="C62" s="9">
         <f t="shared" si="0"/>
-        <v>23600</v>
-      </c>
-      <c r="C62" s="9">
-        <f t="shared" si="1"/>
-        <v>14400</v>
+        <v>192</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B63" s="13">
+        <f>$B$12+$B$22*A63</f>
+        <v>676.3599999999999</v>
+      </c>
+      <c r="C63" s="9">
         <f t="shared" si="0"/>
-        <v>23700</v>
-      </c>
-      <c r="C63" s="9">
-        <f t="shared" si="1"/>
-        <v>14800</v>
+        <v>198</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B64" s="13">
+        <f>$B$12+$B$22*A64</f>
+        <v>678.95999999999992</v>
+      </c>
+      <c r="C64" s="9">
         <f t="shared" si="0"/>
-        <v>23800</v>
-      </c>
-      <c r="C64" s="9">
-        <f t="shared" si="1"/>
-        <v>15200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B65" s="13">
+        <f>$B$12+$B$22*A65</f>
+        <v>681.56</v>
+      </c>
+      <c r="C65" s="9">
         <f t="shared" si="0"/>
-        <v>23900</v>
-      </c>
-      <c r="C65" s="9">
-        <f t="shared" si="1"/>
-        <v>15600</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B66" s="13">
+        <f>$B$12+$B$22*A66</f>
+        <v>684.16</v>
+      </c>
+      <c r="C66" s="9">
         <f t="shared" si="0"/>
-        <v>24000</v>
-      </c>
-      <c r="C66" s="9">
-        <f t="shared" si="1"/>
-        <v>16000</v>
+        <v>216</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B67" s="13">
+        <f>$B$12+$B$22*A67</f>
+        <v>686.76</v>
+      </c>
+      <c r="C67" s="9">
         <f t="shared" si="0"/>
-        <v>24100</v>
-      </c>
-      <c r="C67" s="9">
-        <f t="shared" si="1"/>
-        <v>16400</v>
+        <v>222</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B68" s="13">
+        <f>$B$12+$B$22*A68</f>
+        <v>689.3599999999999</v>
+      </c>
+      <c r="C68" s="9">
         <f t="shared" si="0"/>
-        <v>24200</v>
-      </c>
-      <c r="C68" s="9">
-        <f t="shared" si="1"/>
-        <v>16800</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B69" s="13">
+        <f>$B$12+$B$22*A69</f>
+        <v>691.95999999999992</v>
+      </c>
+      <c r="C69" s="9">
         <f t="shared" si="0"/>
-        <v>24300</v>
-      </c>
-      <c r="C69" s="9">
-        <f t="shared" si="1"/>
-        <v>17200</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B70" s="13">
+        <f>$B$12+$B$22*A70</f>
+        <v>694.56</v>
+      </c>
+      <c r="C70" s="9">
         <f t="shared" si="0"/>
-        <v>24400</v>
-      </c>
-      <c r="C70" s="9">
-        <f t="shared" si="1"/>
-        <v>17600</v>
+        <v>240</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B71" s="13">
+        <f>$B$12+$B$22*A71</f>
+        <v>697.16</v>
+      </c>
+      <c r="C71" s="9">
         <f t="shared" si="0"/>
-        <v>24500</v>
-      </c>
-      <c r="C71" s="9">
-        <f t="shared" si="1"/>
-        <v>18000</v>
+        <v>246</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B72" s="13">
+        <f>$B$12+$B$22*A72</f>
+        <v>699.76</v>
+      </c>
+      <c r="C72" s="9">
         <f t="shared" si="0"/>
-        <v>24600</v>
-      </c>
-      <c r="C72" s="9">
-        <f t="shared" si="1"/>
-        <v>18400</v>
+        <v>252</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B73" s="13">
+        <f>$B$12+$B$22*A73</f>
+        <v>702.3599999999999</v>
+      </c>
+      <c r="C73" s="9">
         <f t="shared" si="0"/>
-        <v>24700</v>
-      </c>
-      <c r="C73" s="9">
-        <f t="shared" si="1"/>
-        <v>18800</v>
+        <v>258</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B74" s="13">
+        <f>$B$12+$B$22*A74</f>
+        <v>704.95999999999992</v>
+      </c>
+      <c r="C74" s="9">
         <f t="shared" si="0"/>
-        <v>24800</v>
-      </c>
-      <c r="C74" s="9">
-        <f t="shared" si="1"/>
-        <v>19200</v>
+        <v>264</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B75" s="13">
+        <f>$B$12+$B$22*A75</f>
+        <v>707.56</v>
+      </c>
+      <c r="C75" s="9">
         <f t="shared" si="0"/>
-        <v>24900</v>
-      </c>
-      <c r="C75" s="9">
-        <f t="shared" si="1"/>
-        <v>19600</v>
+        <v>270</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B76" s="13">
+        <f>$B$12+$B$22*A76</f>
+        <v>710.16</v>
+      </c>
+      <c r="C76" s="9">
         <f t="shared" si="0"/>
-        <v>25000</v>
-      </c>
-      <c r="C76" s="9">
-        <f t="shared" si="1"/>
-        <v>20000</v>
+        <v>276</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B77" s="13">
+        <f>$B$12+$B$22*A77</f>
+        <v>712.76</v>
+      </c>
+      <c r="C77" s="9">
         <f t="shared" si="0"/>
-        <v>25100</v>
-      </c>
-      <c r="C77" s="9">
-        <f t="shared" si="1"/>
-        <v>20400</v>
+        <v>282</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B78" s="13">
+        <f>$B$12+$B$22*A78</f>
+        <v>715.3599999999999</v>
+      </c>
+      <c r="C78" s="9">
         <f t="shared" si="0"/>
-        <v>25200</v>
-      </c>
-      <c r="C78" s="9">
-        <f t="shared" si="1"/>
-        <v>20800</v>
+        <v>288</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B79" s="13">
+        <f>$B$12+$B$22*A79</f>
+        <v>717.95999999999992</v>
+      </c>
+      <c r="C79" s="9">
         <f t="shared" si="0"/>
-        <v>25300</v>
-      </c>
-      <c r="C79" s="9">
-        <f t="shared" si="1"/>
-        <v>21200</v>
+        <v>294</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B80" s="13">
+        <f>$B$12+$B$22*A80</f>
+        <v>720.56</v>
+      </c>
+      <c r="C80" s="9">
         <f t="shared" si="0"/>
-        <v>25400</v>
-      </c>
-      <c r="C80" s="9">
-        <f t="shared" si="1"/>
-        <v>21600</v>
+        <v>300</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B81" s="13">
+        <f>$B$12+$B$22*A81</f>
+        <v>723.16</v>
+      </c>
+      <c r="C81" s="9">
         <f t="shared" si="0"/>
-        <v>25500</v>
-      </c>
-      <c r="C81" s="9">
-        <f t="shared" si="1"/>
-        <v>22000</v>
+        <v>306</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B82" s="13">
+        <f>$B$12+$B$22*A82</f>
+        <v>725.76</v>
+      </c>
+      <c r="C82" s="9">
         <f t="shared" si="0"/>
-        <v>25600</v>
-      </c>
-      <c r="C82" s="9">
-        <f t="shared" si="1"/>
-        <v>22400</v>
+        <v>312</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B83" s="13">
+        <f>$B$12+$B$22*A83</f>
+        <v>728.3599999999999</v>
+      </c>
+      <c r="C83" s="9">
         <f t="shared" si="0"/>
-        <v>25700</v>
-      </c>
-      <c r="C83" s="9">
-        <f t="shared" si="1"/>
-        <v>22800</v>
+        <v>318</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B84" s="13">
+        <f>$B$12+$B$22*A84</f>
+        <v>730.95999999999992</v>
+      </c>
+      <c r="C84" s="9">
         <f t="shared" si="0"/>
-        <v>25800</v>
-      </c>
-      <c r="C84" s="9">
-        <f t="shared" si="1"/>
-        <v>23200</v>
+        <v>324</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B85" s="13">
+        <f>$B$12+$B$22*A85</f>
+        <v>733.56</v>
+      </c>
+      <c r="C85" s="9">
         <f t="shared" si="0"/>
-        <v>25900</v>
-      </c>
-      <c r="C85" s="9">
-        <f t="shared" si="1"/>
-        <v>23600</v>
+        <v>330</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B86" s="13">
+        <f>$B$12+$B$22*A86</f>
+        <v>736.16</v>
+      </c>
+      <c r="C86" s="9">
         <f t="shared" si="0"/>
-        <v>26000</v>
-      </c>
-      <c r="C86" s="9">
-        <f t="shared" si="1"/>
-        <v>24000</v>
+        <v>336</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B87" s="13">
+        <f>$B$12+$B$22*A87</f>
+        <v>738.76</v>
+      </c>
+      <c r="C87" s="9">
         <f t="shared" si="0"/>
-        <v>26100</v>
-      </c>
-      <c r="C87" s="9">
-        <f t="shared" si="1"/>
-        <v>24400</v>
+        <v>342</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B88" s="13">
+        <f>$B$12+$B$22*A88</f>
+        <v>741.3599999999999</v>
+      </c>
+      <c r="C88" s="9">
         <f t="shared" si="0"/>
-        <v>26200</v>
-      </c>
-      <c r="C88" s="9">
-        <f t="shared" si="1"/>
-        <v>24800</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B89" s="13">
+        <f>$B$12+$B$22*A89</f>
+        <v>743.95999999999992</v>
+      </c>
+      <c r="C89" s="9">
         <f t="shared" si="0"/>
-        <v>26300</v>
-      </c>
-      <c r="C89" s="9">
-        <f t="shared" si="1"/>
-        <v>25200</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="8">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B90" s="13">
+        <f>$B$12+$B$22*A90</f>
+        <v>746.56</v>
+      </c>
+      <c r="C90" s="9">
         <f t="shared" si="0"/>
-        <v>26400</v>
-      </c>
-      <c r="C90" s="9">
-        <f t="shared" si="1"/>
-        <v>25600</v>
+        <v>360</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B91" s="13">
-        <f t="shared" ref="B91:B154" si="2">$B$8+$B$18*A91</f>
-        <v>26500</v>
+        <f>$B$12+$B$22*A91</f>
+        <v>749.16</v>
       </c>
       <c r="C91" s="9">
-        <f t="shared" ref="C91:C154" si="3">$B$21*A91</f>
-        <v>26000</v>
+        <f t="shared" si="0"/>
+        <v>366</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="8">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B92" s="13">
-        <f t="shared" si="2"/>
-        <v>26600</v>
+        <f>$B$12+$B$22*A92</f>
+        <v>751.76</v>
       </c>
       <c r="C92" s="9">
-        <f t="shared" si="3"/>
-        <v>26400</v>
+        <f t="shared" si="0"/>
+        <v>372</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="8">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B93" s="13">
-        <f t="shared" si="2"/>
-        <v>26700</v>
+        <f>$B$12+$B$22*A93</f>
+        <v>754.3599999999999</v>
       </c>
       <c r="C93" s="9">
-        <f t="shared" si="3"/>
-        <v>26800</v>
+        <f t="shared" si="0"/>
+        <v>378</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="8">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B94" s="13">
-        <f t="shared" si="2"/>
-        <v>26800</v>
+        <f>$B$12+$B$22*A94</f>
+        <v>756.95999999999992</v>
       </c>
       <c r="C94" s="9">
-        <f t="shared" si="3"/>
-        <v>27200</v>
+        <f t="shared" si="0"/>
+        <v>384</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="8">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B95" s="13">
-        <f t="shared" si="2"/>
-        <v>26900</v>
+        <f>$B$12+$B$22*A95</f>
+        <v>759.56</v>
       </c>
       <c r="C95" s="9">
-        <f t="shared" si="3"/>
-        <v>27600</v>
+        <f t="shared" ref="C95:C158" si="1">$B$25*A95</f>
+        <v>390</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="8">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B96" s="13">
-        <f t="shared" si="2"/>
-        <v>27000</v>
+        <f>$B$12+$B$22*A96</f>
+        <v>762.16</v>
       </c>
       <c r="C96" s="9">
-        <f t="shared" si="3"/>
-        <v>28000</v>
+        <f t="shared" si="1"/>
+        <v>396</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="8">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B97" s="13">
-        <f t="shared" si="2"/>
-        <v>27100</v>
+        <f>$B$12+$B$22*A97</f>
+        <v>764.76</v>
       </c>
       <c r="C97" s="9">
-        <f t="shared" si="3"/>
-        <v>28400</v>
+        <f t="shared" si="1"/>
+        <v>402</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="8">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B98" s="13">
-        <f t="shared" si="2"/>
-        <v>27200</v>
+        <f>$B$12+$B$22*A98</f>
+        <v>767.3599999999999</v>
       </c>
       <c r="C98" s="9">
-        <f t="shared" si="3"/>
-        <v>28800</v>
+        <f t="shared" si="1"/>
+        <v>408</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="8">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B99" s="13">
-        <f t="shared" si="2"/>
-        <v>27300</v>
+        <f>$B$12+$B$22*A99</f>
+        <v>769.95999999999992</v>
       </c>
       <c r="C99" s="9">
-        <f t="shared" si="3"/>
-        <v>29200</v>
+        <f t="shared" si="1"/>
+        <v>414</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="8">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B100" s="13">
-        <f t="shared" si="2"/>
-        <v>27400</v>
+        <f>$B$12+$B$22*A100</f>
+        <v>772.56</v>
       </c>
       <c r="C100" s="9">
-        <f t="shared" si="3"/>
-        <v>29600</v>
+        <f t="shared" si="1"/>
+        <v>420</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="8">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B101" s="13">
-        <f t="shared" si="2"/>
-        <v>27500</v>
+        <f>$B$12+$B$22*A101</f>
+        <v>775.16</v>
       </c>
       <c r="C101" s="9">
-        <f t="shared" si="3"/>
-        <v>30000</v>
+        <f t="shared" si="1"/>
+        <v>426</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="8">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B102" s="13">
-        <f t="shared" si="2"/>
-        <v>27600</v>
+        <f>$B$12+$B$22*A102</f>
+        <v>777.76</v>
       </c>
       <c r="C102" s="9">
-        <f t="shared" si="3"/>
-        <v>30400</v>
+        <f t="shared" si="1"/>
+        <v>432</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="8">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B103" s="13">
-        <f t="shared" si="2"/>
-        <v>27700</v>
+        <f>$B$12+$B$22*A103</f>
+        <v>780.3599999999999</v>
       </c>
       <c r="C103" s="9">
-        <f t="shared" si="3"/>
-        <v>30800</v>
+        <f t="shared" si="1"/>
+        <v>438</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="8">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B104" s="13">
-        <f t="shared" si="2"/>
-        <v>27800</v>
+        <f>$B$12+$B$22*A104</f>
+        <v>782.95999999999992</v>
       </c>
       <c r="C104" s="9">
-        <f t="shared" si="3"/>
-        <v>31200</v>
+        <f t="shared" si="1"/>
+        <v>444</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="8">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B105" s="13">
-        <f t="shared" si="2"/>
-        <v>27900</v>
+        <f>$B$12+$B$22*A105</f>
+        <v>785.56</v>
       </c>
       <c r="C105" s="9">
-        <f t="shared" si="3"/>
-        <v>31600</v>
+        <f t="shared" si="1"/>
+        <v>450</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="8">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B106" s="13">
-        <f t="shared" si="2"/>
-        <v>28000</v>
+        <f>$B$12+$B$22*A106</f>
+        <v>788.16</v>
       </c>
       <c r="C106" s="9">
-        <f t="shared" si="3"/>
-        <v>32000</v>
+        <f t="shared" si="1"/>
+        <v>456</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="8">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B107" s="13">
-        <f t="shared" si="2"/>
-        <v>28100</v>
+        <f>$B$12+$B$22*A107</f>
+        <v>790.76</v>
       </c>
       <c r="C107" s="9">
-        <f t="shared" si="3"/>
-        <v>32400</v>
+        <f t="shared" si="1"/>
+        <v>462</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="8">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B108" s="13">
-        <f t="shared" si="2"/>
-        <v>28200</v>
+        <f>$B$12+$B$22*A108</f>
+        <v>793.3599999999999</v>
       </c>
       <c r="C108" s="9">
-        <f t="shared" si="3"/>
-        <v>32800</v>
+        <f t="shared" si="1"/>
+        <v>468</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="8">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B109" s="13">
-        <f t="shared" si="2"/>
-        <v>28300</v>
+        <f>$B$12+$B$22*A109</f>
+        <v>795.95999999999992</v>
       </c>
       <c r="C109" s="9">
-        <f t="shared" si="3"/>
-        <v>33200</v>
+        <f t="shared" si="1"/>
+        <v>474</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="8">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B110" s="13">
-        <f t="shared" si="2"/>
-        <v>28400</v>
+        <f>$B$12+$B$22*A110</f>
+        <v>798.56</v>
       </c>
       <c r="C110" s="9">
-        <f t="shared" si="3"/>
-        <v>33600</v>
+        <f t="shared" si="1"/>
+        <v>480</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="8">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B111" s="13">
-        <f t="shared" si="2"/>
-        <v>28500</v>
+        <f>$B$12+$B$22*A111</f>
+        <v>801.16</v>
       </c>
       <c r="C111" s="9">
-        <f t="shared" si="3"/>
-        <v>34000</v>
+        <f t="shared" si="1"/>
+        <v>486</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="8">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B112" s="13">
-        <f t="shared" si="2"/>
-        <v>28600</v>
+        <f>$B$12+$B$22*A112</f>
+        <v>803.76</v>
       </c>
       <c r="C112" s="9">
-        <f t="shared" si="3"/>
-        <v>34400</v>
+        <f t="shared" si="1"/>
+        <v>492</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="8">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B113" s="13">
-        <f t="shared" si="2"/>
-        <v>28700</v>
+        <f>$B$12+$B$22*A113</f>
+        <v>806.3599999999999</v>
       </c>
       <c r="C113" s="9">
-        <f t="shared" si="3"/>
-        <v>34800</v>
+        <f t="shared" si="1"/>
+        <v>498</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="8">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B114" s="13">
-        <f t="shared" si="2"/>
-        <v>28800</v>
+        <f>$B$12+$B$22*A114</f>
+        <v>808.95999999999992</v>
       </c>
       <c r="C114" s="9">
-        <f t="shared" si="3"/>
-        <v>35200</v>
+        <f t="shared" si="1"/>
+        <v>504</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="8">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B115" s="13">
-        <f t="shared" si="2"/>
-        <v>28900</v>
+        <f>$B$12+$B$22*A115</f>
+        <v>811.56</v>
       </c>
       <c r="C115" s="9">
-        <f t="shared" si="3"/>
-        <v>35600</v>
+        <f t="shared" si="1"/>
+        <v>510</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="8">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B116" s="13">
-        <f t="shared" si="2"/>
-        <v>29000</v>
+        <f>$B$12+$B$22*A116</f>
+        <v>814.16</v>
       </c>
       <c r="C116" s="9">
-        <f t="shared" si="3"/>
-        <v>36000</v>
+        <f t="shared" si="1"/>
+        <v>516</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="8">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B117" s="13">
-        <f t="shared" si="2"/>
-        <v>29100</v>
+        <f>$B$12+$B$22*A117</f>
+        <v>816.76</v>
       </c>
       <c r="C117" s="9">
-        <f t="shared" si="3"/>
-        <v>36400</v>
+        <f t="shared" si="1"/>
+        <v>522</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="8">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B118" s="13">
-        <f t="shared" si="2"/>
-        <v>29200</v>
+        <f>$B$12+$B$22*A118</f>
+        <v>819.3599999999999</v>
       </c>
       <c r="C118" s="9">
-        <f t="shared" si="3"/>
-        <v>36800</v>
+        <f t="shared" si="1"/>
+        <v>528</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="8">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B119" s="13">
-        <f t="shared" si="2"/>
-        <v>29300</v>
+        <f>$B$12+$B$22*A119</f>
+        <v>821.95999999999992</v>
       </c>
       <c r="C119" s="9">
-        <f t="shared" si="3"/>
-        <v>37200</v>
+        <f t="shared" si="1"/>
+        <v>534</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="8">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B120" s="13">
-        <f t="shared" si="2"/>
-        <v>29400</v>
+        <f>$B$12+$B$22*A120</f>
+        <v>824.56</v>
       </c>
       <c r="C120" s="9">
-        <f t="shared" si="3"/>
-        <v>37600</v>
+        <f t="shared" si="1"/>
+        <v>540</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="8">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B121" s="13">
-        <f t="shared" si="2"/>
-        <v>29500</v>
+        <f>$B$12+$B$22*A121</f>
+        <v>827.16</v>
       </c>
       <c r="C121" s="9">
-        <f t="shared" si="3"/>
-        <v>38000</v>
+        <f t="shared" si="1"/>
+        <v>546</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="8">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B122" s="13">
-        <f t="shared" si="2"/>
-        <v>29600</v>
+        <f>$B$12+$B$22*A122</f>
+        <v>829.76</v>
       </c>
       <c r="C122" s="9">
-        <f t="shared" si="3"/>
-        <v>38400</v>
+        <f t="shared" si="1"/>
+        <v>552</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="8">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B123" s="13">
-        <f t="shared" si="2"/>
-        <v>29700</v>
+        <f>$B$12+$B$22*A123</f>
+        <v>832.3599999999999</v>
       </c>
       <c r="C123" s="9">
-        <f t="shared" si="3"/>
-        <v>38800</v>
+        <f t="shared" si="1"/>
+        <v>558</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="8">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B124" s="13">
-        <f t="shared" si="2"/>
-        <v>29800</v>
+        <f>$B$12+$B$22*A124</f>
+        <v>834.95999999999992</v>
       </c>
       <c r="C124" s="9">
-        <f t="shared" si="3"/>
-        <v>39200</v>
+        <f t="shared" si="1"/>
+        <v>564</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="8">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B125" s="13">
-        <f t="shared" si="2"/>
-        <v>29900</v>
+        <f>$B$12+$B$22*A125</f>
+        <v>837.56</v>
       </c>
       <c r="C125" s="9">
-        <f t="shared" si="3"/>
-        <v>39600</v>
+        <f t="shared" si="1"/>
+        <v>570</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="8">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B126" s="13">
-        <f t="shared" si="2"/>
-        <v>30000</v>
+        <f>$B$12+$B$22*A126</f>
+        <v>840.16</v>
       </c>
       <c r="C126" s="9">
-        <f t="shared" si="3"/>
-        <v>40000</v>
+        <f t="shared" si="1"/>
+        <v>576</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="8">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B127" s="13">
-        <f t="shared" si="2"/>
-        <v>30100</v>
+        <f>$B$12+$B$22*A127</f>
+        <v>842.76</v>
       </c>
       <c r="C127" s="9">
-        <f t="shared" si="3"/>
-        <v>40400</v>
+        <f t="shared" si="1"/>
+        <v>582</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="8">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B128" s="13">
-        <f t="shared" si="2"/>
-        <v>30200</v>
+        <f>$B$12+$B$22*A128</f>
+        <v>845.3599999999999</v>
       </c>
       <c r="C128" s="9">
-        <f t="shared" si="3"/>
-        <v>40800</v>
+        <f t="shared" si="1"/>
+        <v>588</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="8">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B129" s="13">
-        <f t="shared" si="2"/>
-        <v>30300</v>
+        <f>$B$12+$B$22*A129</f>
+        <v>847.96</v>
       </c>
       <c r="C129" s="9">
-        <f t="shared" si="3"/>
-        <v>41200</v>
+        <f t="shared" si="1"/>
+        <v>594</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="8">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B130" s="13">
-        <f t="shared" si="2"/>
-        <v>30400</v>
+        <f>$B$12+$B$22*A130</f>
+        <v>850.56</v>
       </c>
       <c r="C130" s="9">
-        <f t="shared" si="3"/>
-        <v>41600</v>
+        <f t="shared" si="1"/>
+        <v>600</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="8">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B131" s="13">
-        <f t="shared" si="2"/>
-        <v>30500</v>
+        <f>$B$12+$B$22*A131</f>
+        <v>853.16</v>
       </c>
       <c r="C131" s="9">
-        <f t="shared" si="3"/>
-        <v>42000</v>
+        <f t="shared" si="1"/>
+        <v>606</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="8">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B132" s="13">
-        <f t="shared" si="2"/>
-        <v>30600</v>
+        <f>$B$12+$B$22*A132</f>
+        <v>855.76</v>
       </c>
       <c r="C132" s="9">
-        <f t="shared" si="3"/>
-        <v>42400</v>
+        <f t="shared" si="1"/>
+        <v>612</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="8">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B133" s="13">
-        <f t="shared" si="2"/>
-        <v>30700</v>
+        <f>$B$12+$B$22*A133</f>
+        <v>858.3599999999999</v>
       </c>
       <c r="C133" s="9">
-        <f t="shared" si="3"/>
-        <v>42800</v>
+        <f t="shared" si="1"/>
+        <v>618</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="8">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B134" s="13">
-        <f t="shared" si="2"/>
-        <v>30800</v>
+        <f>$B$12+$B$22*A134</f>
+        <v>860.96</v>
       </c>
       <c r="C134" s="9">
-        <f t="shared" si="3"/>
-        <v>43200</v>
+        <f t="shared" si="1"/>
+        <v>624</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="8">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B135" s="13">
-        <f t="shared" si="2"/>
-        <v>30900</v>
+        <f>$B$12+$B$22*A135</f>
+        <v>863.56</v>
       </c>
       <c r="C135" s="9">
-        <f t="shared" si="3"/>
-        <v>43600</v>
+        <f t="shared" si="1"/>
+        <v>630</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="8">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B136" s="13">
-        <f t="shared" si="2"/>
-        <v>31000</v>
+        <f>$B$12+$B$22*A136</f>
+        <v>866.16</v>
       </c>
       <c r="C136" s="9">
-        <f t="shared" si="3"/>
-        <v>44000</v>
+        <f t="shared" si="1"/>
+        <v>636</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="8">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B137" s="13">
-        <f t="shared" si="2"/>
-        <v>31100</v>
+        <f>$B$12+$B$22*A137</f>
+        <v>868.76</v>
       </c>
       <c r="C137" s="9">
-        <f t="shared" si="3"/>
-        <v>44400</v>
+        <f t="shared" si="1"/>
+        <v>642</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="8">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B138" s="13">
-        <f t="shared" si="2"/>
-        <v>31200</v>
+        <f>$B$12+$B$22*A138</f>
+        <v>871.3599999999999</v>
       </c>
       <c r="C138" s="9">
-        <f t="shared" si="3"/>
-        <v>44800</v>
+        <f t="shared" si="1"/>
+        <v>648</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="8">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B139" s="13">
-        <f t="shared" si="2"/>
-        <v>31300</v>
+        <f>$B$12+$B$22*A139</f>
+        <v>873.96</v>
       </c>
       <c r="C139" s="9">
-        <f t="shared" si="3"/>
-        <v>45200</v>
+        <f t="shared" si="1"/>
+        <v>654</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="8">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B140" s="13">
-        <f t="shared" si="2"/>
-        <v>31400</v>
+        <f>$B$12+$B$22*A140</f>
+        <v>876.56</v>
       </c>
       <c r="C140" s="9">
-        <f t="shared" si="3"/>
-        <v>45600</v>
+        <f t="shared" si="1"/>
+        <v>660</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="8">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B141" s="13">
-        <f t="shared" si="2"/>
-        <v>31500</v>
+        <f>$B$12+$B$22*A141</f>
+        <v>879.16</v>
       </c>
       <c r="C141" s="9">
-        <f t="shared" si="3"/>
-        <v>46000</v>
+        <f t="shared" si="1"/>
+        <v>666</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="8">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B142" s="13">
-        <f t="shared" si="2"/>
-        <v>31600</v>
+        <f>$B$12+$B$22*A142</f>
+        <v>881.76</v>
       </c>
       <c r="C142" s="9">
-        <f t="shared" si="3"/>
-        <v>46400</v>
+        <f t="shared" si="1"/>
+        <v>672</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="8">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B143" s="13">
-        <f t="shared" si="2"/>
-        <v>31700</v>
+        <f>$B$12+$B$22*A143</f>
+        <v>884.3599999999999</v>
       </c>
       <c r="C143" s="9">
-        <f t="shared" si="3"/>
-        <v>46800</v>
+        <f t="shared" si="1"/>
+        <v>678</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="8">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B144" s="13">
-        <f t="shared" si="2"/>
-        <v>31800</v>
+        <f>$B$12+$B$22*A144</f>
+        <v>886.96</v>
       </c>
       <c r="C144" s="9">
-        <f t="shared" si="3"/>
-        <v>47200</v>
+        <f t="shared" si="1"/>
+        <v>684</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="8">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B145" s="13">
-        <f t="shared" si="2"/>
-        <v>31900</v>
+        <f>$B$12+$B$22*A145</f>
+        <v>889.56</v>
       </c>
       <c r="C145" s="9">
-        <f t="shared" si="3"/>
-        <v>47600</v>
+        <f t="shared" si="1"/>
+        <v>690</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="8">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B146" s="13">
-        <f t="shared" si="2"/>
-        <v>32000</v>
+        <f>$B$12+$B$22*A146</f>
+        <v>892.16</v>
       </c>
       <c r="C146" s="9">
-        <f t="shared" si="3"/>
-        <v>48000</v>
+        <f t="shared" si="1"/>
+        <v>696</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="8">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B147" s="13">
-        <f t="shared" si="2"/>
-        <v>32100</v>
+        <f>$B$12+$B$22*A147</f>
+        <v>894.76</v>
       </c>
       <c r="C147" s="9">
-        <f t="shared" si="3"/>
-        <v>48400</v>
+        <f t="shared" si="1"/>
+        <v>702</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="8">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B148" s="13">
-        <f t="shared" si="2"/>
-        <v>32200</v>
+        <f>$B$12+$B$22*A148</f>
+        <v>897.3599999999999</v>
       </c>
       <c r="C148" s="9">
-        <f t="shared" si="3"/>
-        <v>48800</v>
+        <f t="shared" si="1"/>
+        <v>708</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="8">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B149" s="13">
-        <f t="shared" si="2"/>
-        <v>32300</v>
+        <f>$B$12+$B$22*A149</f>
+        <v>899.96</v>
       </c>
       <c r="C149" s="9">
-        <f t="shared" si="3"/>
-        <v>49200</v>
+        <f t="shared" si="1"/>
+        <v>714</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="8">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B150" s="13">
-        <f t="shared" si="2"/>
-        <v>32400</v>
+        <f>$B$12+$B$22*A150</f>
+        <v>902.56</v>
       </c>
       <c r="C150" s="9">
-        <f t="shared" si="3"/>
-        <v>49600</v>
+        <f t="shared" si="1"/>
+        <v>720</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="8">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B151" s="13">
-        <f t="shared" si="2"/>
-        <v>32500</v>
+        <f>$B$12+$B$22*A151</f>
+        <v>905.16</v>
       </c>
       <c r="C151" s="9">
-        <f t="shared" si="3"/>
-        <v>50000</v>
+        <f t="shared" si="1"/>
+        <v>726</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="8">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B152" s="13">
-        <f t="shared" si="2"/>
-        <v>32600</v>
+        <f>$B$12+$B$22*A152</f>
+        <v>907.76</v>
       </c>
       <c r="C152" s="9">
-        <f t="shared" si="3"/>
-        <v>50400</v>
+        <f t="shared" si="1"/>
+        <v>732</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="8">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B153" s="13">
-        <f t="shared" si="2"/>
-        <v>32700</v>
+        <f>$B$12+$B$22*A153</f>
+        <v>910.3599999999999</v>
       </c>
       <c r="C153" s="9">
-        <f t="shared" si="3"/>
-        <v>50800</v>
+        <f t="shared" si="1"/>
+        <v>738</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="8">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B154" s="13">
-        <f t="shared" si="2"/>
-        <v>32800</v>
+        <f>$B$12+$B$22*A154</f>
+        <v>912.96</v>
       </c>
       <c r="C154" s="9">
-        <f t="shared" si="3"/>
-        <v>51200</v>
+        <f t="shared" si="1"/>
+        <v>744</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="8">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B155" s="13">
-        <f t="shared" ref="B155:B218" si="4">$B$8+$B$18*A155</f>
-        <v>32900</v>
+        <f>$B$12+$B$22*A155</f>
+        <v>915.56</v>
       </c>
       <c r="C155" s="9">
-        <f t="shared" ref="C155:C218" si="5">$B$21*A155</f>
-        <v>51600</v>
+        <f t="shared" si="1"/>
+        <v>750</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="8">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B156" s="13">
-        <f t="shared" si="4"/>
-        <v>33000</v>
+        <f>$B$12+$B$22*A156</f>
+        <v>918.16</v>
       </c>
       <c r="C156" s="9">
-        <f t="shared" si="5"/>
-        <v>52000</v>
+        <f t="shared" si="1"/>
+        <v>756</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="8">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B157" s="13">
-        <f t="shared" si="4"/>
-        <v>33100</v>
+        <f>$B$12+$B$22*A157</f>
+        <v>920.76</v>
       </c>
       <c r="C157" s="9">
-        <f t="shared" si="5"/>
-        <v>52400</v>
+        <f t="shared" si="1"/>
+        <v>762</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="8">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B158" s="13">
-        <f t="shared" si="4"/>
-        <v>33200</v>
+        <f>$B$12+$B$22*A158</f>
+        <v>923.3599999999999</v>
       </c>
       <c r="C158" s="9">
-        <f t="shared" si="5"/>
-        <v>52800</v>
+        <f t="shared" si="1"/>
+        <v>768</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="8">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B159" s="13">
-        <f t="shared" si="4"/>
-        <v>33300</v>
+        <f>$B$12+$B$22*A159</f>
+        <v>925.96</v>
       </c>
       <c r="C159" s="9">
-        <f t="shared" si="5"/>
-        <v>53200</v>
+        <f t="shared" ref="C159:C222" si="2">$B$25*A159</f>
+        <v>774</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="8">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B160" s="13">
-        <f t="shared" si="4"/>
-        <v>33400</v>
+        <f>$B$12+$B$22*A160</f>
+        <v>928.56</v>
       </c>
       <c r="C160" s="9">
-        <f t="shared" si="5"/>
-        <v>53600</v>
+        <f t="shared" si="2"/>
+        <v>780</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="8">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B161" s="13">
-        <f t="shared" si="4"/>
-        <v>33500</v>
+        <f>$B$12+$B$22*A161</f>
+        <v>931.16</v>
       </c>
       <c r="C161" s="9">
-        <f t="shared" si="5"/>
-        <v>54000</v>
+        <f t="shared" si="2"/>
+        <v>786</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="8">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B162" s="13">
-        <f t="shared" si="4"/>
-        <v>33600</v>
+        <f>$B$12+$B$22*A162</f>
+        <v>933.76</v>
       </c>
       <c r="C162" s="9">
-        <f t="shared" si="5"/>
-        <v>54400</v>
+        <f t="shared" si="2"/>
+        <v>792</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="8">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B163" s="13">
-        <f t="shared" si="4"/>
-        <v>33700</v>
+        <f>$B$12+$B$22*A163</f>
+        <v>936.3599999999999</v>
       </c>
       <c r="C163" s="9">
-        <f t="shared" si="5"/>
-        <v>54800</v>
+        <f t="shared" si="2"/>
+        <v>798</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="8">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B164" s="13">
-        <f t="shared" si="4"/>
-        <v>33800</v>
+        <f>$B$12+$B$22*A164</f>
+        <v>938.96</v>
       </c>
       <c r="C164" s="9">
-        <f t="shared" si="5"/>
-        <v>55200</v>
+        <f t="shared" si="2"/>
+        <v>804</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="8">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B165" s="13">
-        <f t="shared" si="4"/>
-        <v>33900</v>
+        <f>$B$12+$B$22*A165</f>
+        <v>941.56</v>
       </c>
       <c r="C165" s="9">
-        <f t="shared" si="5"/>
-        <v>55600</v>
+        <f t="shared" si="2"/>
+        <v>810</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="8">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B166" s="13">
-        <f t="shared" si="4"/>
-        <v>34000</v>
+        <f>$B$12+$B$22*A166</f>
+        <v>944.16</v>
       </c>
       <c r="C166" s="9">
-        <f t="shared" si="5"/>
-        <v>56000</v>
+        <f t="shared" si="2"/>
+        <v>816</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="8">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B167" s="13">
-        <f t="shared" si="4"/>
-        <v>34100</v>
+        <f>$B$12+$B$22*A167</f>
+        <v>946.76</v>
       </c>
       <c r="C167" s="9">
-        <f t="shared" si="5"/>
-        <v>56400</v>
+        <f t="shared" si="2"/>
+        <v>822</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="8">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B168" s="13">
-        <f t="shared" si="4"/>
-        <v>34200</v>
+        <f>$B$12+$B$22*A168</f>
+        <v>949.3599999999999</v>
       </c>
       <c r="C168" s="9">
-        <f t="shared" si="5"/>
-        <v>56800</v>
+        <f t="shared" si="2"/>
+        <v>828</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="8">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B169" s="13">
-        <f t="shared" si="4"/>
-        <v>34300</v>
+        <f>$B$12+$B$22*A169</f>
+        <v>951.96</v>
       </c>
       <c r="C169" s="9">
-        <f t="shared" si="5"/>
-        <v>57200</v>
+        <f t="shared" si="2"/>
+        <v>834</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="8">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B170" s="13">
-        <f t="shared" si="4"/>
-        <v>34400</v>
+        <f>$B$12+$B$22*A170</f>
+        <v>954.56</v>
       </c>
       <c r="C170" s="9">
-        <f t="shared" si="5"/>
-        <v>57600</v>
+        <f t="shared" si="2"/>
+        <v>840</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="8">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B171" s="13">
-        <f t="shared" si="4"/>
-        <v>34500</v>
+        <f>$B$12+$B$22*A171</f>
+        <v>957.16</v>
       </c>
       <c r="C171" s="9">
-        <f t="shared" si="5"/>
-        <v>58000</v>
+        <f t="shared" si="2"/>
+        <v>846</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="8">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B172" s="13">
-        <f t="shared" si="4"/>
-        <v>34600</v>
+        <f>$B$12+$B$22*A172</f>
+        <v>959.76</v>
       </c>
       <c r="C172" s="9">
-        <f t="shared" si="5"/>
-        <v>58400</v>
+        <f t="shared" si="2"/>
+        <v>852</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="8">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B173" s="13">
-        <f t="shared" si="4"/>
-        <v>34700</v>
+        <f>$B$12+$B$22*A173</f>
+        <v>962.3599999999999</v>
       </c>
       <c r="C173" s="9">
-        <f t="shared" si="5"/>
-        <v>58800</v>
+        <f t="shared" si="2"/>
+        <v>858</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="8">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B174" s="13">
-        <f t="shared" si="4"/>
-        <v>34800</v>
+        <f>$B$12+$B$22*A174</f>
+        <v>964.96</v>
       </c>
       <c r="C174" s="9">
-        <f t="shared" si="5"/>
-        <v>59200</v>
+        <f t="shared" si="2"/>
+        <v>864</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="8">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B175" s="13">
-        <f t="shared" si="4"/>
-        <v>34900</v>
+        <f>$B$12+$B$22*A175</f>
+        <v>967.56</v>
       </c>
       <c r="C175" s="9">
-        <f t="shared" si="5"/>
-        <v>59600</v>
+        <f t="shared" si="2"/>
+        <v>870</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="8">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B176" s="13">
-        <f t="shared" si="4"/>
-        <v>35000</v>
+        <f>$B$12+$B$22*A176</f>
+        <v>970.16</v>
       </c>
       <c r="C176" s="9">
-        <f t="shared" si="5"/>
-        <v>60000</v>
+        <f t="shared" si="2"/>
+        <v>876</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="8">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B177" s="13">
-        <f t="shared" si="4"/>
-        <v>35100</v>
+        <f>$B$12+$B$22*A177</f>
+        <v>972.76</v>
       </c>
       <c r="C177" s="9">
-        <f t="shared" si="5"/>
-        <v>60400</v>
+        <f t="shared" si="2"/>
+        <v>882</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="8">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B178" s="13">
-        <f t="shared" si="4"/>
-        <v>35200</v>
+        <f>$B$12+$B$22*A178</f>
+        <v>975.3599999999999</v>
       </c>
       <c r="C178" s="9">
-        <f t="shared" si="5"/>
-        <v>60800</v>
+        <f t="shared" si="2"/>
+        <v>888</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="8">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B179" s="13">
-        <f t="shared" si="4"/>
-        <v>35300</v>
+        <f>$B$12+$B$22*A179</f>
+        <v>977.96</v>
       </c>
       <c r="C179" s="9">
-        <f t="shared" si="5"/>
-        <v>61200</v>
+        <f t="shared" si="2"/>
+        <v>894</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="8">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B180" s="13">
-        <f t="shared" si="4"/>
-        <v>35400</v>
+        <f>$B$12+$B$22*A180</f>
+        <v>980.56</v>
       </c>
       <c r="C180" s="9">
-        <f t="shared" si="5"/>
-        <v>61600</v>
+        <f t="shared" si="2"/>
+        <v>900</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="8">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B181" s="13">
-        <f t="shared" si="4"/>
-        <v>35500</v>
+        <f>$B$12+$B$22*A181</f>
+        <v>983.16</v>
       </c>
       <c r="C181" s="9">
-        <f t="shared" si="5"/>
-        <v>62000</v>
+        <f t="shared" si="2"/>
+        <v>906</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="8">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B182" s="13">
-        <f t="shared" si="4"/>
-        <v>35600</v>
+        <f>$B$12+$B$22*A182</f>
+        <v>985.76</v>
       </c>
       <c r="C182" s="9">
-        <f t="shared" si="5"/>
-        <v>62400</v>
+        <f t="shared" si="2"/>
+        <v>912</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="8">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B183" s="13">
-        <f t="shared" si="4"/>
-        <v>35700</v>
+        <f>$B$12+$B$22*A183</f>
+        <v>988.3599999999999</v>
       </c>
       <c r="C183" s="9">
-        <f t="shared" si="5"/>
-        <v>62800</v>
+        <f t="shared" si="2"/>
+        <v>918</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="8">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B184" s="13">
-        <f t="shared" si="4"/>
-        <v>35800</v>
+        <f>$B$12+$B$22*A184</f>
+        <v>990.96</v>
       </c>
       <c r="C184" s="9">
-        <f t="shared" si="5"/>
-        <v>63200</v>
+        <f t="shared" si="2"/>
+        <v>924</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="8">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B185" s="13">
-        <f t="shared" si="4"/>
-        <v>35900</v>
+        <f>$B$12+$B$22*A185</f>
+        <v>993.56</v>
       </c>
       <c r="C185" s="9">
-        <f t="shared" si="5"/>
-        <v>63600</v>
+        <f t="shared" si="2"/>
+        <v>930</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="8">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B186" s="13">
-        <f t="shared" si="4"/>
-        <v>36000</v>
+        <f>$B$12+$B$22*A186</f>
+        <v>996.16</v>
       </c>
       <c r="C186" s="9">
-        <f t="shared" si="5"/>
-        <v>64000</v>
+        <f t="shared" si="2"/>
+        <v>936</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="8">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B187" s="13">
-        <f t="shared" si="4"/>
-        <v>36100</v>
+        <f>$B$12+$B$22*A187</f>
+        <v>998.76</v>
       </c>
       <c r="C187" s="9">
-        <f t="shared" si="5"/>
-        <v>64400</v>
+        <f t="shared" si="2"/>
+        <v>942</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="8">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B188" s="13">
-        <f t="shared" si="4"/>
-        <v>36200</v>
+        <f>$B$12+$B$22*A188</f>
+        <v>1001.3599999999999</v>
       </c>
       <c r="C188" s="9">
-        <f t="shared" si="5"/>
-        <v>64800</v>
+        <f t="shared" si="2"/>
+        <v>948</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="8">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B189" s="13">
-        <f t="shared" si="4"/>
-        <v>36300</v>
+        <f>$B$12+$B$22*A189</f>
+        <v>1003.96</v>
       </c>
       <c r="C189" s="9">
-        <f t="shared" si="5"/>
-        <v>65200</v>
+        <f t="shared" si="2"/>
+        <v>954</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="8">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B190" s="13">
-        <f t="shared" si="4"/>
-        <v>36400</v>
+        <f>$B$12+$B$22*A190</f>
+        <v>1006.56</v>
       </c>
       <c r="C190" s="9">
-        <f t="shared" si="5"/>
-        <v>65600</v>
+        <f t="shared" si="2"/>
+        <v>960</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="8">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B191" s="13">
-        <f t="shared" si="4"/>
-        <v>36500</v>
+        <f>$B$12+$B$22*A191</f>
+        <v>1009.16</v>
       </c>
       <c r="C191" s="9">
-        <f t="shared" si="5"/>
-        <v>66000</v>
+        <f t="shared" si="2"/>
+        <v>966</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="8">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B192" s="13">
-        <f t="shared" si="4"/>
-        <v>36600</v>
+        <f>$B$12+$B$22*A192</f>
+        <v>1011.76</v>
       </c>
       <c r="C192" s="9">
-        <f t="shared" si="5"/>
-        <v>66400</v>
+        <f t="shared" si="2"/>
+        <v>972</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="8">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B193" s="13">
-        <f t="shared" si="4"/>
-        <v>36700</v>
+        <f>$B$12+$B$22*A193</f>
+        <v>1014.3599999999999</v>
       </c>
       <c r="C193" s="9">
-        <f t="shared" si="5"/>
-        <v>66800</v>
+        <f t="shared" si="2"/>
+        <v>978</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="8">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B194" s="13">
-        <f t="shared" si="4"/>
-        <v>36800</v>
+        <f>$B$12+$B$22*A194</f>
+        <v>1016.96</v>
       </c>
       <c r="C194" s="9">
-        <f t="shared" si="5"/>
-        <v>67200</v>
+        <f t="shared" si="2"/>
+        <v>984</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="8">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B195" s="13">
-        <f t="shared" si="4"/>
-        <v>36900</v>
+        <f>$B$12+$B$22*A195</f>
+        <v>1019.56</v>
       </c>
       <c r="C195" s="9">
-        <f t="shared" si="5"/>
-        <v>67600</v>
+        <f t="shared" si="2"/>
+        <v>990</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="8">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B196" s="13">
-        <f t="shared" si="4"/>
-        <v>37000</v>
+        <f>$B$12+$B$22*A196</f>
+        <v>1022.16</v>
       </c>
       <c r="C196" s="9">
-        <f t="shared" si="5"/>
-        <v>68000</v>
+        <f t="shared" si="2"/>
+        <v>996</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="8">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B197" s="13">
-        <f t="shared" si="4"/>
-        <v>37100</v>
+        <f>$B$12+$B$22*A197</f>
+        <v>1024.76</v>
       </c>
       <c r="C197" s="9">
-        <f t="shared" si="5"/>
-        <v>68400</v>
+        <f t="shared" si="2"/>
+        <v>1002</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="8">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B198" s="13">
-        <f t="shared" si="4"/>
-        <v>37200</v>
+        <f>$B$12+$B$22*A198</f>
+        <v>1027.3599999999999</v>
       </c>
       <c r="C198" s="9">
-        <f t="shared" si="5"/>
-        <v>68800</v>
+        <f t="shared" si="2"/>
+        <v>1008</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="8">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B199" s="13">
-        <f t="shared" si="4"/>
-        <v>37300</v>
+        <f>$B$12+$B$22*A199</f>
+        <v>1029.96</v>
       </c>
       <c r="C199" s="9">
-        <f t="shared" si="5"/>
-        <v>69200</v>
+        <f t="shared" si="2"/>
+        <v>1014</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="8">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B200" s="13">
-        <f t="shared" si="4"/>
-        <v>37400</v>
+        <f>$B$12+$B$22*A200</f>
+        <v>1032.56</v>
       </c>
       <c r="C200" s="9">
-        <f t="shared" si="5"/>
-        <v>69600</v>
+        <f t="shared" si="2"/>
+        <v>1020</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="8">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B201" s="13">
-        <f t="shared" si="4"/>
-        <v>37500</v>
+        <f>$B$12+$B$22*A201</f>
+        <v>1035.1599999999999</v>
       </c>
       <c r="C201" s="9">
-        <f t="shared" si="5"/>
-        <v>70000</v>
+        <f t="shared" si="2"/>
+        <v>1026</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="8">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B202" s="13">
-        <f t="shared" si="4"/>
-        <v>37600</v>
+        <f>$B$12+$B$22*A202</f>
+        <v>1037.76</v>
       </c>
       <c r="C202" s="9">
-        <f t="shared" si="5"/>
-        <v>70400</v>
+        <f t="shared" si="2"/>
+        <v>1032</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="8">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B203" s="13">
-        <f t="shared" si="4"/>
-        <v>37700</v>
+        <f>$B$12+$B$22*A203</f>
+        <v>1040.3599999999999</v>
       </c>
       <c r="C203" s="9">
-        <f t="shared" si="5"/>
-        <v>70800</v>
+        <f t="shared" si="2"/>
+        <v>1038</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="8">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B204" s="13">
-        <f t="shared" si="4"/>
-        <v>37800</v>
+        <f>$B$12+$B$22*A204</f>
+        <v>1042.96</v>
       </c>
       <c r="C204" s="9">
-        <f t="shared" si="5"/>
-        <v>71200</v>
+        <f t="shared" si="2"/>
+        <v>1044</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="8">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B205" s="13">
-        <f t="shared" si="4"/>
-        <v>37900</v>
+        <f>$B$12+$B$22*A205</f>
+        <v>1045.56</v>
       </c>
       <c r="C205" s="9">
-        <f t="shared" si="5"/>
-        <v>71600</v>
+        <f t="shared" si="2"/>
+        <v>1050</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="8">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B206" s="13">
-        <f t="shared" si="4"/>
-        <v>38000</v>
+        <f>$B$12+$B$22*A206</f>
+        <v>1048.1599999999999</v>
       </c>
       <c r="C206" s="9">
-        <f t="shared" si="5"/>
-        <v>72000</v>
+        <f t="shared" si="2"/>
+        <v>1056</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="8">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B207" s="13">
-        <f t="shared" si="4"/>
-        <v>38100</v>
+        <f>$B$12+$B$22*A207</f>
+        <v>1050.76</v>
       </c>
       <c r="C207" s="9">
-        <f t="shared" si="5"/>
-        <v>72400</v>
+        <f t="shared" si="2"/>
+        <v>1062</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="8">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B208" s="13">
-        <f t="shared" si="4"/>
-        <v>38200</v>
+        <f>$B$12+$B$22*A208</f>
+        <v>1053.3599999999999</v>
       </c>
       <c r="C208" s="9">
-        <f t="shared" si="5"/>
-        <v>72800</v>
+        <f t="shared" si="2"/>
+        <v>1068</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="8">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B209" s="13">
-        <f t="shared" si="4"/>
-        <v>38300</v>
+        <f>$B$12+$B$22*A209</f>
+        <v>1055.96</v>
       </c>
       <c r="C209" s="9">
-        <f t="shared" si="5"/>
-        <v>73200</v>
+        <f t="shared" si="2"/>
+        <v>1074</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="8">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B210" s="13">
-        <f t="shared" si="4"/>
-        <v>38400</v>
+        <f>$B$12+$B$22*A210</f>
+        <v>1058.56</v>
       </c>
       <c r="C210" s="9">
-        <f t="shared" si="5"/>
-        <v>73600</v>
+        <f t="shared" si="2"/>
+        <v>1080</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="8">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B211" s="13">
-        <f t="shared" si="4"/>
-        <v>38500</v>
+        <f>$B$12+$B$22*A211</f>
+        <v>1061.1599999999999</v>
       </c>
       <c r="C211" s="9">
-        <f t="shared" si="5"/>
-        <v>74000</v>
+        <f t="shared" si="2"/>
+        <v>1086</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="8">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B212" s="13">
-        <f t="shared" si="4"/>
-        <v>38600</v>
+        <f>$B$12+$B$22*A212</f>
+        <v>1063.76</v>
       </c>
       <c r="C212" s="9">
-        <f t="shared" si="5"/>
-        <v>74400</v>
+        <f t="shared" si="2"/>
+        <v>1092</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="8">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B213" s="13">
-        <f t="shared" si="4"/>
-        <v>38700</v>
+        <f>$B$12+$B$22*A213</f>
+        <v>1066.3599999999999</v>
       </c>
       <c r="C213" s="9">
-        <f t="shared" si="5"/>
-        <v>74800</v>
+        <f t="shared" si="2"/>
+        <v>1098</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="8">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B214" s="13">
-        <f t="shared" si="4"/>
-        <v>38800</v>
+        <f>$B$12+$B$22*A214</f>
+        <v>1068.96</v>
       </c>
       <c r="C214" s="9">
-        <f t="shared" si="5"/>
-        <v>75200</v>
+        <f t="shared" si="2"/>
+        <v>1104</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="8">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B215" s="13">
-        <f t="shared" si="4"/>
-        <v>38900</v>
+        <f>$B$12+$B$22*A215</f>
+        <v>1071.56</v>
       </c>
       <c r="C215" s="9">
-        <f t="shared" si="5"/>
-        <v>75600</v>
+        <f t="shared" si="2"/>
+        <v>1110</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="8">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B216" s="13">
-        <f t="shared" si="4"/>
-        <v>39000</v>
+        <f>$B$12+$B$22*A216</f>
+        <v>1074.1599999999999</v>
       </c>
       <c r="C216" s="9">
-        <f t="shared" si="5"/>
-        <v>76000</v>
+        <f t="shared" si="2"/>
+        <v>1116</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="8">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B217" s="13">
-        <f t="shared" si="4"/>
-        <v>39100</v>
+        <f>$B$12+$B$22*A217</f>
+        <v>1076.76</v>
       </c>
       <c r="C217" s="9">
-        <f t="shared" si="5"/>
-        <v>76400</v>
+        <f t="shared" si="2"/>
+        <v>1122</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="8">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B218" s="13">
-        <f t="shared" si="4"/>
-        <v>39200</v>
+        <f>$B$12+$B$22*A218</f>
+        <v>1079.3599999999999</v>
       </c>
       <c r="C218" s="9">
-        <f t="shared" si="5"/>
-        <v>76800</v>
+        <f t="shared" si="2"/>
+        <v>1128</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="8">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B219" s="13">
-        <f t="shared" ref="B219:B226" si="6">$B$8+$B$18*A219</f>
-        <v>39300</v>
+        <f>$B$12+$B$22*A219</f>
+        <v>1081.96</v>
       </c>
       <c r="C219" s="9">
-        <f t="shared" ref="C219:C226" si="7">$B$21*A219</f>
-        <v>77200</v>
+        <f t="shared" si="2"/>
+        <v>1134</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="8">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B220" s="13">
-        <f t="shared" si="6"/>
-        <v>39400</v>
+        <f>$B$12+$B$22*A220</f>
+        <v>1084.56</v>
       </c>
       <c r="C220" s="9">
-        <f t="shared" si="7"/>
-        <v>77600</v>
+        <f t="shared" si="2"/>
+        <v>1140</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="8">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B221" s="13">
-        <f t="shared" si="6"/>
-        <v>39500</v>
+        <f>$B$12+$B$22*A221</f>
+        <v>1087.1599999999999</v>
       </c>
       <c r="C221" s="9">
-        <f t="shared" si="7"/>
-        <v>78000</v>
+        <f t="shared" si="2"/>
+        <v>1146</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="8">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B222" s="13">
-        <f t="shared" si="6"/>
-        <v>39600</v>
+        <f>$B$12+$B$22*A222</f>
+        <v>1089.76</v>
       </c>
       <c r="C222" s="9">
-        <f t="shared" si="7"/>
-        <v>78400</v>
+        <f t="shared" si="2"/>
+        <v>1152</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="8">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B223" s="13">
-        <f t="shared" si="6"/>
-        <v>39700</v>
+        <f>$B$12+$B$22*A223</f>
+        <v>1092.3599999999999</v>
       </c>
       <c r="C223" s="9">
-        <f t="shared" si="7"/>
-        <v>78800</v>
+        <f t="shared" ref="C223:C230" si="3">$B$25*A223</f>
+        <v>1158</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="8">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B224" s="13">
-        <f t="shared" si="6"/>
-        <v>39800</v>
+        <f>$B$12+$B$22*A224</f>
+        <v>1094.96</v>
       </c>
       <c r="C224" s="9">
-        <f t="shared" si="7"/>
-        <v>79200</v>
+        <f t="shared" si="3"/>
+        <v>1164</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="8">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B225" s="13">
-        <f t="shared" si="6"/>
-        <v>39900</v>
+        <f>$B$12+$B$22*A225</f>
+        <v>1097.56</v>
       </c>
       <c r="C225" s="9">
-        <f t="shared" si="7"/>
-        <v>79600</v>
+        <f t="shared" si="3"/>
+        <v>1170</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="8">
+        <v>196</v>
+      </c>
+      <c r="B226" s="13">
+        <f>$B$12+$B$22*A226</f>
+        <v>1100.1599999999999</v>
+      </c>
+      <c r="C226" s="9">
+        <f t="shared" si="3"/>
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="8">
+        <v>197</v>
+      </c>
+      <c r="B227" s="13">
+        <f>$B$12+$B$22*A227</f>
+        <v>1102.76</v>
+      </c>
+      <c r="C227" s="9">
+        <f t="shared" si="3"/>
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="8">
+        <v>198</v>
+      </c>
+      <c r="B228" s="13">
+        <f>$B$12+$B$22*A228</f>
+        <v>1105.3600000000001</v>
+      </c>
+      <c r="C228" s="9">
+        <f t="shared" si="3"/>
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="8">
+        <v>199</v>
+      </c>
+      <c r="B229" s="13">
+        <f>$B$12+$B$22*A229</f>
+        <v>1107.96</v>
+      </c>
+      <c r="C229" s="9">
+        <f t="shared" si="3"/>
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="8">
         <v>200</v>
       </c>
-      <c r="B226" s="13">
+      <c r="B230" s="13">
+        <f>$B$12+$B$22*A230</f>
+        <v>1110.56</v>
+      </c>
+      <c r="C230" s="9">
+        <f>$B$25*A230</f>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="8">
+        <v>201</v>
+      </c>
+      <c r="B231" s="13">
+        <f t="shared" ref="B231:B255" si="4">$B$12+$B$22*A231</f>
+        <v>1113.1599999999999</v>
+      </c>
+      <c r="C231" s="9">
+        <f t="shared" ref="C231:C244" si="5">$B$25*A231</f>
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="8">
+        <v>202</v>
+      </c>
+      <c r="B232" s="13">
+        <f t="shared" si="4"/>
+        <v>1115.76</v>
+      </c>
+      <c r="C232" s="9">
+        <f t="shared" si="5"/>
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="8">
+        <v>203</v>
+      </c>
+      <c r="B233" s="13">
+        <f t="shared" si="4"/>
+        <v>1118.3600000000001</v>
+      </c>
+      <c r="C233" s="9">
+        <f t="shared" si="5"/>
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="8">
+        <v>204</v>
+      </c>
+      <c r="B234" s="13">
+        <f t="shared" si="4"/>
+        <v>1120.96</v>
+      </c>
+      <c r="C234" s="9">
+        <f t="shared" si="5"/>
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="8">
+        <v>205</v>
+      </c>
+      <c r="B235" s="13">
+        <f t="shared" si="4"/>
+        <v>1123.56</v>
+      </c>
+      <c r="C235" s="9">
+        <f t="shared" si="5"/>
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="8">
+        <v>206</v>
+      </c>
+      <c r="B236" s="13">
+        <f t="shared" si="4"/>
+        <v>1126.1599999999999</v>
+      </c>
+      <c r="C236" s="9">
+        <f t="shared" si="5"/>
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="8">
+        <v>207</v>
+      </c>
+      <c r="B237" s="13">
+        <f t="shared" si="4"/>
+        <v>1128.76</v>
+      </c>
+      <c r="C237" s="9">
+        <f t="shared" si="5"/>
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="8">
+        <v>208</v>
+      </c>
+      <c r="B238" s="13">
+        <f t="shared" si="4"/>
+        <v>1131.3600000000001</v>
+      </c>
+      <c r="C238" s="9">
+        <f t="shared" si="5"/>
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="8">
+        <v>209</v>
+      </c>
+      <c r="B239" s="13">
+        <f t="shared" si="4"/>
+        <v>1133.96</v>
+      </c>
+      <c r="C239" s="9">
+        <f t="shared" si="5"/>
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="8">
+        <v>210</v>
+      </c>
+      <c r="B240" s="13">
+        <f t="shared" si="4"/>
+        <v>1136.56</v>
+      </c>
+      <c r="C240" s="9">
+        <f t="shared" si="5"/>
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="8">
+        <v>211</v>
+      </c>
+      <c r="B241" s="13">
+        <f t="shared" si="4"/>
+        <v>1139.1599999999999</v>
+      </c>
+      <c r="C241" s="9">
+        <f t="shared" si="5"/>
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="8">
+        <v>212</v>
+      </c>
+      <c r="B242" s="13">
+        <f t="shared" si="4"/>
+        <v>1141.76</v>
+      </c>
+      <c r="C242" s="9">
+        <f t="shared" si="5"/>
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="8">
+        <v>213</v>
+      </c>
+      <c r="B243" s="13">
+        <f t="shared" si="4"/>
+        <v>1144.3600000000001</v>
+      </c>
+      <c r="C243" s="9">
+        <f t="shared" si="5"/>
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="8">
+        <v>214</v>
+      </c>
+      <c r="B244" s="13">
+        <f t="shared" si="4"/>
+        <v>1146.96</v>
+      </c>
+      <c r="C244" s="9">
+        <f t="shared" si="5"/>
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="8">
+        <v>215</v>
+      </c>
+      <c r="B245" s="13">
+        <f>$B$12+$B$22*A245</f>
+        <v>1149.56</v>
+      </c>
+      <c r="C245" s="9">
+        <f>$B$25*A245</f>
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="8">
+        <v>216</v>
+      </c>
+      <c r="B246" s="13">
+        <f t="shared" si="4"/>
+        <v>1152.1599999999999</v>
+      </c>
+      <c r="C246" s="9">
+        <f t="shared" ref="C246:C250" si="6">$B$25*A246</f>
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="8">
+        <v>217</v>
+      </c>
+      <c r="B247" s="13">
+        <f t="shared" si="4"/>
+        <v>1154.76</v>
+      </c>
+      <c r="C247" s="9">
         <f t="shared" si="6"/>
-        <v>40000</v>
-      </c>
-      <c r="C226" s="9">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="8">
+        <v>218</v>
+      </c>
+      <c r="B248" s="13">
+        <f t="shared" si="4"/>
+        <v>1157.3600000000001</v>
+      </c>
+      <c r="C248" s="9">
+        <f t="shared" si="6"/>
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="8">
+        <v>219</v>
+      </c>
+      <c r="B249" s="13">
+        <f t="shared" si="4"/>
+        <v>1159.96</v>
+      </c>
+      <c r="C249" s="9">
+        <f t="shared" si="6"/>
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="8">
+        <v>220</v>
+      </c>
+      <c r="B250" s="13">
+        <f t="shared" si="4"/>
+        <v>1162.56</v>
+      </c>
+      <c r="C250" s="9">
+        <f t="shared" si="6"/>
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="8">
+        <v>221</v>
+      </c>
+      <c r="B251" s="13">
+        <f>$B$12+$B$22*A251</f>
+        <v>1165.1599999999999</v>
+      </c>
+      <c r="C251" s="9">
+        <f>$B$25*A251</f>
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="8">
+        <v>222</v>
+      </c>
+      <c r="B252" s="13">
+        <f t="shared" si="4"/>
+        <v>1167.76</v>
+      </c>
+      <c r="C252" s="9">
+        <f t="shared" ref="C252:C255" si="7">$B$25*A252</f>
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="8">
+        <v>223</v>
+      </c>
+      <c r="B253" s="13">
+        <f t="shared" si="4"/>
+        <v>1170.3600000000001</v>
+      </c>
+      <c r="C253" s="9">
         <f t="shared" si="7"/>
-        <v>80000</v>
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="8">
+        <v>224</v>
+      </c>
+      <c r="B254" s="13">
+        <f t="shared" si="4"/>
+        <v>1172.96</v>
+      </c>
+      <c r="C254" s="9">
+        <f t="shared" si="7"/>
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="8">
+        <v>225</v>
+      </c>
+      <c r="B255" s="13">
+        <f t="shared" si="4"/>
+        <v>1175.56</v>
+      </c>
+      <c r="C255" s="9">
+        <f t="shared" si="7"/>
+        <v>1350</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -13502,12 +14036,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5cfc5781-36c7-40ed-af62-43a27290b458" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13744,17 +14277,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5cfc5781-36c7-40ed-af62-43a27290b458" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5725DCE3-03BC-44D7-BC9C-71C7B5BFC1A0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4FBB6FF-EC5C-4DA6-BDE2-BFD391C0AAC1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="5cfc5781-36c7-40ed-af62-43a27290b458"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c4b568bc-dd8a-4a74-b92a-f01b2ee1149b"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13779,18 +14322,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4FBB6FF-EC5C-4DA6-BDE2-BFD391C0AAC1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5725DCE3-03BC-44D7-BC9C-71C7B5BFC1A0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="5cfc5781-36c7-40ed-af62-43a27290b458"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="c4b568bc-dd8a-4a74-b92a-f01b2ee1149b"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/utilities/Punto_de_equilibrio.xlsx
+++ b/utilities/Punto_de_equilibrio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MaBel\utilities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B51FFB-BE8E-4ED2-9E37-FAB97703844D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F622050-5B34-4B63-89F2-537D3103D9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{E75E3C13-AC3D-4914-9135-F849659ACBFB}"/>
   </bookViews>
@@ -6071,6 +6071,2899 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-EC"/>
+              <a:t>Punto de equilibrio</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13603609157396251"/>
+          <c:y val="0.23764100138743954"/>
+          <c:w val="0.81689392028843366"/>
+          <c:h val="0.69608276593863294"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Ejercicio 2'!$B$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Costo Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Ejercicio 2'!$A$30:$A$230</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="201"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>121</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>123</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>124</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>127</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>131</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>133</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>134</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>139</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>142</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>146</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>147</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>151</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>152</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>158</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>164</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>166</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>173</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>183</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>191</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>196</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>198</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Ejercicio 2'!$B$30:$B$230</c:f>
+              <c:numCache>
+                <c:formatCode>_ "$"* #,##0.00_ ;_ "$"* \-#,##0.00_ ;_ "$"* "-"??_ ;_ @_ </c:formatCode>
+                <c:ptCount val="201"/>
+                <c:pt idx="0">
+                  <c:v>590.55999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>593.16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>595.76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>598.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>600.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>603.55999999999995</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>606.16</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>608.76</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>611.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>613.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>616.55999999999995</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>619.16</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>621.76</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>624.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>626.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>629.55999999999995</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>632.16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>634.76</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>637.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>639.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>642.55999999999995</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>645.16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>647.76</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>650.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>652.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>655.56</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>658.16</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>660.76</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>663.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>665.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>668.56</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>671.16</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>673.76</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>676.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>678.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>681.56</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>684.16</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>686.76</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>689.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>691.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>694.56</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>697.16</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>699.76</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>702.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>704.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>707.56</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>710.16</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>712.76</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>715.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>717.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>720.56</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>723.16</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>725.76</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>728.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>730.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>733.56</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>736.16</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>738.76</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>741.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>743.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>746.56</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>749.16</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>751.76</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>754.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>756.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>759.56</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>762.16</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>764.76</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>767.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>769.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>772.56</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>775.16</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>777.76</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>780.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>782.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>785.56</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>788.16</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>790.76</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>793.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>795.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>798.56</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>801.16</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>803.76</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>806.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>808.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>811.56</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>814.16</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>816.76</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>819.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>821.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>824.56</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>827.16</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>829.76</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>832.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>834.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>837.56</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>840.16</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>842.76</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>845.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>847.96</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>850.56</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>853.16</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>855.76</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>858.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>860.96</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>863.56</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>866.16</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>868.76</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>871.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>873.96</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>876.56</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>879.16</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>881.76</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>884.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>886.96</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>889.56</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>892.16</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>894.76</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>897.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>899.96</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>902.56</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>905.16</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>907.76</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>910.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>912.96</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>915.56</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>918.16</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>920.76</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>923.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>925.96</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>928.56</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>931.16</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>933.76</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>936.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>938.96</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>941.56</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>944.16</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>946.76</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>949.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>951.96</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>954.56</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>957.16</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>959.76</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>962.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>964.96</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>967.56</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>970.16</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>972.76</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>975.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>977.96</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>980.56</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>983.16</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>985.76</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>988.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>990.96</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>993.56</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>996.16</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>998.76</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>1001.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>1003.96</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>1006.56</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>1009.16</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>1011.76</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>1014.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>1016.96</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>1019.56</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>1022.16</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>1024.76</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>1027.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1029.96</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>1032.56</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>1035.1599999999999</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>1037.76</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>1040.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>1042.96</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>1045.56</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>1048.1599999999999</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>1050.76</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>1053.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1055.96</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>1058.56</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>1061.1599999999999</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>1063.76</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>1066.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>1068.96</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>1071.56</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>1074.1599999999999</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>1076.76</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>1079.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>1081.96</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>1084.56</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>1087.1599999999999</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>1089.76</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>1092.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>1094.96</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>1097.56</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>1100.1599999999999</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>1102.76</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>1105.3600000000001</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1107.96</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>1110.56</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C9C0-43B5-977B-05B15A69AF2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Ejercicio 2'!$C$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ingreso de Ventas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="100"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-C9C0-43B5-977B-05B15A69AF2E}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-PE"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Ejercicio 2'!$A$30:$A$230</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="201"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>121</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>123</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>124</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>127</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>131</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>133</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>134</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>139</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>142</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>146</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>147</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>151</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>152</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>158</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>164</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>166</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>173</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>183</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>191</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>196</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>198</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Ejercicio 2'!$C$30:$C$230</c:f>
+              <c:numCache>
+                <c:formatCode>_ "$"* #,##0.00_ ;_ "$"* \-#,##0.00_ ;_ "$"* "-"??_ ;_ @_ </c:formatCode>
+                <c:ptCount val="201"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>198</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>228</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>246</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>258</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>264</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>276</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>282</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>288</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>294</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>312</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>318</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>324</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>330</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>336</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>342</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>348</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>354</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>366</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>372</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>378</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>384</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>396</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>402</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>408</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>414</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>426</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>432</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>438</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>444</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>456</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>462</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>468</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>474</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>486</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>492</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>498</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>504</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>516</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>522</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>528</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>534</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>540</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>546</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>552</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>558</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>564</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>570</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>576</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>582</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>588</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>594</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>606</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>612</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>618</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>624</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>630</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>636</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>642</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>648</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>654</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>666</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>672</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>678</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>684</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>696</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>702</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>708</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>714</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>720</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>726</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>732</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>738</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>756</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>762</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>768</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>774</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>780</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>786</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>792</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>798</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>804</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>816</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>822</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>828</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>834</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>852</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>858</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>864</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>876</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>882</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>888</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>894</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>906</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>912</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>918</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>924</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>930</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>936</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>942</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>948</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>954</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>966</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>972</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>978</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>984</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>990</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>996</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>1002</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>1008</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1014</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>1020</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>1026</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>1032</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>1038</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>1044</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>1056</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>1062</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>1068</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1074</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>1080</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>1086</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>1092</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>1098</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>1104</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>1110</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>1116</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>1122</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>1128</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>1134</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>1140</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>1146</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>1152</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>1158</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>1164</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>1170</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>1176</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>1182</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>1188</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1194</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>1200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C9C0-43B5-977B-05B15A69AF2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="583106400"/>
+        <c:axId val="583114560"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="583106400"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="500"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="583114560"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="583114560"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="2500"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_ &quot;$&quot;* #,##0.00_ ;_ &quot;$&quot;* \-#,##0.00_ ;_ &quot;$&quot;* &quot;-&quot;??_ ;_ @_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="583106400"/>
+        <c:crossesAt val="0"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -6112,6 +9005,46 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -7227,6 +10160,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -7790,7 +11239,308 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>421105</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>184083</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>65405</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{342DB7DB-22B8-2E7B-4BB3-BB7AC3215FE3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>110289</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>30079</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>406621</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>78983</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Imagen 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{246BB3EB-27BC-067F-48ED-A6CA4762F752}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8091236" y="11650579"/>
+          <a:ext cx="1329043" cy="1572904"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>140369</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>100264</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>680975</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>176702</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Imagen 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9D0EF08-AD6C-36E2-38F5-BABD8FBA8D4E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6737685" y="17435764"/>
+          <a:ext cx="4480948" cy="2743438"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.29697</cdr:x>
+      <cdr:y>0.35793</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.45183</cdr:x>
+      <cdr:y>0.59636</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="2" name="Flecha: hacia abajo 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5393CA5C-64FA-28DA-B3EA-462A7A8A3746}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="19760771">
+          <a:off x="1326047" y="977998"/>
+          <a:ext cx="691515" cy="651510"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </cdr:style>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.14769</cdr:x>
+      <cdr:y>0.62911</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.42371</cdr:x>
+      <cdr:y>0.63306</cdr:y>
+    </cdr:to>
+    <cdr:cxnSp macro="">
+      <cdr:nvCxnSpPr>
+        <cdr:cNvPr id="3" name="Conector recto 2">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32FE2D55-C4F6-0FF4-12FB-87574ECDCFD3}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvCxnSpPr/>
+      </cdr:nvCxnSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" flipV="1">
+          <a:off x="659464" y="1718979"/>
+          <a:ext cx="1232535" cy="10795"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+    </cdr:cxnSp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.4234</cdr:x>
+      <cdr:y>0.63218</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.4234</cdr:x>
+      <cdr:y>0.90826</cdr:y>
+    </cdr:to>
+    <cdr:cxnSp macro="">
+      <cdr:nvCxnSpPr>
+        <cdr:cNvPr id="4" name="Conector recto 3">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0900EFF6-3AA3-2ECF-D2C6-F5CE5DBA9AF5}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvCxnSpPr/>
+      </cdr:nvCxnSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" flipH="1">
+          <a:off x="1890596" y="1727367"/>
+          <a:ext cx="0" cy="754380"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+    </cdr:cxnSp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11091,7 +14841,7 @@
         <v>0</v>
       </c>
       <c r="B30" s="13">
-        <f>$B$12+$B$22*A30</f>
+        <f t="shared" ref="B30:B93" si="0">$B$12+$B$22*A30</f>
         <v>590.55999999999995</v>
       </c>
       <c r="C30" s="9">
@@ -11104,7 +14854,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="13">
-        <f>$B$12+$B$22*A31</f>
+        <f t="shared" si="0"/>
         <v>593.16</v>
       </c>
       <c r="C31" s="9">
@@ -11117,11 +14867,11 @@
         <v>2</v>
       </c>
       <c r="B32" s="13">
-        <f>$B$12+$B$22*A32</f>
+        <f t="shared" si="0"/>
         <v>595.76</v>
       </c>
       <c r="C32" s="9">
-        <f t="shared" ref="C32:C94" si="0">$B$25*A32</f>
+        <f t="shared" ref="C32:C94" si="1">$B$25*A32</f>
         <v>12</v>
       </c>
     </row>
@@ -11130,11 +14880,11 @@
         <v>3</v>
       </c>
       <c r="B33" s="13">
-        <f>$B$12+$B$22*A33</f>
+        <f t="shared" si="0"/>
         <v>598.3599999999999</v>
       </c>
       <c r="C33" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
     </row>
@@ -11143,11 +14893,11 @@
         <v>4</v>
       </c>
       <c r="B34" s="13">
-        <f>$B$12+$B$22*A34</f>
+        <f t="shared" si="0"/>
         <v>600.95999999999992</v>
       </c>
       <c r="C34" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
     </row>
@@ -11156,11 +14906,11 @@
         <v>5</v>
       </c>
       <c r="B35" s="13">
-        <f>$B$12+$B$22*A35</f>
+        <f t="shared" si="0"/>
         <v>603.55999999999995</v>
       </c>
       <c r="C35" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
@@ -11169,11 +14919,11 @@
         <v>6</v>
       </c>
       <c r="B36" s="13">
-        <f>$B$12+$B$22*A36</f>
+        <f t="shared" si="0"/>
         <v>606.16</v>
       </c>
       <c r="C36" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
     </row>
@@ -11182,11 +14932,11 @@
         <v>7</v>
       </c>
       <c r="B37" s="13">
-        <f>$B$12+$B$22*A37</f>
+        <f t="shared" si="0"/>
         <v>608.76</v>
       </c>
       <c r="C37" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
     </row>
@@ -11195,11 +14945,11 @@
         <v>8</v>
       </c>
       <c r="B38" s="13">
-        <f>$B$12+$B$22*A38</f>
+        <f t="shared" si="0"/>
         <v>611.3599999999999</v>
       </c>
       <c r="C38" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
     </row>
@@ -11208,11 +14958,11 @@
         <v>9</v>
       </c>
       <c r="B39" s="13">
-        <f>$B$12+$B$22*A39</f>
+        <f t="shared" si="0"/>
         <v>613.95999999999992</v>
       </c>
       <c r="C39" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
     </row>
@@ -11221,11 +14971,11 @@
         <v>10</v>
       </c>
       <c r="B40" s="13">
-        <f>$B$12+$B$22*A40</f>
+        <f t="shared" si="0"/>
         <v>616.55999999999995</v>
       </c>
       <c r="C40" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
     </row>
@@ -11234,11 +14984,11 @@
         <v>11</v>
       </c>
       <c r="B41" s="13">
-        <f>$B$12+$B$22*A41</f>
+        <f t="shared" si="0"/>
         <v>619.16</v>
       </c>
       <c r="C41" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>66</v>
       </c>
     </row>
@@ -11247,11 +14997,11 @@
         <v>12</v>
       </c>
       <c r="B42" s="13">
-        <f>$B$12+$B$22*A42</f>
+        <f t="shared" si="0"/>
         <v>621.76</v>
       </c>
       <c r="C42" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
     </row>
@@ -11260,11 +15010,11 @@
         <v>13</v>
       </c>
       <c r="B43" s="13">
-        <f>$B$12+$B$22*A43</f>
+        <f t="shared" si="0"/>
         <v>624.3599999999999</v>
       </c>
       <c r="C43" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
     </row>
@@ -11273,11 +15023,11 @@
         <v>14</v>
       </c>
       <c r="B44" s="13">
-        <f>$B$12+$B$22*A44</f>
+        <f t="shared" si="0"/>
         <v>626.95999999999992</v>
       </c>
       <c r="C44" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>84</v>
       </c>
     </row>
@@ -11286,11 +15036,11 @@
         <v>15</v>
       </c>
       <c r="B45" s="13">
-        <f>$B$12+$B$22*A45</f>
+        <f t="shared" si="0"/>
         <v>629.55999999999995</v>
       </c>
       <c r="C45" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
     </row>
@@ -11299,11 +15049,11 @@
         <v>16</v>
       </c>
       <c r="B46" s="13">
-        <f>$B$12+$B$22*A46</f>
+        <f t="shared" si="0"/>
         <v>632.16</v>
       </c>
       <c r="C46" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
     </row>
@@ -11312,11 +15062,11 @@
         <v>17</v>
       </c>
       <c r="B47" s="13">
-        <f>$B$12+$B$22*A47</f>
+        <f t="shared" si="0"/>
         <v>634.76</v>
       </c>
       <c r="C47" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>102</v>
       </c>
     </row>
@@ -11325,11 +15075,11 @@
         <v>18</v>
       </c>
       <c r="B48" s="13">
-        <f>$B$12+$B$22*A48</f>
+        <f t="shared" si="0"/>
         <v>637.3599999999999</v>
       </c>
       <c r="C48" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>108</v>
       </c>
     </row>
@@ -11338,11 +15088,11 @@
         <v>19</v>
       </c>
       <c r="B49" s="13">
-        <f>$B$12+$B$22*A49</f>
+        <f t="shared" si="0"/>
         <v>639.95999999999992</v>
       </c>
       <c r="C49" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>114</v>
       </c>
     </row>
@@ -11351,11 +15101,11 @@
         <v>20</v>
       </c>
       <c r="B50" s="13">
-        <f>$B$12+$B$22*A50</f>
+        <f t="shared" si="0"/>
         <v>642.55999999999995</v>
       </c>
       <c r="C50" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
     </row>
@@ -11364,11 +15114,11 @@
         <v>21</v>
       </c>
       <c r="B51" s="13">
-        <f>$B$12+$B$22*A51</f>
+        <f t="shared" si="0"/>
         <v>645.16</v>
       </c>
       <c r="C51" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>126</v>
       </c>
     </row>
@@ -11377,11 +15127,11 @@
         <v>22</v>
       </c>
       <c r="B52" s="13">
-        <f>$B$12+$B$22*A52</f>
+        <f t="shared" si="0"/>
         <v>647.76</v>
       </c>
       <c r="C52" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>132</v>
       </c>
     </row>
@@ -11390,11 +15140,11 @@
         <v>23</v>
       </c>
       <c r="B53" s="13">
-        <f>$B$12+$B$22*A53</f>
+        <f t="shared" si="0"/>
         <v>650.3599999999999</v>
       </c>
       <c r="C53" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>138</v>
       </c>
     </row>
@@ -11403,11 +15153,11 @@
         <v>24</v>
       </c>
       <c r="B54" s="13">
-        <f>$B$12+$B$22*A54</f>
+        <f t="shared" si="0"/>
         <v>652.95999999999992</v>
       </c>
       <c r="C54" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>144</v>
       </c>
     </row>
@@ -11416,11 +15166,11 @@
         <v>25</v>
       </c>
       <c r="B55" s="13">
-        <f>$B$12+$B$22*A55</f>
+        <f t="shared" si="0"/>
         <v>655.56</v>
       </c>
       <c r="C55" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
     </row>
@@ -11429,11 +15179,11 @@
         <v>26</v>
       </c>
       <c r="B56" s="13">
-        <f>$B$12+$B$22*A56</f>
+        <f t="shared" si="0"/>
         <v>658.16</v>
       </c>
       <c r="C56" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>156</v>
       </c>
     </row>
@@ -11442,11 +15192,11 @@
         <v>27</v>
       </c>
       <c r="B57" s="13">
-        <f>$B$12+$B$22*A57</f>
+        <f t="shared" si="0"/>
         <v>660.76</v>
       </c>
       <c r="C57" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>162</v>
       </c>
     </row>
@@ -11455,11 +15205,11 @@
         <v>28</v>
       </c>
       <c r="B58" s="13">
-        <f>$B$12+$B$22*A58</f>
+        <f t="shared" si="0"/>
         <v>663.3599999999999</v>
       </c>
       <c r="C58" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>168</v>
       </c>
     </row>
@@ -11468,11 +15218,11 @@
         <v>29</v>
       </c>
       <c r="B59" s="13">
-        <f>$B$12+$B$22*A59</f>
+        <f t="shared" si="0"/>
         <v>665.95999999999992</v>
       </c>
       <c r="C59" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>174</v>
       </c>
     </row>
@@ -11481,11 +15231,11 @@
         <v>30</v>
       </c>
       <c r="B60" s="13">
-        <f>$B$12+$B$22*A60</f>
+        <f t="shared" si="0"/>
         <v>668.56</v>
       </c>
       <c r="C60" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>180</v>
       </c>
     </row>
@@ -11494,11 +15244,11 @@
         <v>31</v>
       </c>
       <c r="B61" s="13">
-        <f>$B$12+$B$22*A61</f>
+        <f t="shared" si="0"/>
         <v>671.16</v>
       </c>
       <c r="C61" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>186</v>
       </c>
     </row>
@@ -11507,11 +15257,11 @@
         <v>32</v>
       </c>
       <c r="B62" s="13">
-        <f>$B$12+$B$22*A62</f>
+        <f t="shared" si="0"/>
         <v>673.76</v>
       </c>
       <c r="C62" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>192</v>
       </c>
     </row>
@@ -11520,11 +15270,11 @@
         <v>33</v>
       </c>
       <c r="B63" s="13">
-        <f>$B$12+$B$22*A63</f>
+        <f t="shared" si="0"/>
         <v>676.3599999999999</v>
       </c>
       <c r="C63" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>198</v>
       </c>
     </row>
@@ -11533,11 +15283,11 @@
         <v>34</v>
       </c>
       <c r="B64" s="13">
-        <f>$B$12+$B$22*A64</f>
+        <f t="shared" si="0"/>
         <v>678.95999999999992</v>
       </c>
       <c r="C64" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>204</v>
       </c>
     </row>
@@ -11546,11 +15296,11 @@
         <v>35</v>
       </c>
       <c r="B65" s="13">
-        <f>$B$12+$B$22*A65</f>
+        <f t="shared" si="0"/>
         <v>681.56</v>
       </c>
       <c r="C65" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>210</v>
       </c>
     </row>
@@ -11559,11 +15309,11 @@
         <v>36</v>
       </c>
       <c r="B66" s="13">
-        <f>$B$12+$B$22*A66</f>
+        <f t="shared" si="0"/>
         <v>684.16</v>
       </c>
       <c r="C66" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>216</v>
       </c>
     </row>
@@ -11572,11 +15322,11 @@
         <v>37</v>
       </c>
       <c r="B67" s="13">
-        <f>$B$12+$B$22*A67</f>
+        <f t="shared" si="0"/>
         <v>686.76</v>
       </c>
       <c r="C67" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>222</v>
       </c>
     </row>
@@ -11585,11 +15335,11 @@
         <v>38</v>
       </c>
       <c r="B68" s="13">
-        <f>$B$12+$B$22*A68</f>
+        <f t="shared" si="0"/>
         <v>689.3599999999999</v>
       </c>
       <c r="C68" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>228</v>
       </c>
     </row>
@@ -11598,11 +15348,11 @@
         <v>39</v>
       </c>
       <c r="B69" s="13">
-        <f>$B$12+$B$22*A69</f>
+        <f t="shared" si="0"/>
         <v>691.95999999999992</v>
       </c>
       <c r="C69" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>234</v>
       </c>
     </row>
@@ -11611,11 +15361,11 @@
         <v>40</v>
       </c>
       <c r="B70" s="13">
-        <f>$B$12+$B$22*A70</f>
+        <f t="shared" si="0"/>
         <v>694.56</v>
       </c>
       <c r="C70" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>240</v>
       </c>
     </row>
@@ -11624,11 +15374,11 @@
         <v>41</v>
       </c>
       <c r="B71" s="13">
-        <f>$B$12+$B$22*A71</f>
+        <f t="shared" si="0"/>
         <v>697.16</v>
       </c>
       <c r="C71" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>246</v>
       </c>
     </row>
@@ -11637,11 +15387,11 @@
         <v>42</v>
       </c>
       <c r="B72" s="13">
-        <f>$B$12+$B$22*A72</f>
+        <f t="shared" si="0"/>
         <v>699.76</v>
       </c>
       <c r="C72" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>252</v>
       </c>
     </row>
@@ -11650,11 +15400,11 @@
         <v>43</v>
       </c>
       <c r="B73" s="13">
-        <f>$B$12+$B$22*A73</f>
+        <f t="shared" si="0"/>
         <v>702.3599999999999</v>
       </c>
       <c r="C73" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>258</v>
       </c>
     </row>
@@ -11663,11 +15413,11 @@
         <v>44</v>
       </c>
       <c r="B74" s="13">
-        <f>$B$12+$B$22*A74</f>
+        <f t="shared" si="0"/>
         <v>704.95999999999992</v>
       </c>
       <c r="C74" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>264</v>
       </c>
     </row>
@@ -11676,11 +15426,11 @@
         <v>45</v>
       </c>
       <c r="B75" s="13">
-        <f>$B$12+$B$22*A75</f>
+        <f t="shared" si="0"/>
         <v>707.56</v>
       </c>
       <c r="C75" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>270</v>
       </c>
     </row>
@@ -11689,11 +15439,11 @@
         <v>46</v>
       </c>
       <c r="B76" s="13">
-        <f>$B$12+$B$22*A76</f>
+        <f t="shared" si="0"/>
         <v>710.16</v>
       </c>
       <c r="C76" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>276</v>
       </c>
     </row>
@@ -11702,11 +15452,11 @@
         <v>47</v>
       </c>
       <c r="B77" s="13">
-        <f>$B$12+$B$22*A77</f>
+        <f t="shared" si="0"/>
         <v>712.76</v>
       </c>
       <c r="C77" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>282</v>
       </c>
     </row>
@@ -11715,11 +15465,11 @@
         <v>48</v>
       </c>
       <c r="B78" s="13">
-        <f>$B$12+$B$22*A78</f>
+        <f t="shared" si="0"/>
         <v>715.3599999999999</v>
       </c>
       <c r="C78" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>288</v>
       </c>
     </row>
@@ -11728,11 +15478,11 @@
         <v>49</v>
       </c>
       <c r="B79" s="13">
-        <f>$B$12+$B$22*A79</f>
+        <f t="shared" si="0"/>
         <v>717.95999999999992</v>
       </c>
       <c r="C79" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>294</v>
       </c>
     </row>
@@ -11741,11 +15491,11 @@
         <v>50</v>
       </c>
       <c r="B80" s="13">
-        <f>$B$12+$B$22*A80</f>
+        <f t="shared" si="0"/>
         <v>720.56</v>
       </c>
       <c r="C80" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
@@ -11754,11 +15504,11 @@
         <v>51</v>
       </c>
       <c r="B81" s="13">
-        <f>$B$12+$B$22*A81</f>
+        <f t="shared" si="0"/>
         <v>723.16</v>
       </c>
       <c r="C81" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>306</v>
       </c>
     </row>
@@ -11767,11 +15517,11 @@
         <v>52</v>
       </c>
       <c r="B82" s="13">
-        <f>$B$12+$B$22*A82</f>
+        <f t="shared" si="0"/>
         <v>725.76</v>
       </c>
       <c r="C82" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>312</v>
       </c>
     </row>
@@ -11780,11 +15530,11 @@
         <v>53</v>
       </c>
       <c r="B83" s="13">
-        <f>$B$12+$B$22*A83</f>
+        <f t="shared" si="0"/>
         <v>728.3599999999999</v>
       </c>
       <c r="C83" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>318</v>
       </c>
     </row>
@@ -11793,11 +15543,11 @@
         <v>54</v>
       </c>
       <c r="B84" s="13">
-        <f>$B$12+$B$22*A84</f>
+        <f t="shared" si="0"/>
         <v>730.95999999999992</v>
       </c>
       <c r="C84" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>324</v>
       </c>
     </row>
@@ -11806,11 +15556,11 @@
         <v>55</v>
       </c>
       <c r="B85" s="13">
-        <f>$B$12+$B$22*A85</f>
+        <f t="shared" si="0"/>
         <v>733.56</v>
       </c>
       <c r="C85" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>330</v>
       </c>
     </row>
@@ -11819,11 +15569,11 @@
         <v>56</v>
       </c>
       <c r="B86" s="13">
-        <f>$B$12+$B$22*A86</f>
+        <f t="shared" si="0"/>
         <v>736.16</v>
       </c>
       <c r="C86" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>336</v>
       </c>
     </row>
@@ -11832,11 +15582,11 @@
         <v>57</v>
       </c>
       <c r="B87" s="13">
-        <f>$B$12+$B$22*A87</f>
+        <f t="shared" si="0"/>
         <v>738.76</v>
       </c>
       <c r="C87" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>342</v>
       </c>
     </row>
@@ -11845,11 +15595,11 @@
         <v>58</v>
       </c>
       <c r="B88" s="13">
-        <f>$B$12+$B$22*A88</f>
+        <f t="shared" si="0"/>
         <v>741.3599999999999</v>
       </c>
       <c r="C88" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>348</v>
       </c>
     </row>
@@ -11858,11 +15608,11 @@
         <v>59</v>
       </c>
       <c r="B89" s="13">
-        <f>$B$12+$B$22*A89</f>
+        <f t="shared" si="0"/>
         <v>743.95999999999992</v>
       </c>
       <c r="C89" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>354</v>
       </c>
     </row>
@@ -11871,11 +15621,11 @@
         <v>60</v>
       </c>
       <c r="B90" s="13">
-        <f>$B$12+$B$22*A90</f>
+        <f t="shared" si="0"/>
         <v>746.56</v>
       </c>
       <c r="C90" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>360</v>
       </c>
     </row>
@@ -11884,11 +15634,11 @@
         <v>61</v>
       </c>
       <c r="B91" s="13">
-        <f>$B$12+$B$22*A91</f>
+        <f t="shared" si="0"/>
         <v>749.16</v>
       </c>
       <c r="C91" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>366</v>
       </c>
     </row>
@@ -11897,11 +15647,11 @@
         <v>62</v>
       </c>
       <c r="B92" s="13">
-        <f>$B$12+$B$22*A92</f>
+        <f t="shared" si="0"/>
         <v>751.76</v>
       </c>
       <c r="C92" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>372</v>
       </c>
     </row>
@@ -11910,11 +15660,11 @@
         <v>63</v>
       </c>
       <c r="B93" s="13">
-        <f>$B$12+$B$22*A93</f>
+        <f t="shared" si="0"/>
         <v>754.3599999999999</v>
       </c>
       <c r="C93" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>378</v>
       </c>
     </row>
@@ -11923,11 +15673,11 @@
         <v>64</v>
       </c>
       <c r="B94" s="13">
-        <f>$B$12+$B$22*A94</f>
+        <f t="shared" ref="B94:B157" si="2">$B$12+$B$22*A94</f>
         <v>756.95999999999992</v>
       </c>
       <c r="C94" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>384</v>
       </c>
     </row>
@@ -11936,11 +15686,11 @@
         <v>65</v>
       </c>
       <c r="B95" s="13">
-        <f>$B$12+$B$22*A95</f>
+        <f t="shared" si="2"/>
         <v>759.56</v>
       </c>
       <c r="C95" s="9">
-        <f t="shared" ref="C95:C158" si="1">$B$25*A95</f>
+        <f t="shared" ref="C95:C158" si="3">$B$25*A95</f>
         <v>390</v>
       </c>
     </row>
@@ -11949,11 +15699,11 @@
         <v>66</v>
       </c>
       <c r="B96" s="13">
-        <f>$B$12+$B$22*A96</f>
+        <f t="shared" si="2"/>
         <v>762.16</v>
       </c>
       <c r="C96" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>396</v>
       </c>
     </row>
@@ -11962,11 +15712,11 @@
         <v>67</v>
       </c>
       <c r="B97" s="13">
-        <f>$B$12+$B$22*A97</f>
+        <f t="shared" si="2"/>
         <v>764.76</v>
       </c>
       <c r="C97" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>402</v>
       </c>
     </row>
@@ -11975,11 +15725,11 @@
         <v>68</v>
       </c>
       <c r="B98" s="13">
-        <f>$B$12+$B$22*A98</f>
+        <f t="shared" si="2"/>
         <v>767.3599999999999</v>
       </c>
       <c r="C98" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>408</v>
       </c>
     </row>
@@ -11988,11 +15738,11 @@
         <v>69</v>
       </c>
       <c r="B99" s="13">
-        <f>$B$12+$B$22*A99</f>
+        <f t="shared" si="2"/>
         <v>769.95999999999992</v>
       </c>
       <c r="C99" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>414</v>
       </c>
     </row>
@@ -12001,11 +15751,11 @@
         <v>70</v>
       </c>
       <c r="B100" s="13">
-        <f>$B$12+$B$22*A100</f>
+        <f t="shared" si="2"/>
         <v>772.56</v>
       </c>
       <c r="C100" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>420</v>
       </c>
     </row>
@@ -12014,11 +15764,11 @@
         <v>71</v>
       </c>
       <c r="B101" s="13">
-        <f>$B$12+$B$22*A101</f>
+        <f t="shared" si="2"/>
         <v>775.16</v>
       </c>
       <c r="C101" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>426</v>
       </c>
     </row>
@@ -12027,11 +15777,11 @@
         <v>72</v>
       </c>
       <c r="B102" s="13">
-        <f>$B$12+$B$22*A102</f>
+        <f t="shared" si="2"/>
         <v>777.76</v>
       </c>
       <c r="C102" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>432</v>
       </c>
     </row>
@@ -12040,11 +15790,11 @@
         <v>73</v>
       </c>
       <c r="B103" s="13">
-        <f>$B$12+$B$22*A103</f>
+        <f t="shared" si="2"/>
         <v>780.3599999999999</v>
       </c>
       <c r="C103" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>438</v>
       </c>
     </row>
@@ -12053,11 +15803,11 @@
         <v>74</v>
       </c>
       <c r="B104" s="13">
-        <f>$B$12+$B$22*A104</f>
+        <f t="shared" si="2"/>
         <v>782.95999999999992</v>
       </c>
       <c r="C104" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>444</v>
       </c>
     </row>
@@ -12066,11 +15816,11 @@
         <v>75</v>
       </c>
       <c r="B105" s="13">
-        <f>$B$12+$B$22*A105</f>
+        <f t="shared" si="2"/>
         <v>785.56</v>
       </c>
       <c r="C105" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>450</v>
       </c>
     </row>
@@ -12079,11 +15829,11 @@
         <v>76</v>
       </c>
       <c r="B106" s="13">
-        <f>$B$12+$B$22*A106</f>
+        <f t="shared" si="2"/>
         <v>788.16</v>
       </c>
       <c r="C106" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>456</v>
       </c>
     </row>
@@ -12092,11 +15842,11 @@
         <v>77</v>
       </c>
       <c r="B107" s="13">
-        <f>$B$12+$B$22*A107</f>
+        <f t="shared" si="2"/>
         <v>790.76</v>
       </c>
       <c r="C107" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>462</v>
       </c>
     </row>
@@ -12105,11 +15855,11 @@
         <v>78</v>
       </c>
       <c r="B108" s="13">
-        <f>$B$12+$B$22*A108</f>
+        <f t="shared" si="2"/>
         <v>793.3599999999999</v>
       </c>
       <c r="C108" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>468</v>
       </c>
     </row>
@@ -12118,11 +15868,11 @@
         <v>79</v>
       </c>
       <c r="B109" s="13">
-        <f>$B$12+$B$22*A109</f>
+        <f t="shared" si="2"/>
         <v>795.95999999999992</v>
       </c>
       <c r="C109" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>474</v>
       </c>
     </row>
@@ -12131,11 +15881,11 @@
         <v>80</v>
       </c>
       <c r="B110" s="13">
-        <f>$B$12+$B$22*A110</f>
+        <f t="shared" si="2"/>
         <v>798.56</v>
       </c>
       <c r="C110" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>480</v>
       </c>
     </row>
@@ -12144,11 +15894,11 @@
         <v>81</v>
       </c>
       <c r="B111" s="13">
-        <f>$B$12+$B$22*A111</f>
+        <f t="shared" si="2"/>
         <v>801.16</v>
       </c>
       <c r="C111" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>486</v>
       </c>
     </row>
@@ -12157,11 +15907,11 @@
         <v>82</v>
       </c>
       <c r="B112" s="13">
-        <f>$B$12+$B$22*A112</f>
+        <f t="shared" si="2"/>
         <v>803.76</v>
       </c>
       <c r="C112" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>492</v>
       </c>
     </row>
@@ -12170,11 +15920,11 @@
         <v>83</v>
       </c>
       <c r="B113" s="13">
-        <f>$B$12+$B$22*A113</f>
+        <f t="shared" si="2"/>
         <v>806.3599999999999</v>
       </c>
       <c r="C113" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>498</v>
       </c>
     </row>
@@ -12183,11 +15933,11 @@
         <v>84</v>
       </c>
       <c r="B114" s="13">
-        <f>$B$12+$B$22*A114</f>
+        <f t="shared" si="2"/>
         <v>808.95999999999992</v>
       </c>
       <c r="C114" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>504</v>
       </c>
     </row>
@@ -12196,11 +15946,11 @@
         <v>85</v>
       </c>
       <c r="B115" s="13">
-        <f>$B$12+$B$22*A115</f>
+        <f t="shared" si="2"/>
         <v>811.56</v>
       </c>
       <c r="C115" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>510</v>
       </c>
     </row>
@@ -12209,11 +15959,11 @@
         <v>86</v>
       </c>
       <c r="B116" s="13">
-        <f>$B$12+$B$22*A116</f>
+        <f t="shared" si="2"/>
         <v>814.16</v>
       </c>
       <c r="C116" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>516</v>
       </c>
     </row>
@@ -12222,11 +15972,11 @@
         <v>87</v>
       </c>
       <c r="B117" s="13">
-        <f>$B$12+$B$22*A117</f>
+        <f t="shared" si="2"/>
         <v>816.76</v>
       </c>
       <c r="C117" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>522</v>
       </c>
     </row>
@@ -12235,11 +15985,11 @@
         <v>88</v>
       </c>
       <c r="B118" s="13">
-        <f>$B$12+$B$22*A118</f>
+        <f t="shared" si="2"/>
         <v>819.3599999999999</v>
       </c>
       <c r="C118" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>528</v>
       </c>
     </row>
@@ -12248,11 +15998,11 @@
         <v>89</v>
       </c>
       <c r="B119" s="13">
-        <f>$B$12+$B$22*A119</f>
+        <f t="shared" si="2"/>
         <v>821.95999999999992</v>
       </c>
       <c r="C119" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>534</v>
       </c>
     </row>
@@ -12261,11 +16011,11 @@
         <v>90</v>
       </c>
       <c r="B120" s="13">
-        <f>$B$12+$B$22*A120</f>
+        <f t="shared" si="2"/>
         <v>824.56</v>
       </c>
       <c r="C120" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>540</v>
       </c>
     </row>
@@ -12274,11 +16024,11 @@
         <v>91</v>
       </c>
       <c r="B121" s="13">
-        <f>$B$12+$B$22*A121</f>
+        <f t="shared" si="2"/>
         <v>827.16</v>
       </c>
       <c r="C121" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>546</v>
       </c>
     </row>
@@ -12287,11 +16037,11 @@
         <v>92</v>
       </c>
       <c r="B122" s="13">
-        <f>$B$12+$B$22*A122</f>
+        <f t="shared" si="2"/>
         <v>829.76</v>
       </c>
       <c r="C122" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>552</v>
       </c>
     </row>
@@ -12300,11 +16050,11 @@
         <v>93</v>
       </c>
       <c r="B123" s="13">
-        <f>$B$12+$B$22*A123</f>
+        <f t="shared" si="2"/>
         <v>832.3599999999999</v>
       </c>
       <c r="C123" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>558</v>
       </c>
     </row>
@@ -12313,11 +16063,11 @@
         <v>94</v>
       </c>
       <c r="B124" s="13">
-        <f>$B$12+$B$22*A124</f>
+        <f t="shared" si="2"/>
         <v>834.95999999999992</v>
       </c>
       <c r="C124" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>564</v>
       </c>
     </row>
@@ -12326,11 +16076,11 @@
         <v>95</v>
       </c>
       <c r="B125" s="13">
-        <f>$B$12+$B$22*A125</f>
+        <f t="shared" si="2"/>
         <v>837.56</v>
       </c>
       <c r="C125" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>570</v>
       </c>
     </row>
@@ -12339,11 +16089,11 @@
         <v>96</v>
       </c>
       <c r="B126" s="13">
-        <f>$B$12+$B$22*A126</f>
+        <f t="shared" si="2"/>
         <v>840.16</v>
       </c>
       <c r="C126" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>576</v>
       </c>
     </row>
@@ -12352,11 +16102,11 @@
         <v>97</v>
       </c>
       <c r="B127" s="13">
-        <f>$B$12+$B$22*A127</f>
+        <f t="shared" si="2"/>
         <v>842.76</v>
       </c>
       <c r="C127" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>582</v>
       </c>
     </row>
@@ -12365,11 +16115,11 @@
         <v>98</v>
       </c>
       <c r="B128" s="13">
-        <f>$B$12+$B$22*A128</f>
+        <f t="shared" si="2"/>
         <v>845.3599999999999</v>
       </c>
       <c r="C128" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>588</v>
       </c>
     </row>
@@ -12378,11 +16128,11 @@
         <v>99</v>
       </c>
       <c r="B129" s="13">
-        <f>$B$12+$B$22*A129</f>
+        <f t="shared" si="2"/>
         <v>847.96</v>
       </c>
       <c r="C129" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>594</v>
       </c>
     </row>
@@ -12391,11 +16141,11 @@
         <v>100</v>
       </c>
       <c r="B130" s="13">
-        <f>$B$12+$B$22*A130</f>
+        <f t="shared" si="2"/>
         <v>850.56</v>
       </c>
       <c r="C130" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>600</v>
       </c>
     </row>
@@ -12404,11 +16154,11 @@
         <v>101</v>
       </c>
       <c r="B131" s="13">
-        <f>$B$12+$B$22*A131</f>
+        <f t="shared" si="2"/>
         <v>853.16</v>
       </c>
       <c r="C131" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>606</v>
       </c>
     </row>
@@ -12417,11 +16167,11 @@
         <v>102</v>
       </c>
       <c r="B132" s="13">
-        <f>$B$12+$B$22*A132</f>
+        <f t="shared" si="2"/>
         <v>855.76</v>
       </c>
       <c r="C132" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>612</v>
       </c>
     </row>
@@ -12430,11 +16180,11 @@
         <v>103</v>
       </c>
       <c r="B133" s="13">
-        <f>$B$12+$B$22*A133</f>
+        <f t="shared" si="2"/>
         <v>858.3599999999999</v>
       </c>
       <c r="C133" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>618</v>
       </c>
     </row>
@@ -12443,11 +16193,11 @@
         <v>104</v>
       </c>
       <c r="B134" s="13">
-        <f>$B$12+$B$22*A134</f>
+        <f t="shared" si="2"/>
         <v>860.96</v>
       </c>
       <c r="C134" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>624</v>
       </c>
     </row>
@@ -12456,11 +16206,11 @@
         <v>105</v>
       </c>
       <c r="B135" s="13">
-        <f>$B$12+$B$22*A135</f>
+        <f t="shared" si="2"/>
         <v>863.56</v>
       </c>
       <c r="C135" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>630</v>
       </c>
     </row>
@@ -12469,11 +16219,11 @@
         <v>106</v>
       </c>
       <c r="B136" s="13">
-        <f>$B$12+$B$22*A136</f>
+        <f t="shared" si="2"/>
         <v>866.16</v>
       </c>
       <c r="C136" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>636</v>
       </c>
     </row>
@@ -12482,11 +16232,11 @@
         <v>107</v>
       </c>
       <c r="B137" s="13">
-        <f>$B$12+$B$22*A137</f>
+        <f t="shared" si="2"/>
         <v>868.76</v>
       </c>
       <c r="C137" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>642</v>
       </c>
     </row>
@@ -12495,11 +16245,11 @@
         <v>108</v>
       </c>
       <c r="B138" s="13">
-        <f>$B$12+$B$22*A138</f>
+        <f t="shared" si="2"/>
         <v>871.3599999999999</v>
       </c>
       <c r="C138" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>648</v>
       </c>
     </row>
@@ -12508,11 +16258,11 @@
         <v>109</v>
       </c>
       <c r="B139" s="13">
-        <f>$B$12+$B$22*A139</f>
+        <f t="shared" si="2"/>
         <v>873.96</v>
       </c>
       <c r="C139" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>654</v>
       </c>
     </row>
@@ -12521,11 +16271,11 @@
         <v>110</v>
       </c>
       <c r="B140" s="13">
-        <f>$B$12+$B$22*A140</f>
+        <f t="shared" si="2"/>
         <v>876.56</v>
       </c>
       <c r="C140" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>660</v>
       </c>
     </row>
@@ -12534,11 +16284,11 @@
         <v>111</v>
       </c>
       <c r="B141" s="13">
-        <f>$B$12+$B$22*A141</f>
+        <f t="shared" si="2"/>
         <v>879.16</v>
       </c>
       <c r="C141" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>666</v>
       </c>
     </row>
@@ -12547,11 +16297,11 @@
         <v>112</v>
       </c>
       <c r="B142" s="13">
-        <f>$B$12+$B$22*A142</f>
+        <f t="shared" si="2"/>
         <v>881.76</v>
       </c>
       <c r="C142" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>672</v>
       </c>
     </row>
@@ -12560,11 +16310,11 @@
         <v>113</v>
       </c>
       <c r="B143" s="13">
-        <f>$B$12+$B$22*A143</f>
+        <f t="shared" si="2"/>
         <v>884.3599999999999</v>
       </c>
       <c r="C143" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>678</v>
       </c>
     </row>
@@ -12573,11 +16323,11 @@
         <v>114</v>
       </c>
       <c r="B144" s="13">
-        <f>$B$12+$B$22*A144</f>
+        <f t="shared" si="2"/>
         <v>886.96</v>
       </c>
       <c r="C144" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>684</v>
       </c>
     </row>
@@ -12586,11 +16336,11 @@
         <v>115</v>
       </c>
       <c r="B145" s="13">
-        <f>$B$12+$B$22*A145</f>
+        <f t="shared" si="2"/>
         <v>889.56</v>
       </c>
       <c r="C145" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>690</v>
       </c>
     </row>
@@ -12599,11 +16349,11 @@
         <v>116</v>
       </c>
       <c r="B146" s="13">
-        <f>$B$12+$B$22*A146</f>
+        <f t="shared" si="2"/>
         <v>892.16</v>
       </c>
       <c r="C146" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>696</v>
       </c>
     </row>
@@ -12612,11 +16362,11 @@
         <v>117</v>
       </c>
       <c r="B147" s="13">
-        <f>$B$12+$B$22*A147</f>
+        <f t="shared" si="2"/>
         <v>894.76</v>
       </c>
       <c r="C147" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>702</v>
       </c>
     </row>
@@ -12625,11 +16375,11 @@
         <v>118</v>
       </c>
       <c r="B148" s="13">
-        <f>$B$12+$B$22*A148</f>
+        <f t="shared" si="2"/>
         <v>897.3599999999999</v>
       </c>
       <c r="C148" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>708</v>
       </c>
     </row>
@@ -12638,11 +16388,11 @@
         <v>119</v>
       </c>
       <c r="B149" s="13">
-        <f>$B$12+$B$22*A149</f>
+        <f t="shared" si="2"/>
         <v>899.96</v>
       </c>
       <c r="C149" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>714</v>
       </c>
     </row>
@@ -12651,11 +16401,11 @@
         <v>120</v>
       </c>
       <c r="B150" s="13">
-        <f>$B$12+$B$22*A150</f>
+        <f t="shared" si="2"/>
         <v>902.56</v>
       </c>
       <c r="C150" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
     </row>
@@ -12664,11 +16414,11 @@
         <v>121</v>
       </c>
       <c r="B151" s="13">
-        <f>$B$12+$B$22*A151</f>
+        <f t="shared" si="2"/>
         <v>905.16</v>
       </c>
       <c r="C151" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>726</v>
       </c>
     </row>
@@ -12677,11 +16427,11 @@
         <v>122</v>
       </c>
       <c r="B152" s="13">
-        <f>$B$12+$B$22*A152</f>
+        <f t="shared" si="2"/>
         <v>907.76</v>
       </c>
       <c r="C152" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>732</v>
       </c>
     </row>
@@ -12690,11 +16440,11 @@
         <v>123</v>
       </c>
       <c r="B153" s="13">
-        <f>$B$12+$B$22*A153</f>
+        <f t="shared" si="2"/>
         <v>910.3599999999999</v>
       </c>
       <c r="C153" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>738</v>
       </c>
     </row>
@@ -12703,11 +16453,11 @@
         <v>124</v>
       </c>
       <c r="B154" s="13">
-        <f>$B$12+$B$22*A154</f>
+        <f t="shared" si="2"/>
         <v>912.96</v>
       </c>
       <c r="C154" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>744</v>
       </c>
     </row>
@@ -12716,11 +16466,11 @@
         <v>125</v>
       </c>
       <c r="B155" s="13">
-        <f>$B$12+$B$22*A155</f>
+        <f t="shared" si="2"/>
         <v>915.56</v>
       </c>
       <c r="C155" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>750</v>
       </c>
     </row>
@@ -12729,11 +16479,11 @@
         <v>126</v>
       </c>
       <c r="B156" s="13">
-        <f>$B$12+$B$22*A156</f>
+        <f t="shared" si="2"/>
         <v>918.16</v>
       </c>
       <c r="C156" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>756</v>
       </c>
     </row>
@@ -12742,11 +16492,11 @@
         <v>127</v>
       </c>
       <c r="B157" s="13">
-        <f>$B$12+$B$22*A157</f>
+        <f t="shared" si="2"/>
         <v>920.76</v>
       </c>
       <c r="C157" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>762</v>
       </c>
     </row>
@@ -12755,11 +16505,11 @@
         <v>128</v>
       </c>
       <c r="B158" s="13">
-        <f>$B$12+$B$22*A158</f>
+        <f t="shared" ref="B158:B221" si="4">$B$12+$B$22*A158</f>
         <v>923.3599999999999</v>
       </c>
       <c r="C158" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>768</v>
       </c>
     </row>
@@ -12768,11 +16518,11 @@
         <v>129</v>
       </c>
       <c r="B159" s="13">
-        <f>$B$12+$B$22*A159</f>
+        <f t="shared" si="4"/>
         <v>925.96</v>
       </c>
       <c r="C159" s="9">
-        <f t="shared" ref="C159:C222" si="2">$B$25*A159</f>
+        <f t="shared" ref="C159:C222" si="5">$B$25*A159</f>
         <v>774</v>
       </c>
     </row>
@@ -12781,11 +16531,11 @@
         <v>130</v>
       </c>
       <c r="B160" s="13">
-        <f>$B$12+$B$22*A160</f>
+        <f t="shared" si="4"/>
         <v>928.56</v>
       </c>
       <c r="C160" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>780</v>
       </c>
     </row>
@@ -12794,11 +16544,11 @@
         <v>131</v>
       </c>
       <c r="B161" s="13">
-        <f>$B$12+$B$22*A161</f>
+        <f t="shared" si="4"/>
         <v>931.16</v>
       </c>
       <c r="C161" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>786</v>
       </c>
     </row>
@@ -12807,11 +16557,11 @@
         <v>132</v>
       </c>
       <c r="B162" s="13">
-        <f>$B$12+$B$22*A162</f>
+        <f t="shared" si="4"/>
         <v>933.76</v>
       </c>
       <c r="C162" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>792</v>
       </c>
     </row>
@@ -12820,11 +16570,11 @@
         <v>133</v>
       </c>
       <c r="B163" s="13">
-        <f>$B$12+$B$22*A163</f>
+        <f t="shared" si="4"/>
         <v>936.3599999999999</v>
       </c>
       <c r="C163" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>798</v>
       </c>
     </row>
@@ -12833,11 +16583,11 @@
         <v>134</v>
       </c>
       <c r="B164" s="13">
-        <f>$B$12+$B$22*A164</f>
+        <f t="shared" si="4"/>
         <v>938.96</v>
       </c>
       <c r="C164" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>804</v>
       </c>
     </row>
@@ -12846,11 +16596,11 @@
         <v>135</v>
       </c>
       <c r="B165" s="13">
-        <f>$B$12+$B$22*A165</f>
+        <f t="shared" si="4"/>
         <v>941.56</v>
       </c>
       <c r="C165" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>810</v>
       </c>
     </row>
@@ -12859,11 +16609,11 @@
         <v>136</v>
       </c>
       <c r="B166" s="13">
-        <f>$B$12+$B$22*A166</f>
+        <f t="shared" si="4"/>
         <v>944.16</v>
       </c>
       <c r="C166" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>816</v>
       </c>
     </row>
@@ -12872,11 +16622,11 @@
         <v>137</v>
       </c>
       <c r="B167" s="13">
-        <f>$B$12+$B$22*A167</f>
+        <f t="shared" si="4"/>
         <v>946.76</v>
       </c>
       <c r="C167" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>822</v>
       </c>
     </row>
@@ -12885,11 +16635,11 @@
         <v>138</v>
       </c>
       <c r="B168" s="13">
-        <f>$B$12+$B$22*A168</f>
+        <f t="shared" si="4"/>
         <v>949.3599999999999</v>
       </c>
       <c r="C168" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>828</v>
       </c>
     </row>
@@ -12898,11 +16648,11 @@
         <v>139</v>
       </c>
       <c r="B169" s="13">
-        <f>$B$12+$B$22*A169</f>
+        <f t="shared" si="4"/>
         <v>951.96</v>
       </c>
       <c r="C169" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>834</v>
       </c>
     </row>
@@ -12911,11 +16661,11 @@
         <v>140</v>
       </c>
       <c r="B170" s="13">
-        <f>$B$12+$B$22*A170</f>
+        <f t="shared" si="4"/>
         <v>954.56</v>
       </c>
       <c r="C170" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>840</v>
       </c>
     </row>
@@ -12924,11 +16674,11 @@
         <v>141</v>
       </c>
       <c r="B171" s="13">
-        <f>$B$12+$B$22*A171</f>
+        <f t="shared" si="4"/>
         <v>957.16</v>
       </c>
       <c r="C171" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>846</v>
       </c>
     </row>
@@ -12937,11 +16687,11 @@
         <v>142</v>
       </c>
       <c r="B172" s="13">
-        <f>$B$12+$B$22*A172</f>
+        <f t="shared" si="4"/>
         <v>959.76</v>
       </c>
       <c r="C172" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>852</v>
       </c>
     </row>
@@ -12950,11 +16700,11 @@
         <v>143</v>
       </c>
       <c r="B173" s="13">
-        <f>$B$12+$B$22*A173</f>
+        <f t="shared" si="4"/>
         <v>962.3599999999999</v>
       </c>
       <c r="C173" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>858</v>
       </c>
     </row>
@@ -12963,11 +16713,11 @@
         <v>144</v>
       </c>
       <c r="B174" s="13">
-        <f>$B$12+$B$22*A174</f>
+        <f t="shared" si="4"/>
         <v>964.96</v>
       </c>
       <c r="C174" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>864</v>
       </c>
     </row>
@@ -12976,11 +16726,11 @@
         <v>145</v>
       </c>
       <c r="B175" s="13">
-        <f>$B$12+$B$22*A175</f>
+        <f t="shared" si="4"/>
         <v>967.56</v>
       </c>
       <c r="C175" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>870</v>
       </c>
     </row>
@@ -12989,11 +16739,11 @@
         <v>146</v>
       </c>
       <c r="B176" s="13">
-        <f>$B$12+$B$22*A176</f>
+        <f t="shared" si="4"/>
         <v>970.16</v>
       </c>
       <c r="C176" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>876</v>
       </c>
     </row>
@@ -13002,11 +16752,11 @@
         <v>147</v>
       </c>
       <c r="B177" s="13">
-        <f>$B$12+$B$22*A177</f>
+        <f t="shared" si="4"/>
         <v>972.76</v>
       </c>
       <c r="C177" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>882</v>
       </c>
     </row>
@@ -13015,11 +16765,11 @@
         <v>148</v>
       </c>
       <c r="B178" s="13">
-        <f>$B$12+$B$22*A178</f>
+        <f t="shared" si="4"/>
         <v>975.3599999999999</v>
       </c>
       <c r="C178" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>888</v>
       </c>
     </row>
@@ -13028,11 +16778,11 @@
         <v>149</v>
       </c>
       <c r="B179" s="13">
-        <f>$B$12+$B$22*A179</f>
+        <f t="shared" si="4"/>
         <v>977.96</v>
       </c>
       <c r="C179" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>894</v>
       </c>
     </row>
@@ -13041,11 +16791,11 @@
         <v>150</v>
       </c>
       <c r="B180" s="13">
-        <f>$B$12+$B$22*A180</f>
+        <f t="shared" si="4"/>
         <v>980.56</v>
       </c>
       <c r="C180" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>900</v>
       </c>
     </row>
@@ -13054,11 +16804,11 @@
         <v>151</v>
       </c>
       <c r="B181" s="13">
-        <f>$B$12+$B$22*A181</f>
+        <f t="shared" si="4"/>
         <v>983.16</v>
       </c>
       <c r="C181" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>906</v>
       </c>
     </row>
@@ -13067,11 +16817,11 @@
         <v>152</v>
       </c>
       <c r="B182" s="13">
-        <f>$B$12+$B$22*A182</f>
+        <f t="shared" si="4"/>
         <v>985.76</v>
       </c>
       <c r="C182" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>912</v>
       </c>
     </row>
@@ -13080,11 +16830,11 @@
         <v>153</v>
       </c>
       <c r="B183" s="13">
-        <f>$B$12+$B$22*A183</f>
+        <f t="shared" si="4"/>
         <v>988.3599999999999</v>
       </c>
       <c r="C183" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>918</v>
       </c>
     </row>
@@ -13093,11 +16843,11 @@
         <v>154</v>
       </c>
       <c r="B184" s="13">
-        <f>$B$12+$B$22*A184</f>
+        <f t="shared" si="4"/>
         <v>990.96</v>
       </c>
       <c r="C184" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>924</v>
       </c>
     </row>
@@ -13106,11 +16856,11 @@
         <v>155</v>
       </c>
       <c r="B185" s="13">
-        <f>$B$12+$B$22*A185</f>
+        <f t="shared" si="4"/>
         <v>993.56</v>
       </c>
       <c r="C185" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>930</v>
       </c>
     </row>
@@ -13119,11 +16869,11 @@
         <v>156</v>
       </c>
       <c r="B186" s="13">
-        <f>$B$12+$B$22*A186</f>
+        <f t="shared" si="4"/>
         <v>996.16</v>
       </c>
       <c r="C186" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>936</v>
       </c>
     </row>
@@ -13132,11 +16882,11 @@
         <v>157</v>
       </c>
       <c r="B187" s="13">
-        <f>$B$12+$B$22*A187</f>
+        <f t="shared" si="4"/>
         <v>998.76</v>
       </c>
       <c r="C187" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>942</v>
       </c>
     </row>
@@ -13145,11 +16895,11 @@
         <v>158</v>
       </c>
       <c r="B188" s="13">
-        <f>$B$12+$B$22*A188</f>
+        <f t="shared" si="4"/>
         <v>1001.3599999999999</v>
       </c>
       <c r="C188" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>948</v>
       </c>
     </row>
@@ -13158,11 +16908,11 @@
         <v>159</v>
       </c>
       <c r="B189" s="13">
-        <f>$B$12+$B$22*A189</f>
+        <f t="shared" si="4"/>
         <v>1003.96</v>
       </c>
       <c r="C189" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>954</v>
       </c>
     </row>
@@ -13171,11 +16921,11 @@
         <v>160</v>
       </c>
       <c r="B190" s="13">
-        <f>$B$12+$B$22*A190</f>
+        <f t="shared" si="4"/>
         <v>1006.56</v>
       </c>
       <c r="C190" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>960</v>
       </c>
     </row>
@@ -13184,11 +16934,11 @@
         <v>161</v>
       </c>
       <c r="B191" s="13">
-        <f>$B$12+$B$22*A191</f>
+        <f t="shared" si="4"/>
         <v>1009.16</v>
       </c>
       <c r="C191" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>966</v>
       </c>
     </row>
@@ -13197,11 +16947,11 @@
         <v>162</v>
       </c>
       <c r="B192" s="13">
-        <f>$B$12+$B$22*A192</f>
+        <f t="shared" si="4"/>
         <v>1011.76</v>
       </c>
       <c r="C192" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>972</v>
       </c>
     </row>
@@ -13210,11 +16960,11 @@
         <v>163</v>
       </c>
       <c r="B193" s="13">
-        <f>$B$12+$B$22*A193</f>
+        <f t="shared" si="4"/>
         <v>1014.3599999999999</v>
       </c>
       <c r="C193" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>978</v>
       </c>
     </row>
@@ -13223,11 +16973,11 @@
         <v>164</v>
       </c>
       <c r="B194" s="13">
-        <f>$B$12+$B$22*A194</f>
+        <f t="shared" si="4"/>
         <v>1016.96</v>
       </c>
       <c r="C194" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>984</v>
       </c>
     </row>
@@ -13236,11 +16986,11 @@
         <v>165</v>
       </c>
       <c r="B195" s="13">
-        <f>$B$12+$B$22*A195</f>
+        <f t="shared" si="4"/>
         <v>1019.56</v>
       </c>
       <c r="C195" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>990</v>
       </c>
     </row>
@@ -13249,11 +16999,11 @@
         <v>166</v>
       </c>
       <c r="B196" s="13">
-        <f>$B$12+$B$22*A196</f>
+        <f t="shared" si="4"/>
         <v>1022.16</v>
       </c>
       <c r="C196" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>996</v>
       </c>
     </row>
@@ -13262,11 +17012,11 @@
         <v>167</v>
       </c>
       <c r="B197" s="13">
-        <f>$B$12+$B$22*A197</f>
+        <f t="shared" si="4"/>
         <v>1024.76</v>
       </c>
       <c r="C197" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1002</v>
       </c>
     </row>
@@ -13275,11 +17025,11 @@
         <v>168</v>
       </c>
       <c r="B198" s="13">
-        <f>$B$12+$B$22*A198</f>
+        <f t="shared" si="4"/>
         <v>1027.3599999999999</v>
       </c>
       <c r="C198" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1008</v>
       </c>
     </row>
@@ -13288,11 +17038,11 @@
         <v>169</v>
       </c>
       <c r="B199" s="13">
-        <f>$B$12+$B$22*A199</f>
+        <f t="shared" si="4"/>
         <v>1029.96</v>
       </c>
       <c r="C199" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1014</v>
       </c>
     </row>
@@ -13301,11 +17051,11 @@
         <v>170</v>
       </c>
       <c r="B200" s="13">
-        <f>$B$12+$B$22*A200</f>
+        <f t="shared" si="4"/>
         <v>1032.56</v>
       </c>
       <c r="C200" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1020</v>
       </c>
     </row>
@@ -13314,11 +17064,11 @@
         <v>171</v>
       </c>
       <c r="B201" s="13">
-        <f>$B$12+$B$22*A201</f>
+        <f t="shared" si="4"/>
         <v>1035.1599999999999</v>
       </c>
       <c r="C201" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1026</v>
       </c>
     </row>
@@ -13327,11 +17077,11 @@
         <v>172</v>
       </c>
       <c r="B202" s="13">
-        <f>$B$12+$B$22*A202</f>
+        <f t="shared" si="4"/>
         <v>1037.76</v>
       </c>
       <c r="C202" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1032</v>
       </c>
     </row>
@@ -13340,11 +17090,11 @@
         <v>173</v>
       </c>
       <c r="B203" s="13">
-        <f>$B$12+$B$22*A203</f>
+        <f t="shared" si="4"/>
         <v>1040.3599999999999</v>
       </c>
       <c r="C203" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1038</v>
       </c>
     </row>
@@ -13353,11 +17103,11 @@
         <v>174</v>
       </c>
       <c r="B204" s="13">
-        <f>$B$12+$B$22*A204</f>
+        <f t="shared" si="4"/>
         <v>1042.96</v>
       </c>
       <c r="C204" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1044</v>
       </c>
     </row>
@@ -13366,11 +17116,11 @@
         <v>175</v>
       </c>
       <c r="B205" s="13">
-        <f>$B$12+$B$22*A205</f>
+        <f t="shared" si="4"/>
         <v>1045.56</v>
       </c>
       <c r="C205" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1050</v>
       </c>
     </row>
@@ -13379,11 +17129,11 @@
         <v>176</v>
       </c>
       <c r="B206" s="13">
-        <f>$B$12+$B$22*A206</f>
+        <f t="shared" si="4"/>
         <v>1048.1599999999999</v>
       </c>
       <c r="C206" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1056</v>
       </c>
     </row>
@@ -13392,11 +17142,11 @@
         <v>177</v>
       </c>
       <c r="B207" s="13">
-        <f>$B$12+$B$22*A207</f>
+        <f t="shared" si="4"/>
         <v>1050.76</v>
       </c>
       <c r="C207" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1062</v>
       </c>
     </row>
@@ -13405,11 +17155,11 @@
         <v>178</v>
       </c>
       <c r="B208" s="13">
-        <f>$B$12+$B$22*A208</f>
+        <f t="shared" si="4"/>
         <v>1053.3599999999999</v>
       </c>
       <c r="C208" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1068</v>
       </c>
     </row>
@@ -13418,11 +17168,11 @@
         <v>179</v>
       </c>
       <c r="B209" s="13">
-        <f>$B$12+$B$22*A209</f>
+        <f t="shared" si="4"/>
         <v>1055.96</v>
       </c>
       <c r="C209" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1074</v>
       </c>
     </row>
@@ -13431,11 +17181,11 @@
         <v>180</v>
       </c>
       <c r="B210" s="13">
-        <f>$B$12+$B$22*A210</f>
+        <f t="shared" si="4"/>
         <v>1058.56</v>
       </c>
       <c r="C210" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1080</v>
       </c>
     </row>
@@ -13444,11 +17194,11 @@
         <v>181</v>
       </c>
       <c r="B211" s="13">
-        <f>$B$12+$B$22*A211</f>
+        <f t="shared" si="4"/>
         <v>1061.1599999999999</v>
       </c>
       <c r="C211" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1086</v>
       </c>
     </row>
@@ -13457,11 +17207,11 @@
         <v>182</v>
       </c>
       <c r="B212" s="13">
-        <f>$B$12+$B$22*A212</f>
+        <f t="shared" si="4"/>
         <v>1063.76</v>
       </c>
       <c r="C212" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1092</v>
       </c>
     </row>
@@ -13470,11 +17220,11 @@
         <v>183</v>
       </c>
       <c r="B213" s="13">
-        <f>$B$12+$B$22*A213</f>
+        <f t="shared" si="4"/>
         <v>1066.3599999999999</v>
       </c>
       <c r="C213" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1098</v>
       </c>
     </row>
@@ -13483,11 +17233,11 @@
         <v>184</v>
       </c>
       <c r="B214" s="13">
-        <f>$B$12+$B$22*A214</f>
+        <f t="shared" si="4"/>
         <v>1068.96</v>
       </c>
       <c r="C214" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1104</v>
       </c>
     </row>
@@ -13496,11 +17246,11 @@
         <v>185</v>
       </c>
       <c r="B215" s="13">
-        <f>$B$12+$B$22*A215</f>
+        <f t="shared" si="4"/>
         <v>1071.56</v>
       </c>
       <c r="C215" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1110</v>
       </c>
     </row>
@@ -13509,11 +17259,11 @@
         <v>186</v>
       </c>
       <c r="B216" s="13">
-        <f>$B$12+$B$22*A216</f>
+        <f t="shared" si="4"/>
         <v>1074.1599999999999</v>
       </c>
       <c r="C216" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1116</v>
       </c>
     </row>
@@ -13522,11 +17272,11 @@
         <v>187</v>
       </c>
       <c r="B217" s="13">
-        <f>$B$12+$B$22*A217</f>
+        <f t="shared" si="4"/>
         <v>1076.76</v>
       </c>
       <c r="C217" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1122</v>
       </c>
     </row>
@@ -13535,11 +17285,11 @@
         <v>188</v>
       </c>
       <c r="B218" s="13">
-        <f>$B$12+$B$22*A218</f>
+        <f t="shared" si="4"/>
         <v>1079.3599999999999</v>
       </c>
       <c r="C218" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1128</v>
       </c>
     </row>
@@ -13548,11 +17298,11 @@
         <v>189</v>
       </c>
       <c r="B219" s="13">
-        <f>$B$12+$B$22*A219</f>
+        <f t="shared" si="4"/>
         <v>1081.96</v>
       </c>
       <c r="C219" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1134</v>
       </c>
     </row>
@@ -13561,11 +17311,11 @@
         <v>190</v>
       </c>
       <c r="B220" s="13">
-        <f>$B$12+$B$22*A220</f>
+        <f t="shared" si="4"/>
         <v>1084.56</v>
       </c>
       <c r="C220" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1140</v>
       </c>
     </row>
@@ -13574,11 +17324,11 @@
         <v>191</v>
       </c>
       <c r="B221" s="13">
-        <f>$B$12+$B$22*A221</f>
+        <f t="shared" si="4"/>
         <v>1087.1599999999999</v>
       </c>
       <c r="C221" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1146</v>
       </c>
     </row>
@@ -13587,11 +17337,11 @@
         <v>192</v>
       </c>
       <c r="B222" s="13">
-        <f>$B$12+$B$22*A222</f>
+        <f t="shared" ref="B222:B285" si="6">$B$12+$B$22*A222</f>
         <v>1089.76</v>
       </c>
       <c r="C222" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1152</v>
       </c>
     </row>
@@ -13600,11 +17350,11 @@
         <v>193</v>
       </c>
       <c r="B223" s="13">
-        <f>$B$12+$B$22*A223</f>
+        <f t="shared" si="6"/>
         <v>1092.3599999999999</v>
       </c>
       <c r="C223" s="9">
-        <f t="shared" ref="C223:C230" si="3">$B$25*A223</f>
+        <f t="shared" ref="C223:C229" si="7">$B$25*A223</f>
         <v>1158</v>
       </c>
     </row>
@@ -13613,11 +17363,11 @@
         <v>194</v>
       </c>
       <c r="B224" s="13">
-        <f>$B$12+$B$22*A224</f>
+        <f t="shared" si="6"/>
         <v>1094.96</v>
       </c>
       <c r="C224" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1164</v>
       </c>
     </row>
@@ -13626,11 +17376,11 @@
         <v>195</v>
       </c>
       <c r="B225" s="13">
-        <f>$B$12+$B$22*A225</f>
+        <f t="shared" si="6"/>
         <v>1097.56</v>
       </c>
       <c r="C225" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1170</v>
       </c>
     </row>
@@ -13639,11 +17389,11 @@
         <v>196</v>
       </c>
       <c r="B226" s="13">
-        <f>$B$12+$B$22*A226</f>
+        <f t="shared" si="6"/>
         <v>1100.1599999999999</v>
       </c>
       <c r="C226" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1176</v>
       </c>
     </row>
@@ -13652,11 +17402,11 @@
         <v>197</v>
       </c>
       <c r="B227" s="13">
-        <f>$B$12+$B$22*A227</f>
+        <f t="shared" si="6"/>
         <v>1102.76</v>
       </c>
       <c r="C227" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1182</v>
       </c>
     </row>
@@ -13665,11 +17415,11 @@
         <v>198</v>
       </c>
       <c r="B228" s="13">
-        <f>$B$12+$B$22*A228</f>
+        <f t="shared" si="6"/>
         <v>1105.3600000000001</v>
       </c>
       <c r="C228" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1188</v>
       </c>
     </row>
@@ -13678,11 +17428,11 @@
         <v>199</v>
       </c>
       <c r="B229" s="13">
-        <f>$B$12+$B$22*A229</f>
+        <f t="shared" si="6"/>
         <v>1107.96</v>
       </c>
       <c r="C229" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1194</v>
       </c>
     </row>
@@ -13691,7 +17441,7 @@
         <v>200</v>
       </c>
       <c r="B230" s="13">
-        <f>$B$12+$B$22*A230</f>
+        <f t="shared" si="6"/>
         <v>1110.56</v>
       </c>
       <c r="C230" s="9">
@@ -13704,11 +17454,11 @@
         <v>201</v>
       </c>
       <c r="B231" s="13">
-        <f t="shared" ref="B231:B255" si="4">$B$12+$B$22*A231</f>
+        <f t="shared" ref="B231:B255" si="8">$B$12+$B$22*A231</f>
         <v>1113.1599999999999</v>
       </c>
       <c r="C231" s="9">
-        <f t="shared" ref="C231:C244" si="5">$B$25*A231</f>
+        <f t="shared" ref="C231:C244" si="9">$B$25*A231</f>
         <v>1206</v>
       </c>
     </row>
@@ -13717,11 +17467,11 @@
         <v>202</v>
       </c>
       <c r="B232" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1115.76</v>
       </c>
       <c r="C232" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1212</v>
       </c>
     </row>
@@ -13730,11 +17480,11 @@
         <v>203</v>
       </c>
       <c r="B233" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1118.3600000000001</v>
       </c>
       <c r="C233" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1218</v>
       </c>
     </row>
@@ -13743,11 +17493,11 @@
         <v>204</v>
       </c>
       <c r="B234" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1120.96</v>
       </c>
       <c r="C234" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1224</v>
       </c>
     </row>
@@ -13756,11 +17506,11 @@
         <v>205</v>
       </c>
       <c r="B235" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1123.56</v>
       </c>
       <c r="C235" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1230</v>
       </c>
     </row>
@@ -13769,11 +17519,11 @@
         <v>206</v>
       </c>
       <c r="B236" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1126.1599999999999</v>
       </c>
       <c r="C236" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1236</v>
       </c>
     </row>
@@ -13782,11 +17532,11 @@
         <v>207</v>
       </c>
       <c r="B237" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1128.76</v>
       </c>
       <c r="C237" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1242</v>
       </c>
     </row>
@@ -13795,11 +17545,11 @@
         <v>208</v>
       </c>
       <c r="B238" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1131.3600000000001</v>
       </c>
       <c r="C238" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1248</v>
       </c>
     </row>
@@ -13808,11 +17558,11 @@
         <v>209</v>
       </c>
       <c r="B239" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1133.96</v>
       </c>
       <c r="C239" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1254</v>
       </c>
     </row>
@@ -13821,11 +17571,11 @@
         <v>210</v>
       </c>
       <c r="B240" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1136.56</v>
       </c>
       <c r="C240" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1260</v>
       </c>
     </row>
@@ -13834,11 +17584,11 @@
         <v>211</v>
       </c>
       <c r="B241" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1139.1599999999999</v>
       </c>
       <c r="C241" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1266</v>
       </c>
     </row>
@@ -13847,11 +17597,11 @@
         <v>212</v>
       </c>
       <c r="B242" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1141.76</v>
       </c>
       <c r="C242" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1272</v>
       </c>
     </row>
@@ -13860,11 +17610,11 @@
         <v>213</v>
       </c>
       <c r="B243" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1144.3600000000001</v>
       </c>
       <c r="C243" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1278</v>
       </c>
     </row>
@@ -13873,11 +17623,11 @@
         <v>214</v>
       </c>
       <c r="B244" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1146.96</v>
       </c>
       <c r="C244" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1284</v>
       </c>
     </row>
@@ -13899,11 +17649,11 @@
         <v>216</v>
       </c>
       <c r="B246" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1152.1599999999999</v>
       </c>
       <c r="C246" s="9">
-        <f t="shared" ref="C246:C250" si="6">$B$25*A246</f>
+        <f t="shared" ref="C246:C250" si="10">$B$25*A246</f>
         <v>1296</v>
       </c>
     </row>
@@ -13912,11 +17662,11 @@
         <v>217</v>
       </c>
       <c r="B247" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1154.76</v>
       </c>
       <c r="C247" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1302</v>
       </c>
     </row>
@@ -13925,11 +17675,11 @@
         <v>218</v>
       </c>
       <c r="B248" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1157.3600000000001</v>
       </c>
       <c r="C248" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1308</v>
       </c>
     </row>
@@ -13938,11 +17688,11 @@
         <v>219</v>
       </c>
       <c r="B249" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1159.96</v>
       </c>
       <c r="C249" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1314</v>
       </c>
     </row>
@@ -13951,11 +17701,11 @@
         <v>220</v>
       </c>
       <c r="B250" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1162.56</v>
       </c>
       <c r="C250" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1320</v>
       </c>
     </row>
@@ -13977,11 +17727,11 @@
         <v>222</v>
       </c>
       <c r="B252" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1167.76</v>
       </c>
       <c r="C252" s="9">
-        <f t="shared" ref="C252:C255" si="7">$B$25*A252</f>
+        <f t="shared" ref="C252:C255" si="11">$B$25*A252</f>
         <v>1332</v>
       </c>
     </row>
@@ -13990,11 +17740,11 @@
         <v>223</v>
       </c>
       <c r="B253" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1170.3600000000001</v>
       </c>
       <c r="C253" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1338</v>
       </c>
     </row>
@@ -14003,11 +17753,11 @@
         <v>224</v>
       </c>
       <c r="B254" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1172.96</v>
       </c>
       <c r="C254" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1344</v>
       </c>
     </row>
@@ -14016,11 +17766,11 @@
         <v>225</v>
       </c>
       <c r="B255" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1175.56</v>
       </c>
       <c r="C255" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1350</v>
       </c>
     </row>
@@ -14044,6 +17794,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008C371D7D644B574CA89B5F00ED09B0C8" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="bd33285d5daf4dee329ae000bb583124">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5cfc5781-36c7-40ed-af62-43a27290b458" xmlns:ns4="c4b568bc-dd8a-4a74-b92a-f01b2ee1149b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6974282011ce0aef1ed393e1233ba8cc" ns3:_="" ns4:_="">
     <xsd:import namespace="5cfc5781-36c7-40ed-af62-43a27290b458"/>
@@ -14276,15 +18035,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4FBB6FF-EC5C-4DA6-BDE2-BFD391C0AAC1}">
   <ds:schemaRefs>
@@ -14303,6 +18053,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5725DCE3-03BC-44D7-BC9C-71C7B5BFC1A0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7417AF40-C3B2-4E1A-88EB-AB01B9312A09}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14319,12 +18077,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5725DCE3-03BC-44D7-BC9C-71C7B5BFC1A0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/utilities/Punto_de_equilibrio.xlsx
+++ b/utilities/Punto_de_equilibrio.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MaBel\utilities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F622050-5B34-4B63-89F2-537D3103D9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148A9DED-DFF6-4C09-B691-98188151F03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{E75E3C13-AC3D-4914-9135-F849659ACBFB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{E75E3C13-AC3D-4914-9135-F849659ACBFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Ejercicio Clase" sheetId="3" r:id="rId1"/>
     <sheet name="Ejercicio 2" sheetId="4" r:id="rId2"/>
+    <sheet name="Mi Punto de Equilibrio" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
   <si>
     <t xml:space="preserve">Descripción </t>
   </si>
@@ -8964,6 +8965,2888 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-EC"/>
+              <a:t>Punto de Equilibrio</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Mi Punto de Equilibrio'!$B$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Costo Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Mi Punto de Equilibrio'!$A$30:$A$230</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="201"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>121</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>123</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>124</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>127</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>131</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>133</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>134</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>139</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>142</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>146</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>147</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>151</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>152</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>158</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>164</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>166</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>173</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>183</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>191</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>196</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>198</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Mi Punto de Equilibrio'!$B$30:$B$230</c:f>
+              <c:numCache>
+                <c:formatCode>_ "$"* #,##0.00_ ;_ "$"* \-#,##0.00_ ;_ "$"* "-"??_ ;_ @_ </c:formatCode>
+                <c:ptCount val="201"/>
+                <c:pt idx="0">
+                  <c:v>590.55999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>593.16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>595.76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>598.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>600.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>603.55999999999995</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>606.16</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>608.76</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>611.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>613.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>616.55999999999995</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>619.16</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>621.76</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>624.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>626.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>629.55999999999995</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>632.16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>634.76</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>637.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>639.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>642.55999999999995</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>645.16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>647.76</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>650.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>652.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>655.56</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>658.16</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>660.76</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>663.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>665.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>668.56</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>671.16</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>673.76</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>676.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>678.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>681.56</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>684.16</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>686.76</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>689.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>691.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>694.56</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>697.16</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>699.76</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>702.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>704.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>707.56</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>710.16</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>712.76</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>715.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>717.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>720.56</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>723.16</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>725.76</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>728.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>730.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>733.56</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>736.16</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>738.76</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>741.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>743.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>746.56</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>749.16</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>751.76</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>754.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>756.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>759.56</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>762.16</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>764.76</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>767.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>769.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>772.56</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>775.16</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>777.76</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>780.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>782.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>785.56</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>788.16</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>790.76</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>793.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>795.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>798.56</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>801.16</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>803.76</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>806.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>808.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>811.56</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>814.16</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>816.76</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>819.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>821.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>824.56</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>827.16</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>829.76</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>832.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>834.95999999999992</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>837.56</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>840.16</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>842.76</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>845.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>847.96</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>850.56</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>853.16</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>855.76</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>858.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>860.96</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>863.56</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>866.16</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>868.76</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>871.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>873.96</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>876.56</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>879.16</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>881.76</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>884.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>886.96</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>889.56</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>892.16</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>894.76</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>897.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>899.96</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>902.56</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>905.16</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>907.76</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>910.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>912.96</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>915.56</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>918.16</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>920.76</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>923.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>925.96</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>928.56</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>931.16</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>933.76</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>936.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>938.96</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>941.56</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>944.16</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>946.76</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>949.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>951.96</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>954.56</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>957.16</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>959.76</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>962.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>964.96</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>967.56</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>970.16</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>972.76</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>975.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>977.96</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>980.56</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>983.16</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>985.76</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>988.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>990.96</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>993.56</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>996.16</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>998.76</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>1001.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>1003.96</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>1006.56</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>1009.16</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>1011.76</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>1014.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>1016.96</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>1019.56</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>1022.16</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>1024.76</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>1027.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1029.96</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>1032.56</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>1035.1599999999999</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>1037.76</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>1040.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>1042.96</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>1045.56</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>1048.1599999999999</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>1050.76</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>1053.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1055.96</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>1058.56</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>1061.1599999999999</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>1063.76</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>1066.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>1068.96</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>1071.56</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>1074.1599999999999</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>1076.76</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>1079.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>1081.96</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>1084.56</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>1087.1599999999999</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>1089.76</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>1092.3599999999999</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>1094.96</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>1097.56</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>1100.1599999999999</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>1102.76</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>1105.3600000000001</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1107.96</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>1110.56</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-02FF-496B-80EE-EDB21F335468}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Mi Punto de Equilibrio'!$C$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ingreso de Ventas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="100"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-02FF-496B-80EE-EDB21F335468}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-PE"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Mi Punto de Equilibrio'!$A$30:$A$230</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="201"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>63</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>106</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>112</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>121</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>123</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>124</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>127</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>131</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>133</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>134</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>136</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>139</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>142</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>146</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>147</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>151</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>152</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>158</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>164</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>166</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>169</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>173</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>183</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>189</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>191</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>196</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>198</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Mi Punto de Equilibrio'!$C$30:$C$230</c:f>
+              <c:numCache>
+                <c:formatCode>_ "$"* #,##0.00_ ;_ "$"* \-#,##0.00_ ;_ "$"* "-"??_ ;_ @_ </c:formatCode>
+                <c:ptCount val="201"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>174</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>198</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>228</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>234</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>246</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>258</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>264</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>276</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>282</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>288</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>294</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>306</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>312</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>318</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>324</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>330</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>336</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>342</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>348</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>354</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>366</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>372</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>378</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>384</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>396</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>402</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>408</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>414</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>426</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>432</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>438</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>444</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>456</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>462</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>468</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>474</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>486</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>492</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>498</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>504</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>516</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>522</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>528</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>534</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>540</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>546</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>552</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>558</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>564</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>570</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>576</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>582</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>588</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>594</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>606</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>612</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>618</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>624</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>630</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>636</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>642</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>648</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>654</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>666</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>672</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>678</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>684</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>696</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>702</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>708</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>714</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>720</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>726</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>732</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>738</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>744</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>756</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>762</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>768</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>774</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>780</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>786</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>792</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>798</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>804</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>816</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>822</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>828</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>834</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>846</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>852</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>858</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>864</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>876</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>882</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>888</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>894</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>906</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>912</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>918</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>924</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>930</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>936</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>942</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>948</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>954</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>966</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>972</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>978</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>984</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>990</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>996</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>1002</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>1008</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1014</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>1020</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>1026</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>1032</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>1038</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>1044</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>1056</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>1062</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>1068</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1074</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>1080</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>1086</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>1092</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>1098</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>1104</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>1110</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>1116</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>1122</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>1128</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>1134</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>1140</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>1146</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>1152</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>1158</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>1164</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>1170</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>1176</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>1182</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>1188</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1194</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>1200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-02FF-496B-80EE-EDB21F335468}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1710370848"/>
+        <c:axId val="1710371328"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1710370848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:noFill/>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1710371328"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1710371328"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_ &quot;$&quot;* #,##0.00_ ;_ &quot;$&quot;* \-#,##0.00_ ;_ &quot;$&quot;* &quot;-&quot;??_ ;_ @_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1710370848"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -9045,6 +11928,46 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -10676,6 +13599,544 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="245">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="3"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -10696,7 +14157,7 @@
         <xdr:cNvPr id="2" name="Imagen 1" descr="Calculadora de Punto de Equilibrio: Qué es, cómo se calcula | Blog UPSJB">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AE9FC08-7E10-47C6-8D68-B592AC1FC9A3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10770,7 +14231,7 @@
         <xdr:cNvPr id="4" name="CuadroTexto 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D57F19C1-9EE9-57B2-B074-5AEA60F32D99}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10849,7 +14310,7 @@
         <xdr:cNvPr id="5" name="Gráfico 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC5800A0-EC51-763A-92C3-A69C6E4F71FF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10890,7 +14351,7 @@
         <xdr:cNvPr id="2" name="Imagen 1" descr="Calculadora de Punto de Equilibrio: Qué es, cómo se calcula | Blog UPSJB">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8044E58D-FBF1-429F-B55A-9ED86B245CB8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10964,7 +14425,7 @@
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E155FF42-6BCD-43BB-98A0-8FD53C514BAC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11043,7 +14504,7 @@
         <xdr:cNvPr id="8" name="Gráfico 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{342DB7DB-22B8-2E7B-4BB3-BB7AC3215FE3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11079,7 +14540,7 @@
         <xdr:cNvPr id="5" name="Conector recto 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6504A76-8295-B922-8D12-3EBB88529A2B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11138,7 +14599,7 @@
         <xdr:cNvPr id="6" name="Conector recto 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1201A87A-B5BD-4DA7-8F38-188CE1EFC670}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11197,7 +14658,7 @@
         <xdr:cNvPr id="11" name="Flecha: hacia abajo 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B69654D-3AEC-DF77-D0E4-8FE04FD71D61}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11257,7 +14718,7 @@
         <xdr:cNvPr id="4" name="Gráfico 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{342DB7DB-22B8-2E7B-4BB3-BB7AC3215FE3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11293,7 +14754,7 @@
         <xdr:cNvPr id="9" name="Imagen 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{246BB3EB-27BC-067F-48ED-A6CA4762F752}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11337,7 +14798,7 @@
         <xdr:cNvPr id="13" name="Imagen 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9D0EF08-AD6C-36E2-38F5-BABD8FBA8D4E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11541,6 +15002,202 @@
     </cdr:cxnSp>
   </cdr:relSizeAnchor>
 </c:userShapes>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>162432</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1" descr="Calculadora de Punto de Equilibrio: Qué es, cómo se calcula | Blog UPSJB">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0624459-5CB5-45EB-B745-92B3D7C5FCFE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4667250" y="57149"/>
+          <a:ext cx="3067050" cy="1819783"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="sq">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="43000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>476249</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>600074</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="CuadroTexto 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{590309E1-10A2-431A-85FD-5E1D5C64F6AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8324849" y="904875"/>
+          <a:ext cx="3933825" cy="971550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-EC" sz="1400" b="1"/>
+            <a:t>Ingreso</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-EC" sz="1400" b="1" baseline="0"/>
+            <a:t> de equilibrio </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-EC" sz="1400" baseline="0"/>
+            <a:t>=</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-EC" sz="1400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-EC" sz="1400" baseline="0"/>
+            <a:t>Cantidad de equilibrio * Precio de Venta Unitario</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-EC" sz="1400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>685799</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>247649</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15E57B32-C278-4942-A20A-359AF8DC39EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17337,7 +20994,7 @@
         <v>192</v>
       </c>
       <c r="B222" s="13">
-        <f t="shared" ref="B222:B285" si="6">$B$12+$B$22*A222</f>
+        <f t="shared" ref="B222:B230" si="6">$B$12+$B$22*A222</f>
         <v>1089.76</v>
       </c>
       <c r="C222" s="9">
@@ -17785,24 +21442,2813 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5cfc5781-36c7-40ed-af62-43a27290b458" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C51139-5654-43BF-B963-5D244835E3DC}">
+  <dimension ref="A3:F230"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="5">
+        <f>SUM(B5:B11)</f>
+        <v>590.55999999999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="E16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="7">
+        <f>B12/(B25-B22)</f>
+        <v>173.69411764705882</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="7">
+        <f>F16*B25</f>
+        <v>1042.1647058823528</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="F18">
+        <f>F16*B22</f>
+        <v>451.60470588235296</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5">
+        <f>SUM(B18:B21)</f>
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
+        <v>0</v>
+      </c>
+      <c r="B30" s="13">
+        <f>$B$12+$B$22*A30</f>
+        <v>590.55999999999995</v>
+      </c>
+      <c r="C30" s="9">
+        <f>$B$25*A30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>1</v>
+      </c>
+      <c r="B31" s="13">
+        <f t="shared" ref="B31:B94" si="0">$B$12+$B$22*A31</f>
+        <v>593.16</v>
+      </c>
+      <c r="C31" s="9">
+        <f t="shared" ref="C31:C94" si="1">$B$25*A31</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>2</v>
+      </c>
+      <c r="B32" s="13">
+        <f t="shared" si="0"/>
+        <v>595.76</v>
+      </c>
+      <c r="C32" s="9">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <v>3</v>
+      </c>
+      <c r="B33" s="13">
+        <f t="shared" si="0"/>
+        <v>598.3599999999999</v>
+      </c>
+      <c r="C33" s="9">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <v>4</v>
+      </c>
+      <c r="B34" s="13">
+        <f t="shared" si="0"/>
+        <v>600.95999999999992</v>
+      </c>
+      <c r="C34" s="9">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="8">
+        <v>5</v>
+      </c>
+      <c r="B35" s="13">
+        <f t="shared" si="0"/>
+        <v>603.55999999999995</v>
+      </c>
+      <c r="C35" s="9">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
+        <v>6</v>
+      </c>
+      <c r="B36" s="13">
+        <f t="shared" si="0"/>
+        <v>606.16</v>
+      </c>
+      <c r="C36" s="9">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
+        <v>7</v>
+      </c>
+      <c r="B37" s="13">
+        <f t="shared" si="0"/>
+        <v>608.76</v>
+      </c>
+      <c r="C37" s="9">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="8">
+        <v>8</v>
+      </c>
+      <c r="B38" s="13">
+        <f t="shared" si="0"/>
+        <v>611.3599999999999</v>
+      </c>
+      <c r="C38" s="9">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="8">
+        <v>9</v>
+      </c>
+      <c r="B39" s="13">
+        <f t="shared" si="0"/>
+        <v>613.95999999999992</v>
+      </c>
+      <c r="C39" s="9">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="8">
+        <v>10</v>
+      </c>
+      <c r="B40" s="13">
+        <f t="shared" si="0"/>
+        <v>616.55999999999995</v>
+      </c>
+      <c r="C40" s="9">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="8">
+        <v>11</v>
+      </c>
+      <c r="B41" s="13">
+        <f t="shared" si="0"/>
+        <v>619.16</v>
+      </c>
+      <c r="C41" s="9">
+        <f t="shared" si="1"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="8">
+        <v>12</v>
+      </c>
+      <c r="B42" s="13">
+        <f t="shared" si="0"/>
+        <v>621.76</v>
+      </c>
+      <c r="C42" s="9">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="8">
+        <v>13</v>
+      </c>
+      <c r="B43" s="13">
+        <f t="shared" si="0"/>
+        <v>624.3599999999999</v>
+      </c>
+      <c r="C43" s="9">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="8">
+        <v>14</v>
+      </c>
+      <c r="B44" s="13">
+        <f t="shared" si="0"/>
+        <v>626.95999999999992</v>
+      </c>
+      <c r="C44" s="9">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="8">
+        <v>15</v>
+      </c>
+      <c r="B45" s="13">
+        <f t="shared" si="0"/>
+        <v>629.55999999999995</v>
+      </c>
+      <c r="C45" s="9">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="8">
+        <v>16</v>
+      </c>
+      <c r="B46" s="13">
+        <f t="shared" si="0"/>
+        <v>632.16</v>
+      </c>
+      <c r="C46" s="9">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="8">
+        <v>17</v>
+      </c>
+      <c r="B47" s="13">
+        <f t="shared" si="0"/>
+        <v>634.76</v>
+      </c>
+      <c r="C47" s="9">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="8">
+        <v>18</v>
+      </c>
+      <c r="B48" s="13">
+        <f t="shared" si="0"/>
+        <v>637.3599999999999</v>
+      </c>
+      <c r="C48" s="9">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="8">
+        <v>19</v>
+      </c>
+      <c r="B49" s="13">
+        <f t="shared" si="0"/>
+        <v>639.95999999999992</v>
+      </c>
+      <c r="C49" s="9">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="8">
+        <v>20</v>
+      </c>
+      <c r="B50" s="13">
+        <f t="shared" si="0"/>
+        <v>642.55999999999995</v>
+      </c>
+      <c r="C50" s="9">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="8">
+        <v>21</v>
+      </c>
+      <c r="B51" s="13">
+        <f t="shared" si="0"/>
+        <v>645.16</v>
+      </c>
+      <c r="C51" s="9">
+        <f t="shared" si="1"/>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="8">
+        <v>22</v>
+      </c>
+      <c r="B52" s="13">
+        <f t="shared" si="0"/>
+        <v>647.76</v>
+      </c>
+      <c r="C52" s="9">
+        <f t="shared" si="1"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="8">
+        <v>23</v>
+      </c>
+      <c r="B53" s="13">
+        <f t="shared" si="0"/>
+        <v>650.3599999999999</v>
+      </c>
+      <c r="C53" s="9">
+        <f t="shared" si="1"/>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="8">
+        <v>24</v>
+      </c>
+      <c r="B54" s="13">
+        <f t="shared" si="0"/>
+        <v>652.95999999999992</v>
+      </c>
+      <c r="C54" s="9">
+        <f t="shared" si="1"/>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="8">
+        <v>25</v>
+      </c>
+      <c r="B55" s="13">
+        <f t="shared" si="0"/>
+        <v>655.56</v>
+      </c>
+      <c r="C55" s="9">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="8">
+        <v>26</v>
+      </c>
+      <c r="B56" s="13">
+        <f t="shared" si="0"/>
+        <v>658.16</v>
+      </c>
+      <c r="C56" s="9">
+        <f t="shared" si="1"/>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="8">
+        <v>27</v>
+      </c>
+      <c r="B57" s="13">
+        <f t="shared" si="0"/>
+        <v>660.76</v>
+      </c>
+      <c r="C57" s="9">
+        <f t="shared" si="1"/>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="8">
+        <v>28</v>
+      </c>
+      <c r="B58" s="13">
+        <f t="shared" si="0"/>
+        <v>663.3599999999999</v>
+      </c>
+      <c r="C58" s="9">
+        <f t="shared" si="1"/>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="8">
+        <v>29</v>
+      </c>
+      <c r="B59" s="13">
+        <f t="shared" si="0"/>
+        <v>665.95999999999992</v>
+      </c>
+      <c r="C59" s="9">
+        <f t="shared" si="1"/>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="8">
+        <v>30</v>
+      </c>
+      <c r="B60" s="13">
+        <f t="shared" si="0"/>
+        <v>668.56</v>
+      </c>
+      <c r="C60" s="9">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="8">
+        <v>31</v>
+      </c>
+      <c r="B61" s="13">
+        <f t="shared" si="0"/>
+        <v>671.16</v>
+      </c>
+      <c r="C61" s="9">
+        <f t="shared" si="1"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="8">
+        <v>32</v>
+      </c>
+      <c r="B62" s="13">
+        <f t="shared" si="0"/>
+        <v>673.76</v>
+      </c>
+      <c r="C62" s="9">
+        <f t="shared" si="1"/>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="8">
+        <v>33</v>
+      </c>
+      <c r="B63" s="13">
+        <f t="shared" si="0"/>
+        <v>676.3599999999999</v>
+      </c>
+      <c r="C63" s="9">
+        <f t="shared" si="1"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="8">
+        <v>34</v>
+      </c>
+      <c r="B64" s="13">
+        <f t="shared" si="0"/>
+        <v>678.95999999999992</v>
+      </c>
+      <c r="C64" s="9">
+        <f t="shared" si="1"/>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="8">
+        <v>35</v>
+      </c>
+      <c r="B65" s="13">
+        <f t="shared" si="0"/>
+        <v>681.56</v>
+      </c>
+      <c r="C65" s="9">
+        <f t="shared" si="1"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="8">
+        <v>36</v>
+      </c>
+      <c r="B66" s="13">
+        <f t="shared" si="0"/>
+        <v>684.16</v>
+      </c>
+      <c r="C66" s="9">
+        <f t="shared" si="1"/>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="8">
+        <v>37</v>
+      </c>
+      <c r="B67" s="13">
+        <f t="shared" si="0"/>
+        <v>686.76</v>
+      </c>
+      <c r="C67" s="9">
+        <f t="shared" si="1"/>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="8">
+        <v>38</v>
+      </c>
+      <c r="B68" s="13">
+        <f t="shared" si="0"/>
+        <v>689.3599999999999</v>
+      </c>
+      <c r="C68" s="9">
+        <f t="shared" si="1"/>
+        <v>228</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="8">
+        <v>39</v>
+      </c>
+      <c r="B69" s="13">
+        <f t="shared" si="0"/>
+        <v>691.95999999999992</v>
+      </c>
+      <c r="C69" s="9">
+        <f t="shared" si="1"/>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="8">
+        <v>40</v>
+      </c>
+      <c r="B70" s="13">
+        <f t="shared" si="0"/>
+        <v>694.56</v>
+      </c>
+      <c r="C70" s="9">
+        <f t="shared" si="1"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="8">
+        <v>41</v>
+      </c>
+      <c r="B71" s="13">
+        <f t="shared" si="0"/>
+        <v>697.16</v>
+      </c>
+      <c r="C71" s="9">
+        <f t="shared" si="1"/>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="8">
+        <v>42</v>
+      </c>
+      <c r="B72" s="13">
+        <f t="shared" si="0"/>
+        <v>699.76</v>
+      </c>
+      <c r="C72" s="9">
+        <f t="shared" si="1"/>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="8">
+        <v>43</v>
+      </c>
+      <c r="B73" s="13">
+        <f t="shared" si="0"/>
+        <v>702.3599999999999</v>
+      </c>
+      <c r="C73" s="9">
+        <f t="shared" si="1"/>
+        <v>258</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="8">
+        <v>44</v>
+      </c>
+      <c r="B74" s="13">
+        <f t="shared" si="0"/>
+        <v>704.95999999999992</v>
+      </c>
+      <c r="C74" s="9">
+        <f t="shared" si="1"/>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="8">
+        <v>45</v>
+      </c>
+      <c r="B75" s="13">
+        <f t="shared" si="0"/>
+        <v>707.56</v>
+      </c>
+      <c r="C75" s="9">
+        <f t="shared" si="1"/>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="8">
+        <v>46</v>
+      </c>
+      <c r="B76" s="13">
+        <f t="shared" si="0"/>
+        <v>710.16</v>
+      </c>
+      <c r="C76" s="9">
+        <f t="shared" si="1"/>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="8">
+        <v>47</v>
+      </c>
+      <c r="B77" s="13">
+        <f t="shared" si="0"/>
+        <v>712.76</v>
+      </c>
+      <c r="C77" s="9">
+        <f t="shared" si="1"/>
+        <v>282</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="8">
+        <v>48</v>
+      </c>
+      <c r="B78" s="13">
+        <f t="shared" si="0"/>
+        <v>715.3599999999999</v>
+      </c>
+      <c r="C78" s="9">
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="8">
+        <v>49</v>
+      </c>
+      <c r="B79" s="13">
+        <f t="shared" si="0"/>
+        <v>717.95999999999992</v>
+      </c>
+      <c r="C79" s="9">
+        <f t="shared" si="1"/>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="8">
+        <v>50</v>
+      </c>
+      <c r="B80" s="13">
+        <f t="shared" si="0"/>
+        <v>720.56</v>
+      </c>
+      <c r="C80" s="9">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="8">
+        <v>51</v>
+      </c>
+      <c r="B81" s="13">
+        <f t="shared" si="0"/>
+        <v>723.16</v>
+      </c>
+      <c r="C81" s="9">
+        <f t="shared" si="1"/>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="8">
+        <v>52</v>
+      </c>
+      <c r="B82" s="13">
+        <f t="shared" si="0"/>
+        <v>725.76</v>
+      </c>
+      <c r="C82" s="9">
+        <f t="shared" si="1"/>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="8">
+        <v>53</v>
+      </c>
+      <c r="B83" s="13">
+        <f t="shared" si="0"/>
+        <v>728.3599999999999</v>
+      </c>
+      <c r="C83" s="9">
+        <f t="shared" si="1"/>
+        <v>318</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="8">
+        <v>54</v>
+      </c>
+      <c r="B84" s="13">
+        <f t="shared" si="0"/>
+        <v>730.95999999999992</v>
+      </c>
+      <c r="C84" s="9">
+        <f t="shared" si="1"/>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="8">
+        <v>55</v>
+      </c>
+      <c r="B85" s="13">
+        <f t="shared" si="0"/>
+        <v>733.56</v>
+      </c>
+      <c r="C85" s="9">
+        <f t="shared" si="1"/>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="8">
+        <v>56</v>
+      </c>
+      <c r="B86" s="13">
+        <f t="shared" si="0"/>
+        <v>736.16</v>
+      </c>
+      <c r="C86" s="9">
+        <f t="shared" si="1"/>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="8">
+        <v>57</v>
+      </c>
+      <c r="B87" s="13">
+        <f t="shared" si="0"/>
+        <v>738.76</v>
+      </c>
+      <c r="C87" s="9">
+        <f t="shared" si="1"/>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="8">
+        <v>58</v>
+      </c>
+      <c r="B88" s="13">
+        <f t="shared" si="0"/>
+        <v>741.3599999999999</v>
+      </c>
+      <c r="C88" s="9">
+        <f t="shared" si="1"/>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="8">
+        <v>59</v>
+      </c>
+      <c r="B89" s="13">
+        <f t="shared" si="0"/>
+        <v>743.95999999999992</v>
+      </c>
+      <c r="C89" s="9">
+        <f t="shared" si="1"/>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="8">
+        <v>60</v>
+      </c>
+      <c r="B90" s="13">
+        <f t="shared" si="0"/>
+        <v>746.56</v>
+      </c>
+      <c r="C90" s="9">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="8">
+        <v>61</v>
+      </c>
+      <c r="B91" s="13">
+        <f t="shared" si="0"/>
+        <v>749.16</v>
+      </c>
+      <c r="C91" s="9">
+        <f t="shared" si="1"/>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="8">
+        <v>62</v>
+      </c>
+      <c r="B92" s="13">
+        <f t="shared" si="0"/>
+        <v>751.76</v>
+      </c>
+      <c r="C92" s="9">
+        <f t="shared" si="1"/>
+        <v>372</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="8">
+        <v>63</v>
+      </c>
+      <c r="B93" s="13">
+        <f t="shared" si="0"/>
+        <v>754.3599999999999</v>
+      </c>
+      <c r="C93" s="9">
+        <f t="shared" si="1"/>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="8">
+        <v>64</v>
+      </c>
+      <c r="B94" s="13">
+        <f t="shared" si="0"/>
+        <v>756.95999999999992</v>
+      </c>
+      <c r="C94" s="9">
+        <f t="shared" si="1"/>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="8">
+        <v>65</v>
+      </c>
+      <c r="B95" s="13">
+        <f t="shared" ref="B95:B158" si="2">$B$12+$B$22*A95</f>
+        <v>759.56</v>
+      </c>
+      <c r="C95" s="9">
+        <f t="shared" ref="C95:C158" si="3">$B$25*A95</f>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="8">
+        <v>66</v>
+      </c>
+      <c r="B96" s="13">
+        <f t="shared" si="2"/>
+        <v>762.16</v>
+      </c>
+      <c r="C96" s="9">
+        <f t="shared" si="3"/>
+        <v>396</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="8">
+        <v>67</v>
+      </c>
+      <c r="B97" s="13">
+        <f t="shared" si="2"/>
+        <v>764.76</v>
+      </c>
+      <c r="C97" s="9">
+        <f t="shared" si="3"/>
+        <v>402</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="8">
+        <v>68</v>
+      </c>
+      <c r="B98" s="13">
+        <f t="shared" si="2"/>
+        <v>767.3599999999999</v>
+      </c>
+      <c r="C98" s="9">
+        <f t="shared" si="3"/>
+        <v>408</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="8">
+        <v>69</v>
+      </c>
+      <c r="B99" s="13">
+        <f t="shared" si="2"/>
+        <v>769.95999999999992</v>
+      </c>
+      <c r="C99" s="9">
+        <f t="shared" si="3"/>
+        <v>414</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="8">
+        <v>70</v>
+      </c>
+      <c r="B100" s="13">
+        <f t="shared" si="2"/>
+        <v>772.56</v>
+      </c>
+      <c r="C100" s="9">
+        <f t="shared" si="3"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="8">
+        <v>71</v>
+      </c>
+      <c r="B101" s="13">
+        <f t="shared" si="2"/>
+        <v>775.16</v>
+      </c>
+      <c r="C101" s="9">
+        <f t="shared" si="3"/>
+        <v>426</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="8">
+        <v>72</v>
+      </c>
+      <c r="B102" s="13">
+        <f t="shared" si="2"/>
+        <v>777.76</v>
+      </c>
+      <c r="C102" s="9">
+        <f t="shared" si="3"/>
+        <v>432</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="8">
+        <v>73</v>
+      </c>
+      <c r="B103" s="13">
+        <f t="shared" si="2"/>
+        <v>780.3599999999999</v>
+      </c>
+      <c r="C103" s="9">
+        <f t="shared" si="3"/>
+        <v>438</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="8">
+        <v>74</v>
+      </c>
+      <c r="B104" s="13">
+        <f t="shared" si="2"/>
+        <v>782.95999999999992</v>
+      </c>
+      <c r="C104" s="9">
+        <f t="shared" si="3"/>
+        <v>444</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="8">
+        <v>75</v>
+      </c>
+      <c r="B105" s="13">
+        <f t="shared" si="2"/>
+        <v>785.56</v>
+      </c>
+      <c r="C105" s="9">
+        <f t="shared" si="3"/>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="8">
+        <v>76</v>
+      </c>
+      <c r="B106" s="13">
+        <f t="shared" si="2"/>
+        <v>788.16</v>
+      </c>
+      <c r="C106" s="9">
+        <f t="shared" si="3"/>
+        <v>456</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="8">
+        <v>77</v>
+      </c>
+      <c r="B107" s="13">
+        <f t="shared" si="2"/>
+        <v>790.76</v>
+      </c>
+      <c r="C107" s="9">
+        <f t="shared" si="3"/>
+        <v>462</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="8">
+        <v>78</v>
+      </c>
+      <c r="B108" s="13">
+        <f t="shared" si="2"/>
+        <v>793.3599999999999</v>
+      </c>
+      <c r="C108" s="9">
+        <f t="shared" si="3"/>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="8">
+        <v>79</v>
+      </c>
+      <c r="B109" s="13">
+        <f t="shared" si="2"/>
+        <v>795.95999999999992</v>
+      </c>
+      <c r="C109" s="9">
+        <f t="shared" si="3"/>
+        <v>474</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="8">
+        <v>80</v>
+      </c>
+      <c r="B110" s="13">
+        <f t="shared" si="2"/>
+        <v>798.56</v>
+      </c>
+      <c r="C110" s="9">
+        <f t="shared" si="3"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="8">
+        <v>81</v>
+      </c>
+      <c r="B111" s="13">
+        <f t="shared" si="2"/>
+        <v>801.16</v>
+      </c>
+      <c r="C111" s="9">
+        <f t="shared" si="3"/>
+        <v>486</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="8">
+        <v>82</v>
+      </c>
+      <c r="B112" s="13">
+        <f t="shared" si="2"/>
+        <v>803.76</v>
+      </c>
+      <c r="C112" s="9">
+        <f t="shared" si="3"/>
+        <v>492</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="8">
+        <v>83</v>
+      </c>
+      <c r="B113" s="13">
+        <f t="shared" si="2"/>
+        <v>806.3599999999999</v>
+      </c>
+      <c r="C113" s="9">
+        <f t="shared" si="3"/>
+        <v>498</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="8">
+        <v>84</v>
+      </c>
+      <c r="B114" s="13">
+        <f t="shared" si="2"/>
+        <v>808.95999999999992</v>
+      </c>
+      <c r="C114" s="9">
+        <f t="shared" si="3"/>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="8">
+        <v>85</v>
+      </c>
+      <c r="B115" s="13">
+        <f t="shared" si="2"/>
+        <v>811.56</v>
+      </c>
+      <c r="C115" s="9">
+        <f t="shared" si="3"/>
+        <v>510</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="8">
+        <v>86</v>
+      </c>
+      <c r="B116" s="13">
+        <f t="shared" si="2"/>
+        <v>814.16</v>
+      </c>
+      <c r="C116" s="9">
+        <f t="shared" si="3"/>
+        <v>516</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="8">
+        <v>87</v>
+      </c>
+      <c r="B117" s="13">
+        <f t="shared" si="2"/>
+        <v>816.76</v>
+      </c>
+      <c r="C117" s="9">
+        <f t="shared" si="3"/>
+        <v>522</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="8">
+        <v>88</v>
+      </c>
+      <c r="B118" s="13">
+        <f t="shared" si="2"/>
+        <v>819.3599999999999</v>
+      </c>
+      <c r="C118" s="9">
+        <f t="shared" si="3"/>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="8">
+        <v>89</v>
+      </c>
+      <c r="B119" s="13">
+        <f t="shared" si="2"/>
+        <v>821.95999999999992</v>
+      </c>
+      <c r="C119" s="9">
+        <f t="shared" si="3"/>
+        <v>534</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="8">
+        <v>90</v>
+      </c>
+      <c r="B120" s="13">
+        <f t="shared" si="2"/>
+        <v>824.56</v>
+      </c>
+      <c r="C120" s="9">
+        <f t="shared" si="3"/>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="8">
+        <v>91</v>
+      </c>
+      <c r="B121" s="13">
+        <f t="shared" si="2"/>
+        <v>827.16</v>
+      </c>
+      <c r="C121" s="9">
+        <f t="shared" si="3"/>
+        <v>546</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="8">
+        <v>92</v>
+      </c>
+      <c r="B122" s="13">
+        <f t="shared" si="2"/>
+        <v>829.76</v>
+      </c>
+      <c r="C122" s="9">
+        <f t="shared" si="3"/>
+        <v>552</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="8">
+        <v>93</v>
+      </c>
+      <c r="B123" s="13">
+        <f t="shared" si="2"/>
+        <v>832.3599999999999</v>
+      </c>
+      <c r="C123" s="9">
+        <f t="shared" si="3"/>
+        <v>558</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="8">
+        <v>94</v>
+      </c>
+      <c r="B124" s="13">
+        <f t="shared" si="2"/>
+        <v>834.95999999999992</v>
+      </c>
+      <c r="C124" s="9">
+        <f t="shared" si="3"/>
+        <v>564</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="8">
+        <v>95</v>
+      </c>
+      <c r="B125" s="13">
+        <f t="shared" si="2"/>
+        <v>837.56</v>
+      </c>
+      <c r="C125" s="9">
+        <f t="shared" si="3"/>
+        <v>570</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="8">
+        <v>96</v>
+      </c>
+      <c r="B126" s="13">
+        <f t="shared" si="2"/>
+        <v>840.16</v>
+      </c>
+      <c r="C126" s="9">
+        <f t="shared" si="3"/>
+        <v>576</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="8">
+        <v>97</v>
+      </c>
+      <c r="B127" s="13">
+        <f t="shared" si="2"/>
+        <v>842.76</v>
+      </c>
+      <c r="C127" s="9">
+        <f t="shared" si="3"/>
+        <v>582</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="8">
+        <v>98</v>
+      </c>
+      <c r="B128" s="13">
+        <f t="shared" si="2"/>
+        <v>845.3599999999999</v>
+      </c>
+      <c r="C128" s="9">
+        <f t="shared" si="3"/>
+        <v>588</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="8">
+        <v>99</v>
+      </c>
+      <c r="B129" s="13">
+        <f t="shared" si="2"/>
+        <v>847.96</v>
+      </c>
+      <c r="C129" s="9">
+        <f t="shared" si="3"/>
+        <v>594</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="8">
+        <v>100</v>
+      </c>
+      <c r="B130" s="13">
+        <f t="shared" si="2"/>
+        <v>850.56</v>
+      </c>
+      <c r="C130" s="9">
+        <f t="shared" si="3"/>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="15">
+        <v>101</v>
+      </c>
+      <c r="B131" s="16">
+        <f t="shared" si="2"/>
+        <v>853.16</v>
+      </c>
+      <c r="C131" s="17">
+        <f t="shared" si="3"/>
+        <v>606</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="8">
+        <v>102</v>
+      </c>
+      <c r="B132" s="13">
+        <f t="shared" si="2"/>
+        <v>855.76</v>
+      </c>
+      <c r="C132" s="9">
+        <f t="shared" si="3"/>
+        <v>612</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="8">
+        <v>103</v>
+      </c>
+      <c r="B133" s="13">
+        <f t="shared" si="2"/>
+        <v>858.3599999999999</v>
+      </c>
+      <c r="C133" s="9">
+        <f t="shared" si="3"/>
+        <v>618</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="8">
+        <v>104</v>
+      </c>
+      <c r="B134" s="13">
+        <f t="shared" si="2"/>
+        <v>860.96</v>
+      </c>
+      <c r="C134" s="9">
+        <f t="shared" si="3"/>
+        <v>624</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="8">
+        <v>105</v>
+      </c>
+      <c r="B135" s="13">
+        <f t="shared" si="2"/>
+        <v>863.56</v>
+      </c>
+      <c r="C135" s="9">
+        <f t="shared" si="3"/>
+        <v>630</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="8">
+        <v>106</v>
+      </c>
+      <c r="B136" s="13">
+        <f t="shared" si="2"/>
+        <v>866.16</v>
+      </c>
+      <c r="C136" s="9">
+        <f t="shared" si="3"/>
+        <v>636</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="8">
+        <v>107</v>
+      </c>
+      <c r="B137" s="13">
+        <f t="shared" si="2"/>
+        <v>868.76</v>
+      </c>
+      <c r="C137" s="9">
+        <f t="shared" si="3"/>
+        <v>642</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="8">
+        <v>108</v>
+      </c>
+      <c r="B138" s="13">
+        <f t="shared" si="2"/>
+        <v>871.3599999999999</v>
+      </c>
+      <c r="C138" s="9">
+        <f t="shared" si="3"/>
+        <v>648</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="8">
+        <v>109</v>
+      </c>
+      <c r="B139" s="13">
+        <f t="shared" si="2"/>
+        <v>873.96</v>
+      </c>
+      <c r="C139" s="9">
+        <f t="shared" si="3"/>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="8">
+        <v>110</v>
+      </c>
+      <c r="B140" s="13">
+        <f t="shared" si="2"/>
+        <v>876.56</v>
+      </c>
+      <c r="C140" s="9">
+        <f t="shared" si="3"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="8">
+        <v>111</v>
+      </c>
+      <c r="B141" s="13">
+        <f t="shared" si="2"/>
+        <v>879.16</v>
+      </c>
+      <c r="C141" s="9">
+        <f t="shared" si="3"/>
+        <v>666</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="8">
+        <v>112</v>
+      </c>
+      <c r="B142" s="13">
+        <f t="shared" si="2"/>
+        <v>881.76</v>
+      </c>
+      <c r="C142" s="9">
+        <f t="shared" si="3"/>
+        <v>672</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="8">
+        <v>113</v>
+      </c>
+      <c r="B143" s="13">
+        <f t="shared" si="2"/>
+        <v>884.3599999999999</v>
+      </c>
+      <c r="C143" s="9">
+        <f t="shared" si="3"/>
+        <v>678</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="8">
+        <v>114</v>
+      </c>
+      <c r="B144" s="13">
+        <f t="shared" si="2"/>
+        <v>886.96</v>
+      </c>
+      <c r="C144" s="9">
+        <f t="shared" si="3"/>
+        <v>684</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="8">
+        <v>115</v>
+      </c>
+      <c r="B145" s="13">
+        <f t="shared" si="2"/>
+        <v>889.56</v>
+      </c>
+      <c r="C145" s="9">
+        <f t="shared" si="3"/>
+        <v>690</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="8">
+        <v>116</v>
+      </c>
+      <c r="B146" s="13">
+        <f t="shared" si="2"/>
+        <v>892.16</v>
+      </c>
+      <c r="C146" s="9">
+        <f t="shared" si="3"/>
+        <v>696</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="8">
+        <v>117</v>
+      </c>
+      <c r="B147" s="13">
+        <f t="shared" si="2"/>
+        <v>894.76</v>
+      </c>
+      <c r="C147" s="9">
+        <f t="shared" si="3"/>
+        <v>702</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="8">
+        <v>118</v>
+      </c>
+      <c r="B148" s="13">
+        <f t="shared" si="2"/>
+        <v>897.3599999999999</v>
+      </c>
+      <c r="C148" s="9">
+        <f t="shared" si="3"/>
+        <v>708</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="8">
+        <v>119</v>
+      </c>
+      <c r="B149" s="13">
+        <f t="shared" si="2"/>
+        <v>899.96</v>
+      </c>
+      <c r="C149" s="9">
+        <f t="shared" si="3"/>
+        <v>714</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="8">
+        <v>120</v>
+      </c>
+      <c r="B150" s="13">
+        <f t="shared" si="2"/>
+        <v>902.56</v>
+      </c>
+      <c r="C150" s="9">
+        <f t="shared" si="3"/>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="8">
+        <v>121</v>
+      </c>
+      <c r="B151" s="13">
+        <f t="shared" si="2"/>
+        <v>905.16</v>
+      </c>
+      <c r="C151" s="9">
+        <f t="shared" si="3"/>
+        <v>726</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="8">
+        <v>122</v>
+      </c>
+      <c r="B152" s="13">
+        <f t="shared" si="2"/>
+        <v>907.76</v>
+      </c>
+      <c r="C152" s="9">
+        <f t="shared" si="3"/>
+        <v>732</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="8">
+        <v>123</v>
+      </c>
+      <c r="B153" s="13">
+        <f t="shared" si="2"/>
+        <v>910.3599999999999</v>
+      </c>
+      <c r="C153" s="9">
+        <f t="shared" si="3"/>
+        <v>738</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="8">
+        <v>124</v>
+      </c>
+      <c r="B154" s="13">
+        <f t="shared" si="2"/>
+        <v>912.96</v>
+      </c>
+      <c r="C154" s="9">
+        <f t="shared" si="3"/>
+        <v>744</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="8">
+        <v>125</v>
+      </c>
+      <c r="B155" s="13">
+        <f t="shared" si="2"/>
+        <v>915.56</v>
+      </c>
+      <c r="C155" s="9">
+        <f t="shared" si="3"/>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="8">
+        <v>126</v>
+      </c>
+      <c r="B156" s="13">
+        <f t="shared" si="2"/>
+        <v>918.16</v>
+      </c>
+      <c r="C156" s="9">
+        <f t="shared" si="3"/>
+        <v>756</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="8">
+        <v>127</v>
+      </c>
+      <c r="B157" s="13">
+        <f t="shared" si="2"/>
+        <v>920.76</v>
+      </c>
+      <c r="C157" s="9">
+        <f t="shared" si="3"/>
+        <v>762</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="8">
+        <v>128</v>
+      </c>
+      <c r="B158" s="13">
+        <f t="shared" si="2"/>
+        <v>923.3599999999999</v>
+      </c>
+      <c r="C158" s="9">
+        <f t="shared" si="3"/>
+        <v>768</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="8">
+        <v>129</v>
+      </c>
+      <c r="B159" s="13">
+        <f t="shared" ref="B159:B222" si="4">$B$12+$B$22*A159</f>
+        <v>925.96</v>
+      </c>
+      <c r="C159" s="9">
+        <f t="shared" ref="C159:C222" si="5">$B$25*A159</f>
+        <v>774</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="8">
+        <v>130</v>
+      </c>
+      <c r="B160" s="13">
+        <f t="shared" si="4"/>
+        <v>928.56</v>
+      </c>
+      <c r="C160" s="9">
+        <f t="shared" si="5"/>
+        <v>780</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="8">
+        <v>131</v>
+      </c>
+      <c r="B161" s="13">
+        <f t="shared" si="4"/>
+        <v>931.16</v>
+      </c>
+      <c r="C161" s="9">
+        <f t="shared" si="5"/>
+        <v>786</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="8">
+        <v>132</v>
+      </c>
+      <c r="B162" s="13">
+        <f t="shared" si="4"/>
+        <v>933.76</v>
+      </c>
+      <c r="C162" s="9">
+        <f t="shared" si="5"/>
+        <v>792</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="8">
+        <v>133</v>
+      </c>
+      <c r="B163" s="13">
+        <f t="shared" si="4"/>
+        <v>936.3599999999999</v>
+      </c>
+      <c r="C163" s="9">
+        <f t="shared" si="5"/>
+        <v>798</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="8">
+        <v>134</v>
+      </c>
+      <c r="B164" s="13">
+        <f t="shared" si="4"/>
+        <v>938.96</v>
+      </c>
+      <c r="C164" s="9">
+        <f t="shared" si="5"/>
+        <v>804</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="8">
+        <v>135</v>
+      </c>
+      <c r="B165" s="13">
+        <f t="shared" si="4"/>
+        <v>941.56</v>
+      </c>
+      <c r="C165" s="9">
+        <f t="shared" si="5"/>
+        <v>810</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="8">
+        <v>136</v>
+      </c>
+      <c r="B166" s="13">
+        <f t="shared" si="4"/>
+        <v>944.16</v>
+      </c>
+      <c r="C166" s="9">
+        <f t="shared" si="5"/>
+        <v>816</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="8">
+        <v>137</v>
+      </c>
+      <c r="B167" s="13">
+        <f t="shared" si="4"/>
+        <v>946.76</v>
+      </c>
+      <c r="C167" s="9">
+        <f t="shared" si="5"/>
+        <v>822</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="8">
+        <v>138</v>
+      </c>
+      <c r="B168" s="13">
+        <f t="shared" si="4"/>
+        <v>949.3599999999999</v>
+      </c>
+      <c r="C168" s="9">
+        <f t="shared" si="5"/>
+        <v>828</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="8">
+        <v>139</v>
+      </c>
+      <c r="B169" s="13">
+        <f t="shared" si="4"/>
+        <v>951.96</v>
+      </c>
+      <c r="C169" s="9">
+        <f t="shared" si="5"/>
+        <v>834</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="8">
+        <v>140</v>
+      </c>
+      <c r="B170" s="13">
+        <f t="shared" si="4"/>
+        <v>954.56</v>
+      </c>
+      <c r="C170" s="9">
+        <f t="shared" si="5"/>
+        <v>840</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="8">
+        <v>141</v>
+      </c>
+      <c r="B171" s="13">
+        <f t="shared" si="4"/>
+        <v>957.16</v>
+      </c>
+      <c r="C171" s="9">
+        <f t="shared" si="5"/>
+        <v>846</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="8">
+        <v>142</v>
+      </c>
+      <c r="B172" s="13">
+        <f t="shared" si="4"/>
+        <v>959.76</v>
+      </c>
+      <c r="C172" s="9">
+        <f t="shared" si="5"/>
+        <v>852</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="8">
+        <v>143</v>
+      </c>
+      <c r="B173" s="13">
+        <f t="shared" si="4"/>
+        <v>962.3599999999999</v>
+      </c>
+      <c r="C173" s="9">
+        <f t="shared" si="5"/>
+        <v>858</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="8">
+        <v>144</v>
+      </c>
+      <c r="B174" s="13">
+        <f t="shared" si="4"/>
+        <v>964.96</v>
+      </c>
+      <c r="C174" s="9">
+        <f t="shared" si="5"/>
+        <v>864</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="8">
+        <v>145</v>
+      </c>
+      <c r="B175" s="13">
+        <f t="shared" si="4"/>
+        <v>967.56</v>
+      </c>
+      <c r="C175" s="9">
+        <f t="shared" si="5"/>
+        <v>870</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="8">
+        <v>146</v>
+      </c>
+      <c r="B176" s="13">
+        <f t="shared" si="4"/>
+        <v>970.16</v>
+      </c>
+      <c r="C176" s="9">
+        <f t="shared" si="5"/>
+        <v>876</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="8">
+        <v>147</v>
+      </c>
+      <c r="B177" s="13">
+        <f t="shared" si="4"/>
+        <v>972.76</v>
+      </c>
+      <c r="C177" s="9">
+        <f t="shared" si="5"/>
+        <v>882</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="8">
+        <v>148</v>
+      </c>
+      <c r="B178" s="13">
+        <f t="shared" si="4"/>
+        <v>975.3599999999999</v>
+      </c>
+      <c r="C178" s="9">
+        <f t="shared" si="5"/>
+        <v>888</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="8">
+        <v>149</v>
+      </c>
+      <c r="B179" s="13">
+        <f t="shared" si="4"/>
+        <v>977.96</v>
+      </c>
+      <c r="C179" s="9">
+        <f t="shared" si="5"/>
+        <v>894</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="8">
+        <v>150</v>
+      </c>
+      <c r="B180" s="13">
+        <f t="shared" si="4"/>
+        <v>980.56</v>
+      </c>
+      <c r="C180" s="9">
+        <f t="shared" si="5"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="8">
+        <v>151</v>
+      </c>
+      <c r="B181" s="13">
+        <f t="shared" si="4"/>
+        <v>983.16</v>
+      </c>
+      <c r="C181" s="9">
+        <f t="shared" si="5"/>
+        <v>906</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="8">
+        <v>152</v>
+      </c>
+      <c r="B182" s="13">
+        <f t="shared" si="4"/>
+        <v>985.76</v>
+      </c>
+      <c r="C182" s="9">
+        <f t="shared" si="5"/>
+        <v>912</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="8">
+        <v>153</v>
+      </c>
+      <c r="B183" s="13">
+        <f t="shared" si="4"/>
+        <v>988.3599999999999</v>
+      </c>
+      <c r="C183" s="9">
+        <f t="shared" si="5"/>
+        <v>918</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="8">
+        <v>154</v>
+      </c>
+      <c r="B184" s="13">
+        <f t="shared" si="4"/>
+        <v>990.96</v>
+      </c>
+      <c r="C184" s="9">
+        <f t="shared" si="5"/>
+        <v>924</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="8">
+        <v>155</v>
+      </c>
+      <c r="B185" s="13">
+        <f t="shared" si="4"/>
+        <v>993.56</v>
+      </c>
+      <c r="C185" s="9">
+        <f t="shared" si="5"/>
+        <v>930</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="8">
+        <v>156</v>
+      </c>
+      <c r="B186" s="13">
+        <f t="shared" si="4"/>
+        <v>996.16</v>
+      </c>
+      <c r="C186" s="9">
+        <f t="shared" si="5"/>
+        <v>936</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="8">
+        <v>157</v>
+      </c>
+      <c r="B187" s="13">
+        <f t="shared" si="4"/>
+        <v>998.76</v>
+      </c>
+      <c r="C187" s="9">
+        <f t="shared" si="5"/>
+        <v>942</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="8">
+        <v>158</v>
+      </c>
+      <c r="B188" s="13">
+        <f t="shared" si="4"/>
+        <v>1001.3599999999999</v>
+      </c>
+      <c r="C188" s="9">
+        <f t="shared" si="5"/>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="8">
+        <v>159</v>
+      </c>
+      <c r="B189" s="13">
+        <f t="shared" si="4"/>
+        <v>1003.96</v>
+      </c>
+      <c r="C189" s="9">
+        <f t="shared" si="5"/>
+        <v>954</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="8">
+        <v>160</v>
+      </c>
+      <c r="B190" s="13">
+        <f t="shared" si="4"/>
+        <v>1006.56</v>
+      </c>
+      <c r="C190" s="9">
+        <f t="shared" si="5"/>
+        <v>960</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="8">
+        <v>161</v>
+      </c>
+      <c r="B191" s="13">
+        <f t="shared" si="4"/>
+        <v>1009.16</v>
+      </c>
+      <c r="C191" s="9">
+        <f t="shared" si="5"/>
+        <v>966</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="8">
+        <v>162</v>
+      </c>
+      <c r="B192" s="13">
+        <f t="shared" si="4"/>
+        <v>1011.76</v>
+      </c>
+      <c r="C192" s="9">
+        <f t="shared" si="5"/>
+        <v>972</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="8">
+        <v>163</v>
+      </c>
+      <c r="B193" s="13">
+        <f t="shared" si="4"/>
+        <v>1014.3599999999999</v>
+      </c>
+      <c r="C193" s="9">
+        <f t="shared" si="5"/>
+        <v>978</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="8">
+        <v>164</v>
+      </c>
+      <c r="B194" s="13">
+        <f t="shared" si="4"/>
+        <v>1016.96</v>
+      </c>
+      <c r="C194" s="9">
+        <f t="shared" si="5"/>
+        <v>984</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="8">
+        <v>165</v>
+      </c>
+      <c r="B195" s="13">
+        <f t="shared" si="4"/>
+        <v>1019.56</v>
+      </c>
+      <c r="C195" s="9">
+        <f t="shared" si="5"/>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="8">
+        <v>166</v>
+      </c>
+      <c r="B196" s="13">
+        <f t="shared" si="4"/>
+        <v>1022.16</v>
+      </c>
+      <c r="C196" s="9">
+        <f t="shared" si="5"/>
+        <v>996</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="8">
+        <v>167</v>
+      </c>
+      <c r="B197" s="13">
+        <f t="shared" si="4"/>
+        <v>1024.76</v>
+      </c>
+      <c r="C197" s="9">
+        <f t="shared" si="5"/>
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="8">
+        <v>168</v>
+      </c>
+      <c r="B198" s="13">
+        <f t="shared" si="4"/>
+        <v>1027.3599999999999</v>
+      </c>
+      <c r="C198" s="9">
+        <f t="shared" si="5"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="8">
+        <v>169</v>
+      </c>
+      <c r="B199" s="13">
+        <f t="shared" si="4"/>
+        <v>1029.96</v>
+      </c>
+      <c r="C199" s="9">
+        <f t="shared" si="5"/>
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="8">
+        <v>170</v>
+      </c>
+      <c r="B200" s="13">
+        <f t="shared" si="4"/>
+        <v>1032.56</v>
+      </c>
+      <c r="C200" s="9">
+        <f t="shared" si="5"/>
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="8">
+        <v>171</v>
+      </c>
+      <c r="B201" s="13">
+        <f t="shared" si="4"/>
+        <v>1035.1599999999999</v>
+      </c>
+      <c r="C201" s="9">
+        <f t="shared" si="5"/>
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="8">
+        <v>172</v>
+      </c>
+      <c r="B202" s="13">
+        <f t="shared" si="4"/>
+        <v>1037.76</v>
+      </c>
+      <c r="C202" s="9">
+        <f t="shared" si="5"/>
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="8">
+        <v>173</v>
+      </c>
+      <c r="B203" s="13">
+        <f t="shared" si="4"/>
+        <v>1040.3599999999999</v>
+      </c>
+      <c r="C203" s="9">
+        <f t="shared" si="5"/>
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="8">
+        <v>174</v>
+      </c>
+      <c r="B204" s="13">
+        <f t="shared" si="4"/>
+        <v>1042.96</v>
+      </c>
+      <c r="C204" s="9">
+        <f t="shared" si="5"/>
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="8">
+        <v>175</v>
+      </c>
+      <c r="B205" s="13">
+        <f t="shared" si="4"/>
+        <v>1045.56</v>
+      </c>
+      <c r="C205" s="9">
+        <f t="shared" si="5"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="8">
+        <v>176</v>
+      </c>
+      <c r="B206" s="13">
+        <f t="shared" si="4"/>
+        <v>1048.1599999999999</v>
+      </c>
+      <c r="C206" s="9">
+        <f t="shared" si="5"/>
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="8">
+        <v>177</v>
+      </c>
+      <c r="B207" s="13">
+        <f t="shared" si="4"/>
+        <v>1050.76</v>
+      </c>
+      <c r="C207" s="9">
+        <f t="shared" si="5"/>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="8">
+        <v>178</v>
+      </c>
+      <c r="B208" s="13">
+        <f t="shared" si="4"/>
+        <v>1053.3599999999999</v>
+      </c>
+      <c r="C208" s="9">
+        <f t="shared" si="5"/>
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="8">
+        <v>179</v>
+      </c>
+      <c r="B209" s="13">
+        <f t="shared" si="4"/>
+        <v>1055.96</v>
+      </c>
+      <c r="C209" s="9">
+        <f t="shared" si="5"/>
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="8">
+        <v>180</v>
+      </c>
+      <c r="B210" s="13">
+        <f t="shared" si="4"/>
+        <v>1058.56</v>
+      </c>
+      <c r="C210" s="9">
+        <f t="shared" si="5"/>
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="8">
+        <v>181</v>
+      </c>
+      <c r="B211" s="13">
+        <f t="shared" si="4"/>
+        <v>1061.1599999999999</v>
+      </c>
+      <c r="C211" s="9">
+        <f t="shared" si="5"/>
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="8">
+        <v>182</v>
+      </c>
+      <c r="B212" s="13">
+        <f t="shared" si="4"/>
+        <v>1063.76</v>
+      </c>
+      <c r="C212" s="9">
+        <f t="shared" si="5"/>
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="8">
+        <v>183</v>
+      </c>
+      <c r="B213" s="13">
+        <f t="shared" si="4"/>
+        <v>1066.3599999999999</v>
+      </c>
+      <c r="C213" s="9">
+        <f t="shared" si="5"/>
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="8">
+        <v>184</v>
+      </c>
+      <c r="B214" s="13">
+        <f t="shared" si="4"/>
+        <v>1068.96</v>
+      </c>
+      <c r="C214" s="9">
+        <f t="shared" si="5"/>
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="8">
+        <v>185</v>
+      </c>
+      <c r="B215" s="13">
+        <f t="shared" si="4"/>
+        <v>1071.56</v>
+      </c>
+      <c r="C215" s="9">
+        <f t="shared" si="5"/>
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="8">
+        <v>186</v>
+      </c>
+      <c r="B216" s="13">
+        <f t="shared" si="4"/>
+        <v>1074.1599999999999</v>
+      </c>
+      <c r="C216" s="9">
+        <f t="shared" si="5"/>
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="8">
+        <v>187</v>
+      </c>
+      <c r="B217" s="13">
+        <f t="shared" si="4"/>
+        <v>1076.76</v>
+      </c>
+      <c r="C217" s="9">
+        <f t="shared" si="5"/>
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="8">
+        <v>188</v>
+      </c>
+      <c r="B218" s="13">
+        <f t="shared" si="4"/>
+        <v>1079.3599999999999</v>
+      </c>
+      <c r="C218" s="9">
+        <f t="shared" si="5"/>
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="8">
+        <v>189</v>
+      </c>
+      <c r="B219" s="13">
+        <f t="shared" si="4"/>
+        <v>1081.96</v>
+      </c>
+      <c r="C219" s="9">
+        <f t="shared" si="5"/>
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="8">
+        <v>190</v>
+      </c>
+      <c r="B220" s="13">
+        <f t="shared" si="4"/>
+        <v>1084.56</v>
+      </c>
+      <c r="C220" s="9">
+        <f t="shared" si="5"/>
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="8">
+        <v>191</v>
+      </c>
+      <c r="B221" s="13">
+        <f t="shared" si="4"/>
+        <v>1087.1599999999999</v>
+      </c>
+      <c r="C221" s="9">
+        <f t="shared" si="5"/>
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="8">
+        <v>192</v>
+      </c>
+      <c r="B222" s="13">
+        <f t="shared" si="4"/>
+        <v>1089.76</v>
+      </c>
+      <c r="C222" s="9">
+        <f t="shared" si="5"/>
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="8">
+        <v>193</v>
+      </c>
+      <c r="B223" s="13">
+        <f t="shared" ref="B223:B230" si="6">$B$12+$B$22*A223</f>
+        <v>1092.3599999999999</v>
+      </c>
+      <c r="C223" s="9">
+        <f t="shared" ref="C223:C230" si="7">$B$25*A223</f>
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="8">
+        <v>194</v>
+      </c>
+      <c r="B224" s="13">
+        <f t="shared" si="6"/>
+        <v>1094.96</v>
+      </c>
+      <c r="C224" s="9">
+        <f t="shared" si="7"/>
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="8">
+        <v>195</v>
+      </c>
+      <c r="B225" s="13">
+        <f t="shared" si="6"/>
+        <v>1097.56</v>
+      </c>
+      <c r="C225" s="9">
+        <f t="shared" si="7"/>
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="8">
+        <v>196</v>
+      </c>
+      <c r="B226" s="13">
+        <f t="shared" si="6"/>
+        <v>1100.1599999999999</v>
+      </c>
+      <c r="C226" s="9">
+        <f t="shared" si="7"/>
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="8">
+        <v>197</v>
+      </c>
+      <c r="B227" s="13">
+        <f t="shared" si="6"/>
+        <v>1102.76</v>
+      </c>
+      <c r="C227" s="9">
+        <f t="shared" si="7"/>
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="8">
+        <v>198</v>
+      </c>
+      <c r="B228" s="13">
+        <f t="shared" si="6"/>
+        <v>1105.3600000000001</v>
+      </c>
+      <c r="C228" s="9">
+        <f t="shared" si="7"/>
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="8">
+        <v>199</v>
+      </c>
+      <c r="B229" s="13">
+        <f t="shared" si="6"/>
+        <v>1107.96</v>
+      </c>
+      <c r="C229" s="9">
+        <f t="shared" si="7"/>
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="8">
+        <v>200</v>
+      </c>
+      <c r="B230" s="13">
+        <f t="shared" si="6"/>
+        <v>1110.56</v>
+      </c>
+      <c r="C230" s="9">
+        <f t="shared" si="7"/>
+        <v>1200</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A16:B16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008C371D7D644B574CA89B5F00ED09B0C8" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="bd33285d5daf4dee329ae000bb583124">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5cfc5781-36c7-40ed-af62-43a27290b458" xmlns:ns4="c4b568bc-dd8a-4a74-b92a-f01b2ee1149b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6974282011ce0aef1ed393e1233ba8cc" ns3:_="" ns4:_="">
     <xsd:import namespace="5cfc5781-36c7-40ed-af62-43a27290b458"/>
@@ -18035,32 +24481,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4FBB6FF-EC5C-4DA6-BDE2-BFD391C0AAC1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="5cfc5781-36c7-40ed-af62-43a27290b458"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="c4b568bc-dd8a-4a74-b92a-f01b2ee1149b"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5725DCE3-03BC-44D7-BC9C-71C7B5BFC1A0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5cfc5781-36c7-40ed-af62-43a27290b458" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7417AF40-C3B2-4E1A-88EB-AB01B9312A09}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18077,4 +24515,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5725DCE3-03BC-44D7-BC9C-71C7B5BFC1A0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4FBB6FF-EC5C-4DA6-BDE2-BFD391C0AAC1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="5cfc5781-36c7-40ed-af62-43a27290b458"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c4b568bc-dd8a-4a74-b92a-f01b2ee1149b"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/utilities/Punto_de_equilibrio.xlsx
+++ b/utilities/Punto_de_equilibrio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MaBel\utilities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF1841D-A08D-4DCA-8C92-B6B39C5FCB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3989692-B04A-4C88-94B9-19CA18023229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="3" xr2:uid="{E75E3C13-AC3D-4914-9135-F849659ACBFB}"/>
   </bookViews>
@@ -22281,14 +22281,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>685799</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>127226</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>247649</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>103414</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -31576,7 +31576,7 @@
         <v>0</v>
       </c>
       <c r="B28" s="13">
-        <f>$B$11+$B$20*A28</f>
+        <f t="shared" ref="B28:B91" si="0">$B$11+$B$20*A28</f>
         <v>1390</v>
       </c>
       <c r="C28" s="9">
@@ -31589,11 +31589,11 @@
         <v>1</v>
       </c>
       <c r="B29" s="13">
-        <f>$B$11+$B$20*A29</f>
+        <f t="shared" si="0"/>
         <v>1430</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:C92" si="0">$B$23*A29</f>
+        <f t="shared" ref="C29:C92" si="1">$B$23*A29</f>
         <v>100</v>
       </c>
     </row>
@@ -31602,11 +31602,11 @@
         <v>2</v>
       </c>
       <c r="B30" s="13">
-        <f>$B$11+$B$20*A30</f>
+        <f t="shared" si="0"/>
         <v>1470</v>
       </c>
       <c r="C30" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
     </row>
@@ -31615,11 +31615,11 @@
         <v>3</v>
       </c>
       <c r="B31" s="13">
-        <f>$B$11+$B$20*A31</f>
+        <f t="shared" si="0"/>
         <v>1510</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
@@ -31628,11 +31628,11 @@
         <v>4</v>
       </c>
       <c r="B32" s="13">
-        <f>$B$11+$B$20*A32</f>
+        <f t="shared" si="0"/>
         <v>1550</v>
       </c>
       <c r="C32" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>400</v>
       </c>
     </row>
@@ -31641,11 +31641,11 @@
         <v>5</v>
       </c>
       <c r="B33" s="13">
-        <f>$B$11+$B$20*A33</f>
+        <f t="shared" si="0"/>
         <v>1590</v>
       </c>
       <c r="C33" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
     </row>
@@ -31654,11 +31654,11 @@
         <v>6</v>
       </c>
       <c r="B34" s="13">
-        <f>$B$11+$B$20*A34</f>
+        <f t="shared" si="0"/>
         <v>1630</v>
       </c>
       <c r="C34" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>600</v>
       </c>
     </row>
@@ -31667,11 +31667,11 @@
         <v>7</v>
       </c>
       <c r="B35" s="13">
-        <f>$B$11+$B$20*A35</f>
+        <f t="shared" si="0"/>
         <v>1670</v>
       </c>
       <c r="C35" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>700</v>
       </c>
     </row>
@@ -31680,11 +31680,11 @@
         <v>8</v>
       </c>
       <c r="B36" s="13">
-        <f>$B$11+$B$20*A36</f>
+        <f t="shared" si="0"/>
         <v>1710</v>
       </c>
       <c r="C36" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>800</v>
       </c>
     </row>
@@ -31693,11 +31693,11 @@
         <v>9</v>
       </c>
       <c r="B37" s="13">
-        <f>$B$11+$B$20*A37</f>
+        <f t="shared" si="0"/>
         <v>1750</v>
       </c>
       <c r="C37" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>900</v>
       </c>
     </row>
@@ -31706,11 +31706,11 @@
         <v>10</v>
       </c>
       <c r="B38" s="13">
-        <f>$B$11+$B$20*A38</f>
+        <f t="shared" si="0"/>
         <v>1790</v>
       </c>
       <c r="C38" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
     </row>
@@ -31719,11 +31719,11 @@
         <v>11</v>
       </c>
       <c r="B39" s="13">
-        <f>$B$11+$B$20*A39</f>
+        <f t="shared" si="0"/>
         <v>1830</v>
       </c>
       <c r="C39" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1100</v>
       </c>
     </row>
@@ -31732,11 +31732,11 @@
         <v>12</v>
       </c>
       <c r="B40" s="13">
-        <f>$B$11+$B$20*A40</f>
+        <f t="shared" si="0"/>
         <v>1870</v>
       </c>
       <c r="C40" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1200</v>
       </c>
     </row>
@@ -31745,11 +31745,11 @@
         <v>13</v>
       </c>
       <c r="B41" s="13">
-        <f>$B$11+$B$20*A41</f>
+        <f t="shared" si="0"/>
         <v>1910</v>
       </c>
       <c r="C41" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1300</v>
       </c>
     </row>
@@ -31758,11 +31758,11 @@
         <v>14</v>
       </c>
       <c r="B42" s="13">
-        <f>$B$11+$B$20*A42</f>
+        <f t="shared" si="0"/>
         <v>1950</v>
       </c>
       <c r="C42" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1400</v>
       </c>
     </row>
@@ -31771,11 +31771,11 @@
         <v>15</v>
       </c>
       <c r="B43" s="13">
-        <f>$B$11+$B$20*A43</f>
+        <f t="shared" si="0"/>
         <v>1990</v>
       </c>
       <c r="C43" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1500</v>
       </c>
     </row>
@@ -31784,11 +31784,11 @@
         <v>16</v>
       </c>
       <c r="B44" s="13">
-        <f>$B$11+$B$20*A44</f>
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="C44" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1600</v>
       </c>
     </row>
@@ -31797,11 +31797,11 @@
         <v>17</v>
       </c>
       <c r="B45" s="13">
-        <f>$B$11+$B$20*A45</f>
+        <f t="shared" si="0"/>
         <v>2070</v>
       </c>
       <c r="C45" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1700</v>
       </c>
     </row>
@@ -31810,11 +31810,11 @@
         <v>18</v>
       </c>
       <c r="B46" s="13">
-        <f>$B$11+$B$20*A46</f>
+        <f t="shared" si="0"/>
         <v>2110</v>
       </c>
       <c r="C46" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1800</v>
       </c>
     </row>
@@ -31823,11 +31823,11 @@
         <v>19</v>
       </c>
       <c r="B47" s="13">
-        <f>$B$11+$B$20*A47</f>
+        <f t="shared" si="0"/>
         <v>2150</v>
       </c>
       <c r="C47" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1900</v>
       </c>
     </row>
@@ -31836,11 +31836,11 @@
         <v>20</v>
       </c>
       <c r="B48" s="13">
-        <f>$B$11+$B$20*A48</f>
+        <f t="shared" si="0"/>
         <v>2190</v>
       </c>
       <c r="C48" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2000</v>
       </c>
     </row>
@@ -31849,11 +31849,11 @@
         <v>21</v>
       </c>
       <c r="B49" s="13">
-        <f>$B$11+$B$20*A49</f>
+        <f t="shared" si="0"/>
         <v>2230</v>
       </c>
       <c r="C49" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2100</v>
       </c>
     </row>
@@ -31862,11 +31862,11 @@
         <v>22</v>
       </c>
       <c r="B50" s="13">
-        <f>$B$11+$B$20*A50</f>
+        <f t="shared" si="0"/>
         <v>2270</v>
       </c>
       <c r="C50" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2200</v>
       </c>
     </row>
@@ -31875,11 +31875,11 @@
         <v>23</v>
       </c>
       <c r="B51" s="13">
-        <f>$B$11+$B$20*A51</f>
+        <f t="shared" si="0"/>
         <v>2310</v>
       </c>
       <c r="C51" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2300</v>
       </c>
     </row>
@@ -31888,11 +31888,11 @@
         <v>24</v>
       </c>
       <c r="B52" s="13">
-        <f>$B$11+$B$20*A52</f>
+        <f t="shared" si="0"/>
         <v>2350</v>
       </c>
       <c r="C52" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2400</v>
       </c>
     </row>
@@ -31901,11 +31901,11 @@
         <v>25</v>
       </c>
       <c r="B53" s="13">
-        <f>$B$11+$B$20*A53</f>
+        <f t="shared" si="0"/>
         <v>2390</v>
       </c>
       <c r="C53" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2500</v>
       </c>
     </row>
@@ -31914,11 +31914,11 @@
         <v>26</v>
       </c>
       <c r="B54" s="13">
-        <f>$B$11+$B$20*A54</f>
+        <f t="shared" si="0"/>
         <v>2430</v>
       </c>
       <c r="C54" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2600</v>
       </c>
     </row>
@@ -31927,11 +31927,11 @@
         <v>27</v>
       </c>
       <c r="B55" s="13">
-        <f>$B$11+$B$20*A55</f>
+        <f t="shared" si="0"/>
         <v>2470</v>
       </c>
       <c r="C55" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2700</v>
       </c>
     </row>
@@ -31940,11 +31940,11 @@
         <v>28</v>
       </c>
       <c r="B56" s="13">
-        <f>$B$11+$B$20*A56</f>
+        <f t="shared" si="0"/>
         <v>2510</v>
       </c>
       <c r="C56" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2800</v>
       </c>
     </row>
@@ -31953,11 +31953,11 @@
         <v>29</v>
       </c>
       <c r="B57" s="13">
-        <f>$B$11+$B$20*A57</f>
+        <f t="shared" si="0"/>
         <v>2550</v>
       </c>
       <c r="C57" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2900</v>
       </c>
     </row>
@@ -31966,11 +31966,11 @@
         <v>30</v>
       </c>
       <c r="B58" s="13">
-        <f>$B$11+$B$20*A58</f>
+        <f t="shared" si="0"/>
         <v>2590</v>
       </c>
       <c r="C58" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3000</v>
       </c>
     </row>
@@ -31979,11 +31979,11 @@
         <v>31</v>
       </c>
       <c r="B59" s="13">
-        <f>$B$11+$B$20*A59</f>
+        <f t="shared" si="0"/>
         <v>2630</v>
       </c>
       <c r="C59" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3100</v>
       </c>
     </row>
@@ -31992,11 +31992,11 @@
         <v>32</v>
       </c>
       <c r="B60" s="13">
-        <f>$B$11+$B$20*A60</f>
+        <f t="shared" si="0"/>
         <v>2670</v>
       </c>
       <c r="C60" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3200</v>
       </c>
     </row>
@@ -32005,11 +32005,11 @@
         <v>33</v>
       </c>
       <c r="B61" s="13">
-        <f>$B$11+$B$20*A61</f>
+        <f t="shared" si="0"/>
         <v>2710</v>
       </c>
       <c r="C61" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3300</v>
       </c>
     </row>
@@ -32018,11 +32018,11 @@
         <v>34</v>
       </c>
       <c r="B62" s="13">
-        <f>$B$11+$B$20*A62</f>
+        <f t="shared" si="0"/>
         <v>2750</v>
       </c>
       <c r="C62" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3400</v>
       </c>
     </row>
@@ -32031,11 +32031,11 @@
         <v>35</v>
       </c>
       <c r="B63" s="13">
-        <f>$B$11+$B$20*A63</f>
+        <f t="shared" si="0"/>
         <v>2790</v>
       </c>
       <c r="C63" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3500</v>
       </c>
     </row>
@@ -32044,11 +32044,11 @@
         <v>36</v>
       </c>
       <c r="B64" s="13">
-        <f>$B$11+$B$20*A64</f>
+        <f t="shared" si="0"/>
         <v>2830</v>
       </c>
       <c r="C64" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3600</v>
       </c>
     </row>
@@ -32057,11 +32057,11 @@
         <v>37</v>
       </c>
       <c r="B65" s="13">
-        <f>$B$11+$B$20*A65</f>
+        <f t="shared" si="0"/>
         <v>2870</v>
       </c>
       <c r="C65" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3700</v>
       </c>
     </row>
@@ -32070,11 +32070,11 @@
         <v>38</v>
       </c>
       <c r="B66" s="13">
-        <f>$B$11+$B$20*A66</f>
+        <f t="shared" si="0"/>
         <v>2910</v>
       </c>
       <c r="C66" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3800</v>
       </c>
     </row>
@@ -32083,11 +32083,11 @@
         <v>39</v>
       </c>
       <c r="B67" s="13">
-        <f>$B$11+$B$20*A67</f>
+        <f t="shared" si="0"/>
         <v>2950</v>
       </c>
       <c r="C67" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3900</v>
       </c>
     </row>
@@ -32096,11 +32096,11 @@
         <v>40</v>
       </c>
       <c r="B68" s="13">
-        <f>$B$11+$B$20*A68</f>
+        <f t="shared" si="0"/>
         <v>2990</v>
       </c>
       <c r="C68" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4000</v>
       </c>
     </row>
@@ -32109,11 +32109,11 @@
         <v>41</v>
       </c>
       <c r="B69" s="13">
-        <f>$B$11+$B$20*A69</f>
+        <f t="shared" si="0"/>
         <v>3030</v>
       </c>
       <c r="C69" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4100</v>
       </c>
     </row>
@@ -32122,11 +32122,11 @@
         <v>42</v>
       </c>
       <c r="B70" s="13">
-        <f>$B$11+$B$20*A70</f>
+        <f t="shared" si="0"/>
         <v>3070</v>
       </c>
       <c r="C70" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4200</v>
       </c>
     </row>
@@ -32135,11 +32135,11 @@
         <v>43</v>
       </c>
       <c r="B71" s="13">
-        <f>$B$11+$B$20*A71</f>
+        <f t="shared" si="0"/>
         <v>3110</v>
       </c>
       <c r="C71" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4300</v>
       </c>
     </row>
@@ -32148,11 +32148,11 @@
         <v>44</v>
       </c>
       <c r="B72" s="13">
-        <f>$B$11+$B$20*A72</f>
+        <f t="shared" si="0"/>
         <v>3150</v>
       </c>
       <c r="C72" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4400</v>
       </c>
     </row>
@@ -32161,11 +32161,11 @@
         <v>45</v>
       </c>
       <c r="B73" s="13">
-        <f>$B$11+$B$20*A73</f>
+        <f t="shared" si="0"/>
         <v>3190</v>
       </c>
       <c r="C73" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4500</v>
       </c>
     </row>
@@ -32174,11 +32174,11 @@
         <v>46</v>
       </c>
       <c r="B74" s="13">
-        <f>$B$11+$B$20*A74</f>
+        <f t="shared" si="0"/>
         <v>3230</v>
       </c>
       <c r="C74" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4600</v>
       </c>
     </row>
@@ -32187,11 +32187,11 @@
         <v>47</v>
       </c>
       <c r="B75" s="13">
-        <f>$B$11+$B$20*A75</f>
+        <f t="shared" si="0"/>
         <v>3270</v>
       </c>
       <c r="C75" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4700</v>
       </c>
     </row>
@@ -32200,11 +32200,11 @@
         <v>48</v>
       </c>
       <c r="B76" s="13">
-        <f>$B$11+$B$20*A76</f>
+        <f t="shared" si="0"/>
         <v>3310</v>
       </c>
       <c r="C76" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4800</v>
       </c>
     </row>
@@ -32213,11 +32213,11 @@
         <v>49</v>
       </c>
       <c r="B77" s="13">
-        <f>$B$11+$B$20*A77</f>
+        <f t="shared" si="0"/>
         <v>3350</v>
       </c>
       <c r="C77" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4900</v>
       </c>
     </row>
@@ -32226,11 +32226,11 @@
         <v>50</v>
       </c>
       <c r="B78" s="13">
-        <f>$B$11+$B$20*A78</f>
+        <f t="shared" si="0"/>
         <v>3390</v>
       </c>
       <c r="C78" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5000</v>
       </c>
     </row>
@@ -32239,11 +32239,11 @@
         <v>51</v>
       </c>
       <c r="B79" s="13">
-        <f>$B$11+$B$20*A79</f>
+        <f t="shared" si="0"/>
         <v>3430</v>
       </c>
       <c r="C79" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5100</v>
       </c>
     </row>
@@ -32252,11 +32252,11 @@
         <v>52</v>
       </c>
       <c r="B80" s="13">
-        <f>$B$11+$B$20*A80</f>
+        <f t="shared" si="0"/>
         <v>3470</v>
       </c>
       <c r="C80" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5200</v>
       </c>
     </row>
@@ -32265,11 +32265,11 @@
         <v>53</v>
       </c>
       <c r="B81" s="13">
-        <f>$B$11+$B$20*A81</f>
+        <f t="shared" si="0"/>
         <v>3510</v>
       </c>
       <c r="C81" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5300</v>
       </c>
     </row>
@@ -32278,11 +32278,11 @@
         <v>54</v>
       </c>
       <c r="B82" s="13">
-        <f>$B$11+$B$20*A82</f>
+        <f t="shared" si="0"/>
         <v>3550</v>
       </c>
       <c r="C82" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5400</v>
       </c>
     </row>
@@ -32291,11 +32291,11 @@
         <v>55</v>
       </c>
       <c r="B83" s="13">
-        <f>$B$11+$B$20*A83</f>
+        <f t="shared" si="0"/>
         <v>3590</v>
       </c>
       <c r="C83" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5500</v>
       </c>
     </row>
@@ -32304,11 +32304,11 @@
         <v>56</v>
       </c>
       <c r="B84" s="13">
-        <f>$B$11+$B$20*A84</f>
+        <f t="shared" si="0"/>
         <v>3630</v>
       </c>
       <c r="C84" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5600</v>
       </c>
     </row>
@@ -32317,11 +32317,11 @@
         <v>57</v>
       </c>
       <c r="B85" s="13">
-        <f>$B$11+$B$20*A85</f>
+        <f t="shared" si="0"/>
         <v>3670</v>
       </c>
       <c r="C85" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5700</v>
       </c>
     </row>
@@ -32330,11 +32330,11 @@
         <v>58</v>
       </c>
       <c r="B86" s="13">
-        <f>$B$11+$B$20*A86</f>
+        <f t="shared" si="0"/>
         <v>3710</v>
       </c>
       <c r="C86" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5800</v>
       </c>
     </row>
@@ -32343,11 +32343,11 @@
         <v>59</v>
       </c>
       <c r="B87" s="13">
-        <f>$B$11+$B$20*A87</f>
+        <f t="shared" si="0"/>
         <v>3750</v>
       </c>
       <c r="C87" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5900</v>
       </c>
     </row>
@@ -32356,11 +32356,11 @@
         <v>60</v>
       </c>
       <c r="B88" s="13">
-        <f>$B$11+$B$20*A88</f>
+        <f t="shared" si="0"/>
         <v>3790</v>
       </c>
       <c r="C88" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6000</v>
       </c>
     </row>
@@ -32369,11 +32369,11 @@
         <v>61</v>
       </c>
       <c r="B89" s="13">
-        <f>$B$11+$B$20*A89</f>
+        <f t="shared" si="0"/>
         <v>3830</v>
       </c>
       <c r="C89" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6100</v>
       </c>
     </row>
@@ -32382,11 +32382,11 @@
         <v>62</v>
       </c>
       <c r="B90" s="13">
-        <f>$B$11+$B$20*A90</f>
+        <f t="shared" si="0"/>
         <v>3870</v>
       </c>
       <c r="C90" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6200</v>
       </c>
     </row>
@@ -32395,11 +32395,11 @@
         <v>63</v>
       </c>
       <c r="B91" s="13">
-        <f>$B$11+$B$20*A91</f>
+        <f t="shared" si="0"/>
         <v>3910</v>
       </c>
       <c r="C91" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6300</v>
       </c>
     </row>
@@ -32408,11 +32408,11 @@
         <v>64</v>
       </c>
       <c r="B92" s="13">
-        <f>$B$11+$B$20*A92</f>
+        <f t="shared" ref="B92:B155" si="2">$B$11+$B$20*A92</f>
         <v>3950</v>
       </c>
       <c r="C92" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6400</v>
       </c>
     </row>
@@ -32421,11 +32421,11 @@
         <v>65</v>
       </c>
       <c r="B93" s="13">
-        <f>$B$11+$B$20*A93</f>
+        <f t="shared" si="2"/>
         <v>3990</v>
       </c>
       <c r="C93" s="9">
-        <f t="shared" ref="C93:C156" si="1">$B$23*A93</f>
+        <f t="shared" ref="C93:C156" si="3">$B$23*A93</f>
         <v>6500</v>
       </c>
     </row>
@@ -32434,11 +32434,11 @@
         <v>66</v>
       </c>
       <c r="B94" s="13">
-        <f>$B$11+$B$20*A94</f>
+        <f t="shared" si="2"/>
         <v>4030</v>
       </c>
       <c r="C94" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6600</v>
       </c>
     </row>
@@ -32447,11 +32447,11 @@
         <v>67</v>
       </c>
       <c r="B95" s="13">
-        <f>$B$11+$B$20*A95</f>
+        <f t="shared" si="2"/>
         <v>4070</v>
       </c>
       <c r="C95" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6700</v>
       </c>
     </row>
@@ -32460,11 +32460,11 @@
         <v>68</v>
       </c>
       <c r="B96" s="13">
-        <f>$B$11+$B$20*A96</f>
+        <f t="shared" si="2"/>
         <v>4110</v>
       </c>
       <c r="C96" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6800</v>
       </c>
     </row>
@@ -32473,11 +32473,11 @@
         <v>69</v>
       </c>
       <c r="B97" s="13">
-        <f>$B$11+$B$20*A97</f>
+        <f t="shared" si="2"/>
         <v>4150</v>
       </c>
       <c r="C97" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6900</v>
       </c>
     </row>
@@ -32486,11 +32486,11 @@
         <v>70</v>
       </c>
       <c r="B98" s="13">
-        <f>$B$11+$B$20*A98</f>
+        <f t="shared" si="2"/>
         <v>4190</v>
       </c>
       <c r="C98" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7000</v>
       </c>
     </row>
@@ -32499,11 +32499,11 @@
         <v>71</v>
       </c>
       <c r="B99" s="13">
-        <f>$B$11+$B$20*A99</f>
+        <f t="shared" si="2"/>
         <v>4230</v>
       </c>
       <c r="C99" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7100</v>
       </c>
     </row>
@@ -32512,11 +32512,11 @@
         <v>72</v>
       </c>
       <c r="B100" s="13">
-        <f>$B$11+$B$20*A100</f>
+        <f t="shared" si="2"/>
         <v>4270</v>
       </c>
       <c r="C100" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7200</v>
       </c>
     </row>
@@ -32525,11 +32525,11 @@
         <v>73</v>
       </c>
       <c r="B101" s="13">
-        <f>$B$11+$B$20*A101</f>
+        <f t="shared" si="2"/>
         <v>4310</v>
       </c>
       <c r="C101" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7300</v>
       </c>
     </row>
@@ -32538,11 +32538,11 @@
         <v>74</v>
       </c>
       <c r="B102" s="13">
-        <f>$B$11+$B$20*A102</f>
+        <f t="shared" si="2"/>
         <v>4350</v>
       </c>
       <c r="C102" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7400</v>
       </c>
     </row>
@@ -32551,11 +32551,11 @@
         <v>75</v>
       </c>
       <c r="B103" s="13">
-        <f>$B$11+$B$20*A103</f>
+        <f t="shared" si="2"/>
         <v>4390</v>
       </c>
       <c r="C103" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7500</v>
       </c>
     </row>
@@ -32564,11 +32564,11 @@
         <v>76</v>
       </c>
       <c r="B104" s="13">
-        <f>$B$11+$B$20*A104</f>
+        <f t="shared" si="2"/>
         <v>4430</v>
       </c>
       <c r="C104" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7600</v>
       </c>
     </row>
@@ -32577,11 +32577,11 @@
         <v>77</v>
       </c>
       <c r="B105" s="13">
-        <f>$B$11+$B$20*A105</f>
+        <f t="shared" si="2"/>
         <v>4470</v>
       </c>
       <c r="C105" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7700</v>
       </c>
     </row>
@@ -32590,11 +32590,11 @@
         <v>78</v>
       </c>
       <c r="B106" s="13">
-        <f>$B$11+$B$20*A106</f>
+        <f t="shared" si="2"/>
         <v>4510</v>
       </c>
       <c r="C106" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7800</v>
       </c>
     </row>
@@ -32603,11 +32603,11 @@
         <v>79</v>
       </c>
       <c r="B107" s="13">
-        <f>$B$11+$B$20*A107</f>
+        <f t="shared" si="2"/>
         <v>4550</v>
       </c>
       <c r="C107" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7900</v>
       </c>
     </row>
@@ -32616,11 +32616,11 @@
         <v>80</v>
       </c>
       <c r="B108" s="13">
-        <f>$B$11+$B$20*A108</f>
+        <f t="shared" si="2"/>
         <v>4590</v>
       </c>
       <c r="C108" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8000</v>
       </c>
     </row>
@@ -32629,11 +32629,11 @@
         <v>81</v>
       </c>
       <c r="B109" s="13">
-        <f>$B$11+$B$20*A109</f>
+        <f t="shared" si="2"/>
         <v>4630</v>
       </c>
       <c r="C109" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8100</v>
       </c>
     </row>
@@ -32642,11 +32642,11 @@
         <v>82</v>
       </c>
       <c r="B110" s="13">
-        <f>$B$11+$B$20*A110</f>
+        <f t="shared" si="2"/>
         <v>4670</v>
       </c>
       <c r="C110" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8200</v>
       </c>
     </row>
@@ -32655,11 +32655,11 @@
         <v>83</v>
       </c>
       <c r="B111" s="13">
-        <f>$B$11+$B$20*A111</f>
+        <f t="shared" si="2"/>
         <v>4710</v>
       </c>
       <c r="C111" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8300</v>
       </c>
     </row>
@@ -32668,11 +32668,11 @@
         <v>84</v>
       </c>
       <c r="B112" s="13">
-        <f>$B$11+$B$20*A112</f>
+        <f t="shared" si="2"/>
         <v>4750</v>
       </c>
       <c r="C112" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8400</v>
       </c>
     </row>
@@ -32681,11 +32681,11 @@
         <v>85</v>
       </c>
       <c r="B113" s="13">
-        <f>$B$11+$B$20*A113</f>
+        <f t="shared" si="2"/>
         <v>4790</v>
       </c>
       <c r="C113" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8500</v>
       </c>
     </row>
@@ -32694,11 +32694,11 @@
         <v>86</v>
       </c>
       <c r="B114" s="13">
-        <f>$B$11+$B$20*A114</f>
+        <f t="shared" si="2"/>
         <v>4830</v>
       </c>
       <c r="C114" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8600</v>
       </c>
     </row>
@@ -32707,11 +32707,11 @@
         <v>87</v>
       </c>
       <c r="B115" s="13">
-        <f>$B$11+$B$20*A115</f>
+        <f t="shared" si="2"/>
         <v>4870</v>
       </c>
       <c r="C115" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8700</v>
       </c>
     </row>
@@ -32720,11 +32720,11 @@
         <v>88</v>
       </c>
       <c r="B116" s="13">
-        <f>$B$11+$B$20*A116</f>
+        <f t="shared" si="2"/>
         <v>4910</v>
       </c>
       <c r="C116" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8800</v>
       </c>
     </row>
@@ -32733,11 +32733,11 @@
         <v>89</v>
       </c>
       <c r="B117" s="13">
-        <f>$B$11+$B$20*A117</f>
+        <f t="shared" si="2"/>
         <v>4950</v>
       </c>
       <c r="C117" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8900</v>
       </c>
     </row>
@@ -32746,11 +32746,11 @@
         <v>90</v>
       </c>
       <c r="B118" s="13">
-        <f>$B$11+$B$20*A118</f>
+        <f t="shared" si="2"/>
         <v>4990</v>
       </c>
       <c r="C118" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9000</v>
       </c>
     </row>
@@ -32759,11 +32759,11 @@
         <v>91</v>
       </c>
       <c r="B119" s="13">
-        <f>$B$11+$B$20*A119</f>
+        <f t="shared" si="2"/>
         <v>5030</v>
       </c>
       <c r="C119" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9100</v>
       </c>
     </row>
@@ -32772,11 +32772,11 @@
         <v>92</v>
       </c>
       <c r="B120" s="13">
-        <f>$B$11+$B$20*A120</f>
+        <f t="shared" si="2"/>
         <v>5070</v>
       </c>
       <c r="C120" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9200</v>
       </c>
     </row>
@@ -32785,11 +32785,11 @@
         <v>93</v>
       </c>
       <c r="B121" s="13">
-        <f>$B$11+$B$20*A121</f>
+        <f t="shared" si="2"/>
         <v>5110</v>
       </c>
       <c r="C121" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9300</v>
       </c>
     </row>
@@ -32798,11 +32798,11 @@
         <v>94</v>
       </c>
       <c r="B122" s="13">
-        <f>$B$11+$B$20*A122</f>
+        <f t="shared" si="2"/>
         <v>5150</v>
       </c>
       <c r="C122" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9400</v>
       </c>
     </row>
@@ -32811,11 +32811,11 @@
         <v>95</v>
       </c>
       <c r="B123" s="13">
-        <f>$B$11+$B$20*A123</f>
+        <f t="shared" si="2"/>
         <v>5190</v>
       </c>
       <c r="C123" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9500</v>
       </c>
     </row>
@@ -32824,11 +32824,11 @@
         <v>96</v>
       </c>
       <c r="B124" s="13">
-        <f>$B$11+$B$20*A124</f>
+        <f t="shared" si="2"/>
         <v>5230</v>
       </c>
       <c r="C124" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9600</v>
       </c>
     </row>
@@ -32837,11 +32837,11 @@
         <v>97</v>
       </c>
       <c r="B125" s="13">
-        <f>$B$11+$B$20*A125</f>
+        <f t="shared" si="2"/>
         <v>5270</v>
       </c>
       <c r="C125" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9700</v>
       </c>
     </row>
@@ -32850,11 +32850,11 @@
         <v>98</v>
       </c>
       <c r="B126" s="13">
-        <f>$B$11+$B$20*A126</f>
+        <f t="shared" si="2"/>
         <v>5310</v>
       </c>
       <c r="C126" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9800</v>
       </c>
     </row>
@@ -32863,11 +32863,11 @@
         <v>99</v>
       </c>
       <c r="B127" s="13">
-        <f>$B$11+$B$20*A127</f>
+        <f t="shared" si="2"/>
         <v>5350</v>
       </c>
       <c r="C127" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9900</v>
       </c>
     </row>
@@ -32876,11 +32876,11 @@
         <v>100</v>
       </c>
       <c r="B128" s="13">
-        <f>$B$11+$B$20*A128</f>
+        <f t="shared" si="2"/>
         <v>5390</v>
       </c>
       <c r="C128" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10000</v>
       </c>
     </row>
@@ -32889,11 +32889,11 @@
         <v>101</v>
       </c>
       <c r="B129" s="16">
-        <f>$B$11+$B$20*A129</f>
+        <f t="shared" si="2"/>
         <v>5430</v>
       </c>
       <c r="C129" s="17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10100</v>
       </c>
     </row>
@@ -32902,11 +32902,11 @@
         <v>102</v>
       </c>
       <c r="B130" s="13">
-        <f>$B$11+$B$20*A130</f>
+        <f t="shared" si="2"/>
         <v>5470</v>
       </c>
       <c r="C130" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10200</v>
       </c>
     </row>
@@ -32915,11 +32915,11 @@
         <v>103</v>
       </c>
       <c r="B131" s="13">
-        <f>$B$11+$B$20*A131</f>
+        <f t="shared" si="2"/>
         <v>5510</v>
       </c>
       <c r="C131" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10300</v>
       </c>
     </row>
@@ -32928,11 +32928,11 @@
         <v>104</v>
       </c>
       <c r="B132" s="13">
-        <f>$B$11+$B$20*A132</f>
+        <f t="shared" si="2"/>
         <v>5550</v>
       </c>
       <c r="C132" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10400</v>
       </c>
     </row>
@@ -32941,11 +32941,11 @@
         <v>105</v>
       </c>
       <c r="B133" s="13">
-        <f>$B$11+$B$20*A133</f>
+        <f t="shared" si="2"/>
         <v>5590</v>
       </c>
       <c r="C133" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10500</v>
       </c>
     </row>
@@ -32954,11 +32954,11 @@
         <v>106</v>
       </c>
       <c r="B134" s="13">
-        <f>$B$11+$B$20*A134</f>
+        <f t="shared" si="2"/>
         <v>5630</v>
       </c>
       <c r="C134" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10600</v>
       </c>
     </row>
@@ -32967,11 +32967,11 @@
         <v>107</v>
       </c>
       <c r="B135" s="13">
-        <f>$B$11+$B$20*A135</f>
+        <f t="shared" si="2"/>
         <v>5670</v>
       </c>
       <c r="C135" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10700</v>
       </c>
     </row>
@@ -32980,11 +32980,11 @@
         <v>108</v>
       </c>
       <c r="B136" s="13">
-        <f>$B$11+$B$20*A136</f>
+        <f t="shared" si="2"/>
         <v>5710</v>
       </c>
       <c r="C136" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10800</v>
       </c>
     </row>
@@ -32993,11 +32993,11 @@
         <v>109</v>
       </c>
       <c r="B137" s="13">
-        <f>$B$11+$B$20*A137</f>
+        <f t="shared" si="2"/>
         <v>5750</v>
       </c>
       <c r="C137" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10900</v>
       </c>
     </row>
@@ -33006,11 +33006,11 @@
         <v>110</v>
       </c>
       <c r="B138" s="13">
-        <f>$B$11+$B$20*A138</f>
+        <f t="shared" si="2"/>
         <v>5790</v>
       </c>
       <c r="C138" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11000</v>
       </c>
     </row>
@@ -33019,11 +33019,11 @@
         <v>111</v>
       </c>
       <c r="B139" s="13">
-        <f>$B$11+$B$20*A139</f>
+        <f t="shared" si="2"/>
         <v>5830</v>
       </c>
       <c r="C139" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11100</v>
       </c>
     </row>
@@ -33032,11 +33032,11 @@
         <v>112</v>
       </c>
       <c r="B140" s="13">
-        <f>$B$11+$B$20*A140</f>
+        <f t="shared" si="2"/>
         <v>5870</v>
       </c>
       <c r="C140" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11200</v>
       </c>
     </row>
@@ -33045,11 +33045,11 @@
         <v>113</v>
       </c>
       <c r="B141" s="13">
-        <f>$B$11+$B$20*A141</f>
+        <f t="shared" si="2"/>
         <v>5910</v>
       </c>
       <c r="C141" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11300</v>
       </c>
     </row>
@@ -33058,11 +33058,11 @@
         <v>114</v>
       </c>
       <c r="B142" s="13">
-        <f>$B$11+$B$20*A142</f>
+        <f t="shared" si="2"/>
         <v>5950</v>
       </c>
       <c r="C142" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11400</v>
       </c>
     </row>
@@ -33071,11 +33071,11 @@
         <v>115</v>
       </c>
       <c r="B143" s="13">
-        <f>$B$11+$B$20*A143</f>
+        <f t="shared" si="2"/>
         <v>5990</v>
       </c>
       <c r="C143" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11500</v>
       </c>
     </row>
@@ -33084,11 +33084,11 @@
         <v>116</v>
       </c>
       <c r="B144" s="13">
-        <f>$B$11+$B$20*A144</f>
+        <f t="shared" si="2"/>
         <v>6030</v>
       </c>
       <c r="C144" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11600</v>
       </c>
     </row>
@@ -33097,11 +33097,11 @@
         <v>117</v>
       </c>
       <c r="B145" s="13">
-        <f>$B$11+$B$20*A145</f>
+        <f t="shared" si="2"/>
         <v>6070</v>
       </c>
       <c r="C145" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11700</v>
       </c>
     </row>
@@ -33110,11 +33110,11 @@
         <v>118</v>
       </c>
       <c r="B146" s="13">
-        <f>$B$11+$B$20*A146</f>
+        <f t="shared" si="2"/>
         <v>6110</v>
       </c>
       <c r="C146" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11800</v>
       </c>
     </row>
@@ -33123,11 +33123,11 @@
         <v>119</v>
       </c>
       <c r="B147" s="13">
-        <f>$B$11+$B$20*A147</f>
+        <f t="shared" si="2"/>
         <v>6150</v>
       </c>
       <c r="C147" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11900</v>
       </c>
     </row>
@@ -33136,11 +33136,11 @@
         <v>120</v>
       </c>
       <c r="B148" s="13">
-        <f>$B$11+$B$20*A148</f>
+        <f t="shared" si="2"/>
         <v>6190</v>
       </c>
       <c r="C148" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12000</v>
       </c>
     </row>
@@ -33149,11 +33149,11 @@
         <v>121</v>
       </c>
       <c r="B149" s="13">
-        <f>$B$11+$B$20*A149</f>
+        <f t="shared" si="2"/>
         <v>6230</v>
       </c>
       <c r="C149" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12100</v>
       </c>
     </row>
@@ -33162,11 +33162,11 @@
         <v>122</v>
       </c>
       <c r="B150" s="13">
-        <f>$B$11+$B$20*A150</f>
+        <f t="shared" si="2"/>
         <v>6270</v>
       </c>
       <c r="C150" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12200</v>
       </c>
     </row>
@@ -33175,11 +33175,11 @@
         <v>123</v>
       </c>
       <c r="B151" s="13">
-        <f>$B$11+$B$20*A151</f>
+        <f t="shared" si="2"/>
         <v>6310</v>
       </c>
       <c r="C151" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12300</v>
       </c>
     </row>
@@ -33188,11 +33188,11 @@
         <v>124</v>
       </c>
       <c r="B152" s="13">
-        <f>$B$11+$B$20*A152</f>
+        <f t="shared" si="2"/>
         <v>6350</v>
       </c>
       <c r="C152" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12400</v>
       </c>
     </row>
@@ -33201,11 +33201,11 @@
         <v>125</v>
       </c>
       <c r="B153" s="13">
-        <f>$B$11+$B$20*A153</f>
+        <f t="shared" si="2"/>
         <v>6390</v>
       </c>
       <c r="C153" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12500</v>
       </c>
     </row>
@@ -33214,11 +33214,11 @@
         <v>126</v>
       </c>
       <c r="B154" s="13">
-        <f>$B$11+$B$20*A154</f>
+        <f t="shared" si="2"/>
         <v>6430</v>
       </c>
       <c r="C154" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12600</v>
       </c>
     </row>
@@ -33227,11 +33227,11 @@
         <v>127</v>
       </c>
       <c r="B155" s="13">
-        <f>$B$11+$B$20*A155</f>
+        <f t="shared" si="2"/>
         <v>6470</v>
       </c>
       <c r="C155" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12700</v>
       </c>
     </row>
@@ -33240,11 +33240,11 @@
         <v>128</v>
       </c>
       <c r="B156" s="13">
-        <f>$B$11+$B$20*A156</f>
+        <f t="shared" ref="B156:B219" si="4">$B$11+$B$20*A156</f>
         <v>6510</v>
       </c>
       <c r="C156" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12800</v>
       </c>
     </row>
@@ -33253,11 +33253,11 @@
         <v>129</v>
       </c>
       <c r="B157" s="13">
-        <f>$B$11+$B$20*A157</f>
+        <f t="shared" si="4"/>
         <v>6550</v>
       </c>
       <c r="C157" s="9">
-        <f t="shared" ref="C157:C220" si="2">$B$23*A157</f>
+        <f t="shared" ref="C157:C220" si="5">$B$23*A157</f>
         <v>12900</v>
       </c>
     </row>
@@ -33266,11 +33266,11 @@
         <v>130</v>
       </c>
       <c r="B158" s="13">
-        <f>$B$11+$B$20*A158</f>
+        <f t="shared" si="4"/>
         <v>6590</v>
       </c>
       <c r="C158" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>13000</v>
       </c>
     </row>
@@ -33279,11 +33279,11 @@
         <v>131</v>
       </c>
       <c r="B159" s="13">
-        <f>$B$11+$B$20*A159</f>
+        <f t="shared" si="4"/>
         <v>6630</v>
       </c>
       <c r="C159" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>13100</v>
       </c>
     </row>
@@ -33292,11 +33292,11 @@
         <v>132</v>
       </c>
       <c r="B160" s="13">
-        <f>$B$11+$B$20*A160</f>
+        <f t="shared" si="4"/>
         <v>6670</v>
       </c>
       <c r="C160" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>13200</v>
       </c>
     </row>
@@ -33305,11 +33305,11 @@
         <v>133</v>
       </c>
       <c r="B161" s="13">
-        <f>$B$11+$B$20*A161</f>
+        <f t="shared" si="4"/>
         <v>6710</v>
       </c>
       <c r="C161" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>13300</v>
       </c>
     </row>
@@ -33318,11 +33318,11 @@
         <v>134</v>
       </c>
       <c r="B162" s="13">
-        <f>$B$11+$B$20*A162</f>
+        <f t="shared" si="4"/>
         <v>6750</v>
       </c>
       <c r="C162" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>13400</v>
       </c>
     </row>
@@ -33331,11 +33331,11 @@
         <v>135</v>
       </c>
       <c r="B163" s="13">
-        <f>$B$11+$B$20*A163</f>
+        <f t="shared" si="4"/>
         <v>6790</v>
       </c>
       <c r="C163" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>13500</v>
       </c>
     </row>
@@ -33344,11 +33344,11 @@
         <v>136</v>
       </c>
       <c r="B164" s="13">
-        <f>$B$11+$B$20*A164</f>
+        <f t="shared" si="4"/>
         <v>6830</v>
       </c>
       <c r="C164" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>13600</v>
       </c>
     </row>
@@ -33357,11 +33357,11 @@
         <v>137</v>
       </c>
       <c r="B165" s="13">
-        <f>$B$11+$B$20*A165</f>
+        <f t="shared" si="4"/>
         <v>6870</v>
       </c>
       <c r="C165" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>13700</v>
       </c>
     </row>
@@ -33370,11 +33370,11 @@
         <v>138</v>
       </c>
       <c r="B166" s="13">
-        <f>$B$11+$B$20*A166</f>
+        <f t="shared" si="4"/>
         <v>6910</v>
       </c>
       <c r="C166" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>13800</v>
       </c>
     </row>
@@ -33383,11 +33383,11 @@
         <v>139</v>
       </c>
       <c r="B167" s="13">
-        <f>$B$11+$B$20*A167</f>
+        <f t="shared" si="4"/>
         <v>6950</v>
       </c>
       <c r="C167" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>13900</v>
       </c>
     </row>
@@ -33396,11 +33396,11 @@
         <v>140</v>
       </c>
       <c r="B168" s="13">
-        <f>$B$11+$B$20*A168</f>
+        <f t="shared" si="4"/>
         <v>6990</v>
       </c>
       <c r="C168" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>14000</v>
       </c>
     </row>
@@ -33409,11 +33409,11 @@
         <v>141</v>
       </c>
       <c r="B169" s="13">
-        <f>$B$11+$B$20*A169</f>
+        <f t="shared" si="4"/>
         <v>7030</v>
       </c>
       <c r="C169" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>14100</v>
       </c>
     </row>
@@ -33422,11 +33422,11 @@
         <v>142</v>
       </c>
       <c r="B170" s="13">
-        <f>$B$11+$B$20*A170</f>
+        <f t="shared" si="4"/>
         <v>7070</v>
       </c>
       <c r="C170" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>14200</v>
       </c>
     </row>
@@ -33435,11 +33435,11 @@
         <v>143</v>
       </c>
       <c r="B171" s="13">
-        <f>$B$11+$B$20*A171</f>
+        <f t="shared" si="4"/>
         <v>7110</v>
       </c>
       <c r="C171" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>14300</v>
       </c>
     </row>
@@ -33448,11 +33448,11 @@
         <v>144</v>
       </c>
       <c r="B172" s="13">
-        <f>$B$11+$B$20*A172</f>
+        <f t="shared" si="4"/>
         <v>7150</v>
       </c>
       <c r="C172" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>14400</v>
       </c>
     </row>
@@ -33461,11 +33461,11 @@
         <v>145</v>
       </c>
       <c r="B173" s="13">
-        <f>$B$11+$B$20*A173</f>
+        <f t="shared" si="4"/>
         <v>7190</v>
       </c>
       <c r="C173" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>14500</v>
       </c>
     </row>
@@ -33474,11 +33474,11 @@
         <v>146</v>
       </c>
       <c r="B174" s="13">
-        <f>$B$11+$B$20*A174</f>
+        <f t="shared" si="4"/>
         <v>7230</v>
       </c>
       <c r="C174" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>14600</v>
       </c>
     </row>
@@ -33487,11 +33487,11 @@
         <v>147</v>
       </c>
       <c r="B175" s="13">
-        <f>$B$11+$B$20*A175</f>
+        <f t="shared" si="4"/>
         <v>7270</v>
       </c>
       <c r="C175" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>14700</v>
       </c>
     </row>
@@ -33500,11 +33500,11 @@
         <v>148</v>
       </c>
       <c r="B176" s="13">
-        <f>$B$11+$B$20*A176</f>
+        <f t="shared" si="4"/>
         <v>7310</v>
       </c>
       <c r="C176" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>14800</v>
       </c>
     </row>
@@ -33513,11 +33513,11 @@
         <v>149</v>
       </c>
       <c r="B177" s="13">
-        <f>$B$11+$B$20*A177</f>
+        <f t="shared" si="4"/>
         <v>7350</v>
       </c>
       <c r="C177" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>14900</v>
       </c>
     </row>
@@ -33526,11 +33526,11 @@
         <v>150</v>
       </c>
       <c r="B178" s="13">
-        <f>$B$11+$B$20*A178</f>
+        <f t="shared" si="4"/>
         <v>7390</v>
       </c>
       <c r="C178" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>15000</v>
       </c>
     </row>
@@ -33539,11 +33539,11 @@
         <v>151</v>
       </c>
       <c r="B179" s="13">
-        <f>$B$11+$B$20*A179</f>
+        <f t="shared" si="4"/>
         <v>7430</v>
       </c>
       <c r="C179" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>15100</v>
       </c>
     </row>
@@ -33552,11 +33552,11 @@
         <v>152</v>
       </c>
       <c r="B180" s="13">
-        <f>$B$11+$B$20*A180</f>
+        <f t="shared" si="4"/>
         <v>7470</v>
       </c>
       <c r="C180" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>15200</v>
       </c>
     </row>
@@ -33565,11 +33565,11 @@
         <v>153</v>
       </c>
       <c r="B181" s="13">
-        <f>$B$11+$B$20*A181</f>
+        <f t="shared" si="4"/>
         <v>7510</v>
       </c>
       <c r="C181" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>15300</v>
       </c>
     </row>
@@ -33578,11 +33578,11 @@
         <v>154</v>
       </c>
       <c r="B182" s="13">
-        <f>$B$11+$B$20*A182</f>
+        <f t="shared" si="4"/>
         <v>7550</v>
       </c>
       <c r="C182" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>15400</v>
       </c>
     </row>
@@ -33591,11 +33591,11 @@
         <v>155</v>
       </c>
       <c r="B183" s="13">
-        <f>$B$11+$B$20*A183</f>
+        <f t="shared" si="4"/>
         <v>7590</v>
       </c>
       <c r="C183" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>15500</v>
       </c>
     </row>
@@ -33604,11 +33604,11 @@
         <v>156</v>
       </c>
       <c r="B184" s="13">
-        <f>$B$11+$B$20*A184</f>
+        <f t="shared" si="4"/>
         <v>7630</v>
       </c>
       <c r="C184" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>15600</v>
       </c>
     </row>
@@ -33617,11 +33617,11 @@
         <v>157</v>
       </c>
       <c r="B185" s="13">
-        <f>$B$11+$B$20*A185</f>
+        <f t="shared" si="4"/>
         <v>7670</v>
       </c>
       <c r="C185" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>15700</v>
       </c>
     </row>
@@ -33630,11 +33630,11 @@
         <v>158</v>
       </c>
       <c r="B186" s="13">
-        <f>$B$11+$B$20*A186</f>
+        <f t="shared" si="4"/>
         <v>7710</v>
       </c>
       <c r="C186" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>15800</v>
       </c>
     </row>
@@ -33643,11 +33643,11 @@
         <v>159</v>
       </c>
       <c r="B187" s="13">
-        <f>$B$11+$B$20*A187</f>
+        <f t="shared" si="4"/>
         <v>7750</v>
       </c>
       <c r="C187" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>15900</v>
       </c>
     </row>
@@ -33656,11 +33656,11 @@
         <v>160</v>
       </c>
       <c r="B188" s="13">
-        <f>$B$11+$B$20*A188</f>
+        <f t="shared" si="4"/>
         <v>7790</v>
       </c>
       <c r="C188" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>16000</v>
       </c>
     </row>
@@ -33669,11 +33669,11 @@
         <v>161</v>
       </c>
       <c r="B189" s="13">
-        <f>$B$11+$B$20*A189</f>
+        <f t="shared" si="4"/>
         <v>7830</v>
       </c>
       <c r="C189" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>16100</v>
       </c>
     </row>
@@ -33682,11 +33682,11 @@
         <v>162</v>
       </c>
       <c r="B190" s="13">
-        <f>$B$11+$B$20*A190</f>
+        <f t="shared" si="4"/>
         <v>7870</v>
       </c>
       <c r="C190" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>16200</v>
       </c>
     </row>
@@ -33695,11 +33695,11 @@
         <v>163</v>
       </c>
       <c r="B191" s="13">
-        <f>$B$11+$B$20*A191</f>
+        <f t="shared" si="4"/>
         <v>7910</v>
       </c>
       <c r="C191" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>16300</v>
       </c>
     </row>
@@ -33708,11 +33708,11 @@
         <v>164</v>
       </c>
       <c r="B192" s="13">
-        <f>$B$11+$B$20*A192</f>
+        <f t="shared" si="4"/>
         <v>7950</v>
       </c>
       <c r="C192" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>16400</v>
       </c>
     </row>
@@ -33721,11 +33721,11 @@
         <v>165</v>
       </c>
       <c r="B193" s="13">
-        <f>$B$11+$B$20*A193</f>
+        <f t="shared" si="4"/>
         <v>7990</v>
       </c>
       <c r="C193" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>16500</v>
       </c>
     </row>
@@ -33734,11 +33734,11 @@
         <v>166</v>
       </c>
       <c r="B194" s="13">
-        <f>$B$11+$B$20*A194</f>
+        <f t="shared" si="4"/>
         <v>8030</v>
       </c>
       <c r="C194" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>16600</v>
       </c>
     </row>
@@ -33747,11 +33747,11 @@
         <v>167</v>
       </c>
       <c r="B195" s="13">
-        <f>$B$11+$B$20*A195</f>
+        <f t="shared" si="4"/>
         <v>8070</v>
       </c>
       <c r="C195" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>16700</v>
       </c>
     </row>
@@ -33760,11 +33760,11 @@
         <v>168</v>
       </c>
       <c r="B196" s="13">
-        <f>$B$11+$B$20*A196</f>
+        <f t="shared" si="4"/>
         <v>8110</v>
       </c>
       <c r="C196" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>16800</v>
       </c>
     </row>
@@ -33773,11 +33773,11 @@
         <v>169</v>
       </c>
       <c r="B197" s="13">
-        <f>$B$11+$B$20*A197</f>
+        <f t="shared" si="4"/>
         <v>8150</v>
       </c>
       <c r="C197" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>16900</v>
       </c>
     </row>
@@ -33786,11 +33786,11 @@
         <v>170</v>
       </c>
       <c r="B198" s="13">
-        <f>$B$11+$B$20*A198</f>
+        <f t="shared" si="4"/>
         <v>8190</v>
       </c>
       <c r="C198" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17000</v>
       </c>
     </row>
@@ -33799,11 +33799,11 @@
         <v>171</v>
       </c>
       <c r="B199" s="13">
-        <f>$B$11+$B$20*A199</f>
+        <f t="shared" si="4"/>
         <v>8230</v>
       </c>
       <c r="C199" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17100</v>
       </c>
     </row>
@@ -33812,11 +33812,11 @@
         <v>172</v>
       </c>
       <c r="B200" s="13">
-        <f>$B$11+$B$20*A200</f>
+        <f t="shared" si="4"/>
         <v>8270</v>
       </c>
       <c r="C200" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17200</v>
       </c>
     </row>
@@ -33825,11 +33825,11 @@
         <v>173</v>
       </c>
       <c r="B201" s="13">
-        <f>$B$11+$B$20*A201</f>
+        <f t="shared" si="4"/>
         <v>8310</v>
       </c>
       <c r="C201" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17300</v>
       </c>
     </row>
@@ -33838,11 +33838,11 @@
         <v>174</v>
       </c>
       <c r="B202" s="13">
-        <f>$B$11+$B$20*A202</f>
+        <f t="shared" si="4"/>
         <v>8350</v>
       </c>
       <c r="C202" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17400</v>
       </c>
     </row>
@@ -33851,11 +33851,11 @@
         <v>175</v>
       </c>
       <c r="B203" s="13">
-        <f>$B$11+$B$20*A203</f>
+        <f t="shared" si="4"/>
         <v>8390</v>
       </c>
       <c r="C203" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17500</v>
       </c>
     </row>
@@ -33864,11 +33864,11 @@
         <v>176</v>
       </c>
       <c r="B204" s="13">
-        <f>$B$11+$B$20*A204</f>
+        <f t="shared" si="4"/>
         <v>8430</v>
       </c>
       <c r="C204" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17600</v>
       </c>
     </row>
@@ -33877,11 +33877,11 @@
         <v>177</v>
       </c>
       <c r="B205" s="13">
-        <f>$B$11+$B$20*A205</f>
+        <f t="shared" si="4"/>
         <v>8470</v>
       </c>
       <c r="C205" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17700</v>
       </c>
     </row>
@@ -33890,11 +33890,11 @@
         <v>178</v>
       </c>
       <c r="B206" s="13">
-        <f>$B$11+$B$20*A206</f>
+        <f t="shared" si="4"/>
         <v>8510</v>
       </c>
       <c r="C206" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17800</v>
       </c>
     </row>
@@ -33903,11 +33903,11 @@
         <v>179</v>
       </c>
       <c r="B207" s="13">
-        <f>$B$11+$B$20*A207</f>
+        <f t="shared" si="4"/>
         <v>8550</v>
       </c>
       <c r="C207" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17900</v>
       </c>
     </row>
@@ -33916,11 +33916,11 @@
         <v>180</v>
       </c>
       <c r="B208" s="13">
-        <f>$B$11+$B$20*A208</f>
+        <f t="shared" si="4"/>
         <v>8590</v>
       </c>
       <c r="C208" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>18000</v>
       </c>
     </row>
@@ -33929,11 +33929,11 @@
         <v>181</v>
       </c>
       <c r="B209" s="13">
-        <f>$B$11+$B$20*A209</f>
+        <f t="shared" si="4"/>
         <v>8630</v>
       </c>
       <c r="C209" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>18100</v>
       </c>
     </row>
@@ -33942,11 +33942,11 @@
         <v>182</v>
       </c>
       <c r="B210" s="13">
-        <f>$B$11+$B$20*A210</f>
+        <f t="shared" si="4"/>
         <v>8670</v>
       </c>
       <c r="C210" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>18200</v>
       </c>
     </row>
@@ -33955,11 +33955,11 @@
         <v>183</v>
       </c>
       <c r="B211" s="13">
-        <f>$B$11+$B$20*A211</f>
+        <f t="shared" si="4"/>
         <v>8710</v>
       </c>
       <c r="C211" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>18300</v>
       </c>
     </row>
@@ -33968,11 +33968,11 @@
         <v>184</v>
       </c>
       <c r="B212" s="13">
-        <f>$B$11+$B$20*A212</f>
+        <f t="shared" si="4"/>
         <v>8750</v>
       </c>
       <c r="C212" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>18400</v>
       </c>
     </row>
@@ -33981,11 +33981,11 @@
         <v>185</v>
       </c>
       <c r="B213" s="13">
-        <f>$B$11+$B$20*A213</f>
+        <f t="shared" si="4"/>
         <v>8790</v>
       </c>
       <c r="C213" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>18500</v>
       </c>
     </row>
@@ -33994,11 +33994,11 @@
         <v>186</v>
       </c>
       <c r="B214" s="13">
-        <f>$B$11+$B$20*A214</f>
+        <f t="shared" si="4"/>
         <v>8830</v>
       </c>
       <c r="C214" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>18600</v>
       </c>
     </row>
@@ -34007,11 +34007,11 @@
         <v>187</v>
       </c>
       <c r="B215" s="13">
-        <f>$B$11+$B$20*A215</f>
+        <f t="shared" si="4"/>
         <v>8870</v>
       </c>
       <c r="C215" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>18700</v>
       </c>
     </row>
@@ -34020,11 +34020,11 @@
         <v>188</v>
       </c>
       <c r="B216" s="13">
-        <f>$B$11+$B$20*A216</f>
+        <f t="shared" si="4"/>
         <v>8910</v>
       </c>
       <c r="C216" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>18800</v>
       </c>
     </row>
@@ -34033,11 +34033,11 @@
         <v>189</v>
       </c>
       <c r="B217" s="13">
-        <f>$B$11+$B$20*A217</f>
+        <f t="shared" si="4"/>
         <v>8950</v>
       </c>
       <c r="C217" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>18900</v>
       </c>
     </row>
@@ -34046,11 +34046,11 @@
         <v>190</v>
       </c>
       <c r="B218" s="13">
-        <f>$B$11+$B$20*A218</f>
+        <f t="shared" si="4"/>
         <v>8990</v>
       </c>
       <c r="C218" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>19000</v>
       </c>
     </row>
@@ -34059,11 +34059,11 @@
         <v>191</v>
       </c>
       <c r="B219" s="13">
-        <f>$B$11+$B$20*A219</f>
+        <f t="shared" si="4"/>
         <v>9030</v>
       </c>
       <c r="C219" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>19100</v>
       </c>
     </row>
@@ -34072,11 +34072,11 @@
         <v>192</v>
       </c>
       <c r="B220" s="13">
-        <f>$B$11+$B$20*A220</f>
+        <f t="shared" ref="B220:B283" si="6">$B$11+$B$20*A220</f>
         <v>9070</v>
       </c>
       <c r="C220" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>19200</v>
       </c>
     </row>
@@ -34085,11 +34085,11 @@
         <v>193</v>
       </c>
       <c r="B221" s="13">
-        <f>$B$11+$B$20*A221</f>
+        <f t="shared" si="6"/>
         <v>9110</v>
       </c>
       <c r="C221" s="9">
-        <f t="shared" ref="C221:C228" si="3">$B$23*A221</f>
+        <f t="shared" ref="C221:C228" si="7">$B$23*A221</f>
         <v>19300</v>
       </c>
     </row>
@@ -34098,11 +34098,11 @@
         <v>194</v>
       </c>
       <c r="B222" s="13">
-        <f>$B$11+$B$20*A222</f>
+        <f t="shared" si="6"/>
         <v>9150</v>
       </c>
       <c r="C222" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>19400</v>
       </c>
     </row>
@@ -34111,11 +34111,11 @@
         <v>195</v>
       </c>
       <c r="B223" s="13">
-        <f>$B$11+$B$20*A223</f>
+        <f t="shared" si="6"/>
         <v>9190</v>
       </c>
       <c r="C223" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>19500</v>
       </c>
     </row>
@@ -34124,11 +34124,11 @@
         <v>196</v>
       </c>
       <c r="B224" s="13">
-        <f>$B$11+$B$20*A224</f>
+        <f t="shared" si="6"/>
         <v>9230</v>
       </c>
       <c r="C224" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>19600</v>
       </c>
     </row>
@@ -34137,11 +34137,11 @@
         <v>197</v>
       </c>
       <c r="B225" s="13">
-        <f>$B$11+$B$20*A225</f>
+        <f t="shared" si="6"/>
         <v>9270</v>
       </c>
       <c r="C225" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>19700</v>
       </c>
     </row>
@@ -34150,11 +34150,11 @@
         <v>198</v>
       </c>
       <c r="B226" s="13">
-        <f>$B$11+$B$20*A226</f>
+        <f t="shared" si="6"/>
         <v>9310</v>
       </c>
       <c r="C226" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>19800</v>
       </c>
     </row>
@@ -34163,11 +34163,11 @@
         <v>199</v>
       </c>
       <c r="B227" s="13">
-        <f>$B$11+$B$20*A227</f>
+        <f t="shared" si="6"/>
         <v>9350</v>
       </c>
       <c r="C227" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>19900</v>
       </c>
     </row>
@@ -34176,11 +34176,11 @@
         <v>200</v>
       </c>
       <c r="B228" s="13">
-        <f>$B$11+$B$20*A228</f>
+        <f t="shared" si="6"/>
         <v>9390</v>
       </c>
       <c r="C228" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>20000</v>
       </c>
     </row>
@@ -34195,23 +34195,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5cfc5781-36c7-40ed-af62-43a27290b458" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008C371D7D644B574CA89B5F00ED09B0C8" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="bd33285d5daf4dee329ae000bb583124">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5cfc5781-36c7-40ed-af62-43a27290b458" xmlns:ns4="c4b568bc-dd8a-4a74-b92a-f01b2ee1149b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6974282011ce0aef1ed393e1233ba8cc" ns3:_="" ns4:_="">
     <xsd:import namespace="5cfc5781-36c7-40ed-af62-43a27290b458"/>
@@ -34444,32 +34427,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4FBB6FF-EC5C-4DA6-BDE2-BFD391C0AAC1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="5cfc5781-36c7-40ed-af62-43a27290b458"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="c4b568bc-dd8a-4a74-b92a-f01b2ee1149b"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5725DCE3-03BC-44D7-BC9C-71C7B5BFC1A0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5cfc5781-36c7-40ed-af62-43a27290b458" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7417AF40-C3B2-4E1A-88EB-AB01B9312A09}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34486,4 +34461,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5725DCE3-03BC-44D7-BC9C-71C7B5BFC1A0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4FBB6FF-EC5C-4DA6-BDE2-BFD391C0AAC1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="5cfc5781-36c7-40ed-af62-43a27290b458"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c4b568bc-dd8a-4a74-b92a-f01b2ee1149b"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>